--- a/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -794,25 +794,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1839100</v>
+        <v>1907400</v>
       </c>
       <c r="E8" s="3">
-        <v>1849700</v>
+        <v>1918400</v>
       </c>
       <c r="F8" s="3">
-        <v>1754800</v>
+        <v>1820100</v>
       </c>
       <c r="G8" s="3">
-        <v>1415800</v>
+        <v>1468400</v>
       </c>
       <c r="H8" s="3">
-        <v>2600000</v>
+        <v>2696700</v>
       </c>
       <c r="I8" s="3">
-        <v>2564200</v>
+        <v>2659500</v>
       </c>
       <c r="J8" s="3">
-        <v>2470200</v>
+        <v>2562100</v>
       </c>
       <c r="K8" s="3">
         <v>1417100</v>
@@ -886,25 +886,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>413900</v>
+        <v>429200</v>
       </c>
       <c r="E9" s="3">
-        <v>427900</v>
+        <v>443800</v>
       </c>
       <c r="F9" s="3">
-        <v>426900</v>
+        <v>442800</v>
       </c>
       <c r="G9" s="3">
-        <v>422500</v>
+        <v>438200</v>
       </c>
       <c r="H9" s="3">
-        <v>664600</v>
+        <v>689300</v>
       </c>
       <c r="I9" s="3">
-        <v>671800</v>
+        <v>696700</v>
       </c>
       <c r="J9" s="3">
-        <v>656000</v>
+        <v>680400</v>
       </c>
       <c r="K9" s="3">
         <v>426600</v>
@@ -978,25 +978,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1425200</v>
+        <v>1478200</v>
       </c>
       <c r="E10" s="3">
-        <v>1421700</v>
+        <v>1474600</v>
       </c>
       <c r="F10" s="3">
-        <v>1327900</v>
+        <v>1377300</v>
       </c>
       <c r="G10" s="3">
-        <v>993300</v>
+        <v>1030300</v>
       </c>
       <c r="H10" s="3">
-        <v>1935400</v>
+        <v>2007300</v>
       </c>
       <c r="I10" s="3">
-        <v>1892400</v>
+        <v>1962700</v>
       </c>
       <c r="J10" s="3">
-        <v>1814200</v>
+        <v>1881600</v>
       </c>
       <c r="K10" s="3">
         <v>990500</v>
@@ -1288,25 +1288,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>9100</v>
+        <v>9400</v>
       </c>
       <c r="E14" s="3">
-        <v>51800</v>
+        <v>53700</v>
       </c>
       <c r="F14" s="3">
-        <v>16800</v>
+        <v>17500</v>
       </c>
       <c r="G14" s="3">
-        <v>31200</v>
+        <v>32300</v>
       </c>
       <c r="H14" s="3">
-        <v>10400</v>
+        <v>10800</v>
       </c>
       <c r="I14" s="3">
-        <v>250500</v>
+        <v>259800</v>
       </c>
       <c r="J14" s="3">
-        <v>16300</v>
+        <v>16900</v>
       </c>
       <c r="K14" s="3">
         <v>93600</v>
@@ -1380,25 +1380,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>376400</v>
+        <v>390400</v>
       </c>
       <c r="E15" s="3">
-        <v>384600</v>
+        <v>398900</v>
       </c>
       <c r="F15" s="3">
-        <v>367600</v>
+        <v>381200</v>
       </c>
       <c r="G15" s="3">
-        <v>356100</v>
+        <v>369400</v>
       </c>
       <c r="H15" s="3">
-        <v>590700</v>
+        <v>612700</v>
       </c>
       <c r="I15" s="3">
-        <v>599700</v>
+        <v>622000</v>
       </c>
       <c r="J15" s="3">
-        <v>581700</v>
+        <v>603300</v>
       </c>
       <c r="K15" s="3">
         <v>360100</v>
@@ -1503,25 +1503,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1378700</v>
+        <v>1429900</v>
       </c>
       <c r="E17" s="3">
-        <v>1493500</v>
+        <v>1549100</v>
       </c>
       <c r="F17" s="3">
-        <v>1404200</v>
+        <v>1456400</v>
       </c>
       <c r="G17" s="3">
-        <v>1332700</v>
+        <v>1382200</v>
       </c>
       <c r="H17" s="3">
-        <v>2009800</v>
+        <v>2084500</v>
       </c>
       <c r="I17" s="3">
-        <v>2283600</v>
+        <v>2368500</v>
       </c>
       <c r="J17" s="3">
-        <v>1843900</v>
+        <v>1912500</v>
       </c>
       <c r="K17" s="3">
         <v>1395100</v>
@@ -1595,25 +1595,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>460400</v>
+        <v>477500</v>
       </c>
       <c r="E18" s="3">
-        <v>356100</v>
+        <v>369400</v>
       </c>
       <c r="F18" s="3">
-        <v>350700</v>
+        <v>363700</v>
       </c>
       <c r="G18" s="3">
-        <v>83100</v>
+        <v>86200</v>
       </c>
       <c r="H18" s="3">
-        <v>590200</v>
+        <v>612100</v>
       </c>
       <c r="I18" s="3">
-        <v>280600</v>
+        <v>291000</v>
       </c>
       <c r="J18" s="3">
-        <v>626300</v>
+        <v>649600</v>
       </c>
       <c r="K18" s="3">
         <v>22000</v>
@@ -1721,25 +1721,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>26300</v>
+        <v>27300</v>
       </c>
       <c r="E20" s="3">
-        <v>-84500</v>
+        <v>-87700</v>
       </c>
       <c r="F20" s="3">
-        <v>-312800</v>
+        <v>-324400</v>
       </c>
       <c r="G20" s="3">
-        <v>53100</v>
+        <v>55100</v>
       </c>
       <c r="H20" s="3">
-        <v>-221900</v>
+        <v>-230100</v>
       </c>
       <c r="I20" s="3">
-        <v>-203700</v>
+        <v>-211300</v>
       </c>
       <c r="J20" s="3">
-        <v>15200</v>
+        <v>15700</v>
       </c>
       <c r="K20" s="3">
         <v>-9600</v>
@@ -1813,25 +1813,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>862500</v>
+        <v>894500</v>
       </c>
       <c r="E21" s="3">
-        <v>657500</v>
+        <v>681900</v>
       </c>
       <c r="F21" s="3">
-        <v>493600</v>
+        <v>512000</v>
       </c>
       <c r="G21" s="3">
-        <v>718100</v>
+        <v>744800</v>
       </c>
       <c r="H21" s="3">
-        <v>957100</v>
+        <v>992700</v>
       </c>
       <c r="I21" s="3">
-        <v>905300</v>
+        <v>938900</v>
       </c>
       <c r="J21" s="3">
-        <v>1223200</v>
+        <v>1268700</v>
       </c>
       <c r="K21" s="3">
         <v>712400</v>
@@ -1905,25 +1905,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>69100</v>
+        <v>71600</v>
       </c>
       <c r="E22" s="3">
-        <v>62400</v>
+        <v>64700</v>
       </c>
       <c r="F22" s="3">
-        <v>42400</v>
+        <v>44000</v>
       </c>
       <c r="G22" s="3">
-        <v>70700</v>
+        <v>73300</v>
       </c>
       <c r="H22" s="3">
-        <v>70500</v>
+        <v>73100</v>
       </c>
       <c r="I22" s="3">
-        <v>56600</v>
+        <v>58700</v>
       </c>
       <c r="J22" s="3">
-        <v>43600</v>
+        <v>45200</v>
       </c>
       <c r="K22" s="3">
         <v>48700</v>
@@ -1997,25 +1997,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>417700</v>
+        <v>433200</v>
       </c>
       <c r="E23" s="3">
-        <v>209300</v>
+        <v>217000</v>
       </c>
       <c r="F23" s="3">
-        <v>-4600</v>
+        <v>-4700</v>
       </c>
       <c r="G23" s="3">
-        <v>65600</v>
+        <v>68000</v>
       </c>
       <c r="H23" s="3">
-        <v>297800</v>
+        <v>308900</v>
       </c>
       <c r="I23" s="3">
-        <v>20300</v>
+        <v>21100</v>
       </c>
       <c r="J23" s="3">
-        <v>597900</v>
+        <v>620100</v>
       </c>
       <c r="K23" s="3">
         <v>-36300</v>
@@ -2089,25 +2089,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>151400</v>
+        <v>157000</v>
       </c>
       <c r="E24" s="3">
-        <v>65600</v>
+        <v>68000</v>
       </c>
       <c r="F24" s="3">
-        <v>17300</v>
+        <v>17900</v>
       </c>
       <c r="G24" s="3">
-        <v>-233400</v>
+        <v>-242100</v>
       </c>
       <c r="H24" s="3">
-        <v>98800</v>
+        <v>102400</v>
       </c>
       <c r="I24" s="3">
-        <v>-35000</v>
+        <v>-36300</v>
       </c>
       <c r="J24" s="3">
-        <v>-96900</v>
+        <v>-100500</v>
       </c>
       <c r="K24" s="3">
         <v>39800</v>
@@ -2273,25 +2273,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>266300</v>
+        <v>276200</v>
       </c>
       <c r="E26" s="3">
-        <v>143700</v>
+        <v>149000</v>
       </c>
       <c r="F26" s="3">
-        <v>-21900</v>
+        <v>-22700</v>
       </c>
       <c r="G26" s="3">
-        <v>299000</v>
+        <v>310100</v>
       </c>
       <c r="H26" s="3">
-        <v>199000</v>
+        <v>206400</v>
       </c>
       <c r="I26" s="3">
-        <v>55300</v>
+        <v>57400</v>
       </c>
       <c r="J26" s="3">
-        <v>694700</v>
+        <v>720600</v>
       </c>
       <c r="K26" s="3">
         <v>-76100</v>
@@ -2365,25 +2365,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>230700</v>
+        <v>239200</v>
       </c>
       <c r="E27" s="3">
-        <v>88000</v>
+        <v>91300</v>
       </c>
       <c r="F27" s="3">
-        <v>-56500</v>
+        <v>-58600</v>
       </c>
       <c r="G27" s="3">
-        <v>259100</v>
+        <v>268700</v>
       </c>
       <c r="H27" s="3">
-        <v>128200</v>
+        <v>133000</v>
       </c>
       <c r="I27" s="3">
-        <v>-15500</v>
+        <v>-16100</v>
       </c>
       <c r="J27" s="3">
-        <v>632400</v>
+        <v>656000</v>
       </c>
       <c r="K27" s="3">
         <v>-142100</v>
@@ -2549,25 +2549,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-6500</v>
+        <v>-6700</v>
       </c>
       <c r="E29" s="3">
-        <v>-12900</v>
+        <v>-13400</v>
       </c>
       <c r="F29" s="3">
-        <v>1716200</v>
+        <v>1780000</v>
       </c>
       <c r="G29" s="3">
-        <v>3207900</v>
+        <v>3327100</v>
       </c>
       <c r="H29" s="3">
-        <v>13400</v>
+        <v>13900</v>
       </c>
       <c r="I29" s="3">
-        <v>-86200</v>
+        <v>-89500</v>
       </c>
       <c r="J29" s="3">
-        <v>-31600</v>
+        <v>-32700</v>
       </c>
       <c r="K29" s="3">
         <v>147100</v>
@@ -2825,25 +2825,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-26300</v>
+        <v>-27300</v>
       </c>
       <c r="E32" s="3">
-        <v>84500</v>
+        <v>87700</v>
       </c>
       <c r="F32" s="3">
-        <v>312800</v>
+        <v>324400</v>
       </c>
       <c r="G32" s="3">
-        <v>-53100</v>
+        <v>-55100</v>
       </c>
       <c r="H32" s="3">
-        <v>221900</v>
+        <v>230100</v>
       </c>
       <c r="I32" s="3">
-        <v>203700</v>
+        <v>211300</v>
       </c>
       <c r="J32" s="3">
-        <v>-15200</v>
+        <v>-15700</v>
       </c>
       <c r="K32" s="3">
         <v>9600</v>
@@ -2917,25 +2917,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>224200</v>
+        <v>232500</v>
       </c>
       <c r="E33" s="3">
-        <v>75100</v>
+        <v>77900</v>
       </c>
       <c r="F33" s="3">
-        <v>1659600</v>
+        <v>1721300</v>
       </c>
       <c r="G33" s="3">
-        <v>3467000</v>
+        <v>3595900</v>
       </c>
       <c r="H33" s="3">
-        <v>141700</v>
+        <v>146900</v>
       </c>
       <c r="I33" s="3">
-        <v>-101800</v>
+        <v>-105600</v>
       </c>
       <c r="J33" s="3">
-        <v>600900</v>
+        <v>623200</v>
       </c>
       <c r="K33" s="3">
         <v>5000</v>
@@ -3101,25 +3101,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>224200</v>
+        <v>232500</v>
       </c>
       <c r="E35" s="3">
-        <v>75100</v>
+        <v>77900</v>
       </c>
       <c r="F35" s="3">
-        <v>1659600</v>
+        <v>1721300</v>
       </c>
       <c r="G35" s="3">
-        <v>3467000</v>
+        <v>3595900</v>
       </c>
       <c r="H35" s="3">
-        <v>141700</v>
+        <v>146900</v>
       </c>
       <c r="I35" s="3">
-        <v>-101800</v>
+        <v>-105600</v>
       </c>
       <c r="J35" s="3">
-        <v>600900</v>
+        <v>623200</v>
       </c>
       <c r="K35" s="3">
         <v>5000</v>
@@ -3358,25 +3358,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>888100</v>
+        <v>921100</v>
       </c>
       <c r="E41" s="3">
-        <v>1145400</v>
+        <v>1187900</v>
       </c>
       <c r="F41" s="3">
-        <v>1312500</v>
+        <v>1361200</v>
       </c>
       <c r="G41" s="3">
-        <v>908100</v>
+        <v>941900</v>
       </c>
       <c r="H41" s="3">
-        <v>1483800</v>
+        <v>1539000</v>
       </c>
       <c r="I41" s="3">
-        <v>860800</v>
+        <v>892800</v>
       </c>
       <c r="J41" s="3">
-        <v>1902200</v>
+        <v>1972900</v>
       </c>
       <c r="K41" s="3">
         <v>1431900</v>
@@ -3450,25 +3450,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>75000</v>
+        <v>77800</v>
       </c>
       <c r="E42" s="3">
-        <v>76100</v>
+        <v>78900</v>
       </c>
       <c r="F42" s="3">
-        <v>54000</v>
+        <v>56000</v>
       </c>
       <c r="G42" s="3">
-        <v>33000</v>
+        <v>34200</v>
       </c>
       <c r="H42" s="3">
-        <v>67200</v>
+        <v>69700</v>
       </c>
       <c r="I42" s="3">
-        <v>55400</v>
+        <v>57500</v>
       </c>
       <c r="J42" s="3">
-        <v>59800</v>
+        <v>62000</v>
       </c>
       <c r="K42" s="3">
         <v>78900</v>
@@ -3542,25 +3542,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1359000</v>
+        <v>1409500</v>
       </c>
       <c r="E43" s="3">
-        <v>1424900</v>
+        <v>1477900</v>
       </c>
       <c r="F43" s="3">
-        <v>1500500</v>
+        <v>1556300</v>
       </c>
       <c r="G43" s="3">
-        <v>1723300</v>
+        <v>1787400</v>
       </c>
       <c r="H43" s="3">
-        <v>2075000</v>
+        <v>2152200</v>
       </c>
       <c r="I43" s="3">
-        <v>2090000</v>
+        <v>2167600</v>
       </c>
       <c r="J43" s="3">
-        <v>1953000</v>
+        <v>2025600</v>
       </c>
       <c r="K43" s="3">
         <v>2044800</v>
@@ -3634,25 +3634,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>97300</v>
+        <v>100900</v>
       </c>
       <c r="E44" s="3">
-        <v>114100</v>
+        <v>118300</v>
       </c>
       <c r="F44" s="3">
-        <v>117300</v>
+        <v>121700</v>
       </c>
       <c r="G44" s="3">
-        <v>142600</v>
+        <v>147900</v>
       </c>
       <c r="H44" s="3">
-        <v>168300</v>
+        <v>174500</v>
       </c>
       <c r="I44" s="3">
-        <v>152900</v>
+        <v>158600</v>
       </c>
       <c r="J44" s="3">
-        <v>142900</v>
+        <v>148200</v>
       </c>
       <c r="K44" s="3">
         <v>147000</v>
@@ -3726,25 +3726,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>82800</v>
+        <v>85800</v>
       </c>
       <c r="E45" s="3">
-        <v>68100</v>
+        <v>70700</v>
       </c>
       <c r="F45" s="3">
-        <v>49300</v>
+        <v>51100</v>
       </c>
       <c r="G45" s="3">
-        <v>136400</v>
+        <v>141400</v>
       </c>
       <c r="H45" s="3">
-        <v>136600</v>
+        <v>141700</v>
       </c>
       <c r="I45" s="3">
-        <v>149400</v>
+        <v>154900</v>
       </c>
       <c r="J45" s="3">
-        <v>135800</v>
+        <v>140900</v>
       </c>
       <c r="K45" s="3">
         <v>421300</v>
@@ -3818,25 +3818,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2502200</v>
+        <v>2595200</v>
       </c>
       <c r="E46" s="3">
-        <v>2828600</v>
+        <v>2933700</v>
       </c>
       <c r="F46" s="3">
-        <v>3033500</v>
+        <v>3146300</v>
       </c>
       <c r="G46" s="3">
-        <v>2943400</v>
+        <v>3052800</v>
       </c>
       <c r="H46" s="3">
-        <v>3931000</v>
+        <v>4077200</v>
       </c>
       <c r="I46" s="3">
-        <v>3308500</v>
+        <v>3431500</v>
       </c>
       <c r="J46" s="3">
-        <v>4193700</v>
+        <v>4349600</v>
       </c>
       <c r="K46" s="3">
         <v>4123900</v>
@@ -3910,25 +3910,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5583600</v>
+        <v>5791200</v>
       </c>
       <c r="E47" s="3">
-        <v>5750500</v>
+        <v>5964200</v>
       </c>
       <c r="F47" s="3">
-        <v>5500400</v>
+        <v>5704900</v>
       </c>
       <c r="G47" s="3">
-        <v>3629700</v>
+        <v>3764600</v>
       </c>
       <c r="H47" s="3">
-        <v>557800</v>
+        <v>578600</v>
       </c>
       <c r="I47" s="3">
-        <v>538400</v>
+        <v>558400</v>
       </c>
       <c r="J47" s="3">
-        <v>513100</v>
+        <v>532200</v>
       </c>
       <c r="K47" s="3">
         <v>534500</v>
@@ -4002,25 +4002,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7281500</v>
+        <v>7552200</v>
       </c>
       <c r="E48" s="3">
-        <v>7439100</v>
+        <v>7715600</v>
       </c>
       <c r="F48" s="3">
-        <v>7350400</v>
+        <v>7623600</v>
       </c>
       <c r="G48" s="3">
-        <v>10183600</v>
+        <v>10562200</v>
       </c>
       <c r="H48" s="3">
-        <v>11591500</v>
+        <v>12022500</v>
       </c>
       <c r="I48" s="3">
-        <v>11479800</v>
+        <v>11906500</v>
       </c>
       <c r="J48" s="3">
-        <v>11213500</v>
+        <v>11630300</v>
       </c>
       <c r="K48" s="3">
         <v>11694700</v>
@@ -4094,25 +4094,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3148200</v>
+        <v>3265300</v>
       </c>
       <c r="E49" s="3">
-        <v>3269100</v>
+        <v>3390600</v>
       </c>
       <c r="F49" s="3">
-        <v>3206700</v>
+        <v>3325900</v>
       </c>
       <c r="G49" s="3">
-        <v>3386100</v>
+        <v>3512000</v>
       </c>
       <c r="H49" s="3">
-        <v>3552700</v>
+        <v>3684700</v>
       </c>
       <c r="I49" s="3">
-        <v>3474400</v>
+        <v>3603500</v>
       </c>
       <c r="J49" s="3">
-        <v>3299800</v>
+        <v>3422500</v>
       </c>
       <c r="K49" s="3">
         <v>3540700</v>
@@ -4370,25 +4370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1922000</v>
+        <v>1993500</v>
       </c>
       <c r="E52" s="3">
-        <v>2047100</v>
+        <v>2123300</v>
       </c>
       <c r="F52" s="3">
-        <v>2315400</v>
+        <v>2401500</v>
       </c>
       <c r="G52" s="3">
-        <v>1738900</v>
+        <v>1803600</v>
       </c>
       <c r="H52" s="3">
-        <v>1730100</v>
+        <v>1794500</v>
       </c>
       <c r="I52" s="3">
-        <v>1708900</v>
+        <v>1772500</v>
       </c>
       <c r="J52" s="3">
-        <v>1508400</v>
+        <v>1564500</v>
       </c>
       <c r="K52" s="3">
         <v>1339300</v>
@@ -4554,25 +4554,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>20437600</v>
+        <v>21197300</v>
       </c>
       <c r="E54" s="3">
-        <v>21334300</v>
+        <v>22127400</v>
       </c>
       <c r="F54" s="3">
-        <v>21406400</v>
+        <v>22202200</v>
       </c>
       <c r="G54" s="3">
-        <v>21881700</v>
+        <v>22695200</v>
       </c>
       <c r="H54" s="3">
-        <v>21363200</v>
+        <v>22157400</v>
       </c>
       <c r="I54" s="3">
-        <v>20510000</v>
+        <v>21272400</v>
       </c>
       <c r="J54" s="3">
-        <v>20728500</v>
+        <v>21499100</v>
       </c>
       <c r="K54" s="3">
         <v>21233100</v>
@@ -4714,25 +4714,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1898200</v>
+        <v>1968700</v>
       </c>
       <c r="E57" s="3">
-        <v>1979900</v>
+        <v>2053500</v>
       </c>
       <c r="F57" s="3">
-        <v>2013100</v>
+        <v>2088000</v>
       </c>
       <c r="G57" s="3">
-        <v>2581600</v>
+        <v>2677600</v>
       </c>
       <c r="H57" s="3">
-        <v>2881500</v>
+        <v>2988700</v>
       </c>
       <c r="I57" s="3">
-        <v>2848900</v>
+        <v>2954800</v>
       </c>
       <c r="J57" s="3">
-        <v>2822400</v>
+        <v>2927300</v>
       </c>
       <c r="K57" s="3">
         <v>3040000</v>
@@ -4806,25 +4806,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>916300</v>
+        <v>950400</v>
       </c>
       <c r="E58" s="3">
-        <v>1581800</v>
+        <v>1640600</v>
       </c>
       <c r="F58" s="3">
-        <v>1361100</v>
+        <v>1411700</v>
       </c>
       <c r="G58" s="3">
-        <v>1449000</v>
+        <v>1502900</v>
       </c>
       <c r="H58" s="3">
-        <v>1623700</v>
+        <v>1684000</v>
       </c>
       <c r="I58" s="3">
-        <v>1194200</v>
+        <v>1238600</v>
       </c>
       <c r="J58" s="3">
-        <v>1433100</v>
+        <v>1486400</v>
       </c>
       <c r="K58" s="3">
         <v>1528800</v>
@@ -4898,25 +4898,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1285700</v>
+        <v>1333500</v>
       </c>
       <c r="E59" s="3">
-        <v>1250000</v>
+        <v>1296500</v>
       </c>
       <c r="F59" s="3">
-        <v>794400</v>
+        <v>824000</v>
       </c>
       <c r="G59" s="3">
-        <v>887800</v>
+        <v>920800</v>
       </c>
       <c r="H59" s="3">
-        <v>1627700</v>
+        <v>1688200</v>
       </c>
       <c r="I59" s="3">
-        <v>1563900</v>
+        <v>1622000</v>
       </c>
       <c r="J59" s="3">
-        <v>1092600</v>
+        <v>1133200</v>
       </c>
       <c r="K59" s="3">
         <v>1278700</v>
@@ -4990,25 +4990,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4100200</v>
+        <v>4252700</v>
       </c>
       <c r="E60" s="3">
-        <v>4811700</v>
+        <v>4990600</v>
       </c>
       <c r="F60" s="3">
-        <v>4168700</v>
+        <v>4323600</v>
       </c>
       <c r="G60" s="3">
-        <v>4918400</v>
+        <v>5101300</v>
       </c>
       <c r="H60" s="3">
-        <v>6132900</v>
+        <v>6360900</v>
       </c>
       <c r="I60" s="3">
-        <v>5607000</v>
+        <v>5815400</v>
       </c>
       <c r="J60" s="3">
-        <v>5348000</v>
+        <v>5546800</v>
       </c>
       <c r="K60" s="3">
         <v>5847400</v>
@@ -5082,25 +5082,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7857100</v>
+        <v>8149200</v>
       </c>
       <c r="E61" s="3">
-        <v>8124700</v>
+        <v>8426700</v>
       </c>
       <c r="F61" s="3">
-        <v>7644000</v>
+        <v>7928200</v>
       </c>
       <c r="G61" s="3">
-        <v>9799100</v>
+        <v>10163400</v>
       </c>
       <c r="H61" s="3">
-        <v>10883400</v>
+        <v>11288000</v>
       </c>
       <c r="I61" s="3">
-        <v>10922000</v>
+        <v>11328000</v>
       </c>
       <c r="J61" s="3">
-        <v>10349000</v>
+        <v>10733700</v>
       </c>
       <c r="K61" s="3">
         <v>10902700</v>
@@ -5174,25 +5174,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1157200</v>
+        <v>1200200</v>
       </c>
       <c r="E62" s="3">
-        <v>1177000</v>
+        <v>1220800</v>
       </c>
       <c r="F62" s="3">
-        <v>1238000</v>
+        <v>1284000</v>
       </c>
       <c r="G62" s="3">
-        <v>1276400</v>
+        <v>1323900</v>
       </c>
       <c r="H62" s="3">
-        <v>1630800</v>
+        <v>1691400</v>
       </c>
       <c r="I62" s="3">
-        <v>1506100</v>
+        <v>1562100</v>
       </c>
       <c r="J62" s="3">
-        <v>1428100</v>
+        <v>1481200</v>
       </c>
       <c r="K62" s="3">
         <v>1520100</v>
@@ -5542,25 +5542,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13646600</v>
+        <v>14153900</v>
       </c>
       <c r="E66" s="3">
-        <v>14627900</v>
+        <v>15171700</v>
       </c>
       <c r="F66" s="3">
-        <v>13560200</v>
+        <v>14064300</v>
       </c>
       <c r="G66" s="3">
-        <v>16381500</v>
+        <v>16990500</v>
       </c>
       <c r="H66" s="3">
-        <v>19101500</v>
+        <v>19811600</v>
       </c>
       <c r="I66" s="3">
-        <v>18518300</v>
+        <v>19206700</v>
       </c>
       <c r="J66" s="3">
-        <v>17627500</v>
+        <v>18282800</v>
       </c>
       <c r="K66" s="3">
         <v>18759900</v>
@@ -6036,25 +6036,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>6484100</v>
+        <v>6725200</v>
       </c>
       <c r="E72" s="3">
-        <v>6243700</v>
+        <v>6475800</v>
       </c>
       <c r="F72" s="3">
-        <v>7315500</v>
+        <v>7587500</v>
       </c>
       <c r="G72" s="3">
-        <v>5038600</v>
+        <v>5225900</v>
       </c>
       <c r="H72" s="3">
-        <v>1673000</v>
+        <v>1735200</v>
       </c>
       <c r="I72" s="3">
-        <v>1494300</v>
+        <v>1549800</v>
       </c>
       <c r="J72" s="3">
-        <v>2745600</v>
+        <v>2847700</v>
       </c>
       <c r="K72" s="3">
         <v>2111700</v>
@@ -6404,25 +6404,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6791000</v>
+        <v>7043400</v>
       </c>
       <c r="E76" s="3">
-        <v>6706400</v>
+        <v>6955700</v>
       </c>
       <c r="F76" s="3">
-        <v>7846200</v>
+        <v>8137800</v>
       </c>
       <c r="G76" s="3">
-        <v>5500200</v>
+        <v>5704700</v>
       </c>
       <c r="H76" s="3">
-        <v>2261700</v>
+        <v>2345800</v>
       </c>
       <c r="I76" s="3">
-        <v>1991700</v>
+        <v>2065800</v>
       </c>
       <c r="J76" s="3">
-        <v>3101000</v>
+        <v>3216200</v>
       </c>
       <c r="K76" s="3">
         <v>2473200</v>
@@ -6685,25 +6685,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>224200</v>
+        <v>232500</v>
       </c>
       <c r="E81" s="3">
-        <v>75100</v>
+        <v>77900</v>
       </c>
       <c r="F81" s="3">
-        <v>1659600</v>
+        <v>1721300</v>
       </c>
       <c r="G81" s="3">
-        <v>3467000</v>
+        <v>3595900</v>
       </c>
       <c r="H81" s="3">
-        <v>141700</v>
+        <v>146900</v>
       </c>
       <c r="I81" s="3">
-        <v>-101800</v>
+        <v>-105600</v>
       </c>
       <c r="J81" s="3">
-        <v>600900</v>
+        <v>623200</v>
       </c>
       <c r="K81" s="3">
         <v>5000</v>
@@ -6811,25 +6811,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>375700</v>
+        <v>389700</v>
       </c>
       <c r="E83" s="3">
-        <v>385900</v>
+        <v>400200</v>
       </c>
       <c r="F83" s="3">
-        <v>455700</v>
+        <v>472700</v>
       </c>
       <c r="G83" s="3">
-        <v>581900</v>
+        <v>603500</v>
       </c>
       <c r="H83" s="3">
-        <v>588800</v>
+        <v>610700</v>
       </c>
       <c r="I83" s="3">
-        <v>828400</v>
+        <v>859100</v>
       </c>
       <c r="J83" s="3">
-        <v>581700</v>
+        <v>603300</v>
       </c>
       <c r="K83" s="3">
         <v>700000</v>
@@ -7363,25 +7363,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>768800</v>
+        <v>797400</v>
       </c>
       <c r="E89" s="3">
-        <v>520700</v>
+        <v>540000</v>
       </c>
       <c r="F89" s="3">
-        <v>558100</v>
+        <v>578800</v>
       </c>
       <c r="G89" s="3">
-        <v>856600</v>
+        <v>888500</v>
       </c>
       <c r="H89" s="3">
-        <v>992700</v>
+        <v>1029600</v>
       </c>
       <c r="I89" s="3">
-        <v>877000</v>
+        <v>909600</v>
       </c>
       <c r="J89" s="3">
-        <v>861000</v>
+        <v>893000</v>
       </c>
       <c r="K89" s="3">
         <v>801700</v>
@@ -7765,25 +7765,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-290300</v>
+        <v>-301100</v>
       </c>
       <c r="E94" s="3">
-        <v>-357300</v>
+        <v>-370600</v>
       </c>
       <c r="F94" s="3">
-        <v>188800</v>
+        <v>195800</v>
       </c>
       <c r="G94" s="3">
-        <v>-1052800</v>
+        <v>-1091900</v>
       </c>
       <c r="H94" s="3">
-        <v>-279500</v>
+        <v>-289900</v>
       </c>
       <c r="I94" s="3">
-        <v>-502300</v>
+        <v>-521000</v>
       </c>
       <c r="J94" s="3">
-        <v>-282200</v>
+        <v>-292700</v>
       </c>
       <c r="K94" s="3">
         <v>-469500</v>
@@ -7894,19 +7894,19 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-633200</v>
+        <v>-656700</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-550400</v>
+        <v>-570900</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-639900</v>
+        <v>-663700</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -8259,25 +8259,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-746600</v>
+        <v>-774300</v>
       </c>
       <c r="E100" s="3">
-        <v>-370600</v>
+        <v>-384400</v>
       </c>
       <c r="F100" s="3">
-        <v>-370200</v>
+        <v>-384000</v>
       </c>
       <c r="G100" s="3">
-        <v>-358500</v>
+        <v>-371900</v>
       </c>
       <c r="H100" s="3">
-        <v>-168600</v>
+        <v>-174800</v>
       </c>
       <c r="I100" s="3">
-        <v>-1420100</v>
+        <v>-1472900</v>
       </c>
       <c r="J100" s="3">
-        <v>-246400</v>
+        <v>-255600</v>
       </c>
       <c r="K100" s="3">
         <v>-933400</v>
@@ -8351,25 +8351,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E101" s="3">
-        <v>13700</v>
+        <v>14200</v>
       </c>
       <c r="F101" s="3">
-        <v>40200</v>
+        <v>41700</v>
       </c>
       <c r="G101" s="3">
-        <v>-23200</v>
+        <v>-24100</v>
       </c>
       <c r="H101" s="3">
-        <v>70800</v>
+        <v>73400</v>
       </c>
       <c r="I101" s="3">
-        <v>20200</v>
+        <v>21000</v>
       </c>
       <c r="J101" s="3">
-        <v>-12900</v>
+        <v>-13400</v>
       </c>
       <c r="K101" s="3">
         <v>19600</v>
@@ -8443,25 +8443,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-267400</v>
+        <v>-277400</v>
       </c>
       <c r="E102" s="3">
-        <v>-193500</v>
+        <v>-200700</v>
       </c>
       <c r="F102" s="3">
-        <v>416900</v>
+        <v>432400</v>
       </c>
       <c r="G102" s="3">
-        <v>-577900</v>
+        <v>-599400</v>
       </c>
       <c r="H102" s="3">
-        <v>615400</v>
+        <v>638300</v>
       </c>
       <c r="I102" s="3">
-        <v>-1025200</v>
+        <v>-1063300</v>
       </c>
       <c r="J102" s="3">
-        <v>319500</v>
+        <v>331300</v>
       </c>
       <c r="K102" s="3">
         <v>-581600</v>

--- a/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>TELNY</t>
   </si>
@@ -656,416 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1907400</v>
+        <v>1840400</v>
       </c>
       <c r="E8" s="3">
-        <v>1918400</v>
+        <v>1980100</v>
       </c>
       <c r="F8" s="3">
-        <v>1820100</v>
+        <v>1902000</v>
       </c>
       <c r="G8" s="3">
-        <v>1468400</v>
+        <v>1913000</v>
       </c>
       <c r="H8" s="3">
-        <v>2696700</v>
+        <v>1814900</v>
       </c>
       <c r="I8" s="3">
+        <v>1860300</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1847400</v>
+      </c>
+      <c r="K8" s="3">
         <v>2659500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2562100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1417100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2515000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2550100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>2583900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2483500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3039500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3219500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3236500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>3165100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3421100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>3112400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3010000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2674300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2820000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2813600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2777400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2247000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>3179900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3280600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>3402600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>15461200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>3853000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>429200</v>
+        <v>401800</v>
       </c>
       <c r="E9" s="3">
-        <v>443800</v>
+        <v>490400</v>
       </c>
       <c r="F9" s="3">
-        <v>442800</v>
+        <v>428000</v>
       </c>
       <c r="G9" s="3">
-        <v>438200</v>
+        <v>442600</v>
       </c>
       <c r="H9" s="3">
-        <v>689300</v>
+        <v>441500</v>
       </c>
       <c r="I9" s="3">
+        <v>460900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>406600</v>
+      </c>
+      <c r="K9" s="3">
         <v>696700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>680400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>426600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>628700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>647300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>686400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>780400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>702800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>780300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>795900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>785200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>816200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>725100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>700800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>588400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>619800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>662700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>632900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>523300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>725500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>760900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1192600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>5577700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1329500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1478200</v>
+        <v>1438600</v>
       </c>
       <c r="E10" s="3">
-        <v>1474600</v>
+        <v>1489800</v>
       </c>
       <c r="F10" s="3">
-        <v>1377300</v>
+        <v>1474000</v>
       </c>
       <c r="G10" s="3">
-        <v>1030300</v>
+        <v>1470400</v>
       </c>
       <c r="H10" s="3">
-        <v>2007300</v>
+        <v>1373400</v>
       </c>
       <c r="I10" s="3">
+        <v>1399400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1440800</v>
+      </c>
+      <c r="K10" s="3">
         <v>1962700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1881600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>990500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1886300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1902900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1897500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1703200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2336700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2439200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2440500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2380000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2605000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2387300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2309300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>2085900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2200200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>2150900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2144500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1723800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2454400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>2519700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>2210000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>9883500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>2523500</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,192 +1315,210 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-654600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>740300</v>
+      </c>
+      <c r="F14" s="3">
         <v>9400</v>
       </c>
-      <c r="E14" s="3">
-        <v>53700</v>
-      </c>
-      <c r="F14" s="3">
-        <v>17500</v>
-      </c>
       <c r="G14" s="3">
+        <v>53500</v>
+      </c>
+      <c r="H14" s="3">
+        <v>17400</v>
+      </c>
+      <c r="I14" s="3">
         <v>32300</v>
       </c>
-      <c r="H14" s="3">
-        <v>10800</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
+        <v>10500</v>
+      </c>
+      <c r="K14" s="3">
         <v>259800</v>
-      </c>
-      <c r="J14" s="3">
-        <v>16900</v>
-      </c>
-      <c r="K14" s="3">
-        <v>93600</v>
       </c>
       <c r="L14" s="3">
         <v>16900</v>
       </c>
       <c r="M14" s="3">
+        <v>93600</v>
+      </c>
+      <c r="N14" s="3">
+        <v>16900</v>
+      </c>
+      <c r="O14" s="3">
         <v>13700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>10300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>15300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>10900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>147800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>37000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>37100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>5200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>26900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>20700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>268700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>25500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>26600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>18600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>59900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>55600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>718100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>-82400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>158900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>707900</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>390400</v>
+        <v>393100</v>
       </c>
       <c r="E15" s="3">
-        <v>398900</v>
+        <v>396700</v>
       </c>
       <c r="F15" s="3">
-        <v>381200</v>
+        <v>389300</v>
       </c>
       <c r="G15" s="3">
-        <v>369400</v>
+        <v>397800</v>
       </c>
       <c r="H15" s="3">
-        <v>612700</v>
+        <v>380200</v>
       </c>
       <c r="I15" s="3">
+        <v>412700</v>
+      </c>
+      <c r="J15" s="3">
+        <v>394500</v>
+      </c>
+      <c r="K15" s="3">
         <v>622000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>603300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>360100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>607100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>603000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>599100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>459400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>722500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>761100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>722000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>756200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>757100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>666800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>637800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>462800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>553400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>529200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>547800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>457600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>556300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>570100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>581900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>2414600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>617700</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1429900</v>
+        <v>644800</v>
       </c>
       <c r="E17" s="3">
-        <v>1549100</v>
+        <v>2323900</v>
       </c>
       <c r="F17" s="3">
-        <v>1456400</v>
+        <v>1425800</v>
       </c>
       <c r="G17" s="3">
-        <v>1382200</v>
+        <v>1544700</v>
       </c>
       <c r="H17" s="3">
-        <v>2084500</v>
+        <v>1452200</v>
       </c>
       <c r="I17" s="3">
+        <v>1552100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1376400</v>
+      </c>
+      <c r="K17" s="3">
         <v>2368500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1912500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1395100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1956000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2017600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2050200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1679400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2209800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2664400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2547000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2550200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2612300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2398400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2269400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2378100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2132300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2221000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2183200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1893900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2354800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>3111300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2705400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>12375000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>3663500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>477500</v>
+        <v>1195600</v>
       </c>
       <c r="E18" s="3">
-        <v>369400</v>
+        <v>-343700</v>
       </c>
       <c r="F18" s="3">
-        <v>363700</v>
+        <v>476200</v>
       </c>
       <c r="G18" s="3">
-        <v>86200</v>
+        <v>368300</v>
       </c>
       <c r="H18" s="3">
-        <v>612100</v>
+        <v>362700</v>
       </c>
       <c r="I18" s="3">
+        <v>308200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>471100</v>
+      </c>
+      <c r="K18" s="3">
         <v>291000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>649600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>22000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>558900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>532500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>533700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>804100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>829700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>555100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>689500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>614900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>808800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>714000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>740600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>296200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>687700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>592500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>594300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>353200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>825100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>169300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>697100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>3086200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>189500</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1780,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>27300</v>
+        <v>114500</v>
       </c>
       <c r="E20" s="3">
-        <v>-87700</v>
+        <v>-134800</v>
       </c>
       <c r="F20" s="3">
-        <v>-324400</v>
+        <v>27200</v>
       </c>
       <c r="G20" s="3">
-        <v>55100</v>
+        <v>-87400</v>
       </c>
       <c r="H20" s="3">
-        <v>-230100</v>
+        <v>-323500</v>
       </c>
       <c r="I20" s="3">
+        <v>91000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-228500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-211300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>15700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-9600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-86700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-59500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>19500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>219500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>49700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>120200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-404300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>85200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-202000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>7100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>62800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-258100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>9800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-124000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>233900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-45200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>211800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>102900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>100400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-323500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>90900</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>894500</v>
+        <v>1703400</v>
       </c>
       <c r="E21" s="3">
-        <v>681900</v>
+        <v>-79600</v>
       </c>
       <c r="F21" s="3">
-        <v>512000</v>
+        <v>892000</v>
       </c>
       <c r="G21" s="3">
-        <v>744800</v>
+        <v>680000</v>
       </c>
       <c r="H21" s="3">
-        <v>992700</v>
+        <v>510500</v>
       </c>
       <c r="I21" s="3">
+        <v>1001000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>851500</v>
+      </c>
+      <c r="K21" s="3">
         <v>938900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1268700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>712400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1083600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1108000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1820400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1768500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1602000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1517400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1080600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1464700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1363200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1387700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1445100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>516500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1252700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1017600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1422600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1009200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1647600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>934400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1428400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>6219100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>1416700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>71600</v>
+        <v>93900</v>
       </c>
       <c r="E22" s="3">
-        <v>64700</v>
+        <v>61400</v>
       </c>
       <c r="F22" s="3">
-        <v>44000</v>
+        <v>71400</v>
       </c>
       <c r="G22" s="3">
-        <v>73300</v>
+        <v>64500</v>
       </c>
       <c r="H22" s="3">
-        <v>73100</v>
+        <v>43900</v>
       </c>
       <c r="I22" s="3">
+        <v>124000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>43700</v>
+      </c>
+      <c r="K22" s="3">
         <v>58700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>45200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>48700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>61000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>61600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>60700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>110900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>107400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>85400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>89800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>173900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>135400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>117100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>100900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>104900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>45900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>46200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>30500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>105800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>54700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>72700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>72500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>382700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>433200</v>
+        <v>1216200</v>
       </c>
       <c r="E23" s="3">
-        <v>217000</v>
+        <v>-539900</v>
       </c>
       <c r="F23" s="3">
+        <v>432000</v>
+      </c>
+      <c r="G23" s="3">
+        <v>216400</v>
+      </c>
+      <c r="H23" s="3">
         <v>-4700</v>
       </c>
-      <c r="G23" s="3">
-        <v>68000</v>
-      </c>
-      <c r="H23" s="3">
-        <v>308900</v>
-      </c>
       <c r="I23" s="3">
+        <v>275200</v>
+      </c>
+      <c r="J23" s="3">
+        <v>198800</v>
+      </c>
+      <c r="K23" s="3">
         <v>21100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>620100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-36300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>411200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>411400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>492600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>912600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>772100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>589800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>195400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>526300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>471500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>603900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>702600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-66900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>651500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>422300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>797600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>202200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>982200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>199500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>725000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>2379900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>210800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>157000</v>
+        <v>48900</v>
       </c>
       <c r="E24" s="3">
-        <v>68000</v>
+        <v>167500</v>
       </c>
       <c r="F24" s="3">
+        <v>156500</v>
+      </c>
+      <c r="G24" s="3">
+        <v>67800</v>
+      </c>
+      <c r="H24" s="3">
         <v>17900</v>
       </c>
-      <c r="G24" s="3">
-        <v>-242100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>102400</v>
-      </c>
       <c r="I24" s="3">
+        <v>-167900</v>
+      </c>
+      <c r="J24" s="3">
+        <v>78100</v>
+      </c>
+      <c r="K24" s="3">
         <v>-36300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-100500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>39800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>134300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>138100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>154900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>158700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>217500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>221300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>69100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>147500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>483800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>216100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>203000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>55800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>205700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>125000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>235000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>77200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>272900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>186400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>197900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>730400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>276200</v>
+        <v>1167300</v>
       </c>
       <c r="E26" s="3">
-        <v>149000</v>
+        <v>-707400</v>
       </c>
       <c r="F26" s="3">
-        <v>-22700</v>
+        <v>275400</v>
       </c>
       <c r="G26" s="3">
-        <v>310100</v>
+        <v>148600</v>
       </c>
       <c r="H26" s="3">
-        <v>206400</v>
+        <v>-22600</v>
       </c>
       <c r="I26" s="3">
+        <v>443100</v>
+      </c>
+      <c r="J26" s="3">
+        <v>120700</v>
+      </c>
+      <c r="K26" s="3">
         <v>57400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>720600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-76100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>276900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>273200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>337700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>754000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>554600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>368500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>126300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>378700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-12400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>387800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>499600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-122700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>445800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>297300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>562700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>124900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>709300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>13100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>527100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>1649500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>239200</v>
+        <v>1106800</v>
       </c>
       <c r="E27" s="3">
-        <v>91300</v>
+        <v>-732700</v>
       </c>
       <c r="F27" s="3">
-        <v>-58600</v>
+        <v>238600</v>
       </c>
       <c r="G27" s="3">
-        <v>268700</v>
+        <v>91000</v>
       </c>
       <c r="H27" s="3">
-        <v>133000</v>
+        <v>-58500</v>
       </c>
       <c r="I27" s="3">
+        <v>401800</v>
+      </c>
+      <c r="J27" s="3">
+        <v>47500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-16100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>656000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-142100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>203200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>197800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>266500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>668600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>461100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>266200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>9600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>277900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-113600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>302100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>397100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-160200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>370200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>208100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>484100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>46100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>623500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-79500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>441500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>1282600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-93500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,100 +2658,112 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E29" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F29" s="3">
         <v>-6700</v>
       </c>
-      <c r="E29" s="3">
-        <v>-13400</v>
-      </c>
-      <c r="F29" s="3">
-        <v>1780000</v>
-      </c>
       <c r="G29" s="3">
-        <v>3327100</v>
+        <v>-13300</v>
       </c>
       <c r="H29" s="3">
-        <v>13900</v>
+        <v>1774900</v>
       </c>
       <c r="I29" s="3">
+        <v>3183800</v>
+      </c>
+      <c r="J29" s="3">
+        <v>99000</v>
+      </c>
+      <c r="K29" s="3">
         <v>-89500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-32700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>147100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>39200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>7600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-631800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>127800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>225600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>67900</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>-86600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>31900</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>28000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>35400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>297100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>231400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>62500</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>26600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>211500</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>42800</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>60200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>72400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>-933600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AH29" s="3">
         <v>-501000</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2952,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-27300</v>
+        <v>-114500</v>
       </c>
       <c r="E32" s="3">
-        <v>87700</v>
+        <v>134800</v>
       </c>
       <c r="F32" s="3">
-        <v>324400</v>
+        <v>-27200</v>
       </c>
       <c r="G32" s="3">
-        <v>-55100</v>
+        <v>87400</v>
       </c>
       <c r="H32" s="3">
-        <v>230100</v>
+        <v>323500</v>
       </c>
       <c r="I32" s="3">
+        <v>-91000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>228500</v>
+      </c>
+      <c r="K32" s="3">
         <v>211300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-15700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>9600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>86700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>59500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-19500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-219500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-49700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-120200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>404300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-85200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>202000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-7100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-62800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>258100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>124000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-233900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>45200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-211800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-102900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-100400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>323500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-90900</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>232500</v>
+        <v>1093500</v>
       </c>
       <c r="E33" s="3">
-        <v>77900</v>
+        <v>-726700</v>
       </c>
       <c r="F33" s="3">
-        <v>1721300</v>
+        <v>231800</v>
       </c>
       <c r="G33" s="3">
-        <v>3595900</v>
+        <v>77700</v>
       </c>
       <c r="H33" s="3">
-        <v>146900</v>
+        <v>1716400</v>
       </c>
       <c r="I33" s="3">
+        <v>3585600</v>
+      </c>
+      <c r="J33" s="3">
+        <v>146500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-105600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>623200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>5000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>242400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>205500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-365300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>796400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>458600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>491800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>77400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>191400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-81700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>330100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>432600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>136900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>601600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>270600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>510700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>257600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>666400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-19300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>513900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>348900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>232500</v>
+        <v>1093500</v>
       </c>
       <c r="E35" s="3">
-        <v>77900</v>
+        <v>-726700</v>
       </c>
       <c r="F35" s="3">
-        <v>1721300</v>
+        <v>231800</v>
       </c>
       <c r="G35" s="3">
-        <v>3595900</v>
+        <v>77700</v>
       </c>
       <c r="H35" s="3">
-        <v>146900</v>
+        <v>1716400</v>
       </c>
       <c r="I35" s="3">
+        <v>3585600</v>
+      </c>
+      <c r="J35" s="3">
+        <v>146500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-105600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>623200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>5000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>242400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>205500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-365300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>796400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>458600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>491800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>77400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>191400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-81700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>330100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>432600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>136900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>601600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>270600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>510700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>257600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>666400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-19300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>513900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>348900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,836 +3523,892 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>921100</v>
+        <v>1973200</v>
       </c>
       <c r="E41" s="3">
-        <v>1187900</v>
+        <v>1849800</v>
       </c>
       <c r="F41" s="3">
-        <v>1361200</v>
+        <v>918500</v>
       </c>
       <c r="G41" s="3">
-        <v>941900</v>
+        <v>1184600</v>
       </c>
       <c r="H41" s="3">
-        <v>1539000</v>
+        <v>1357400</v>
       </c>
       <c r="I41" s="3">
+        <v>939200</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1534600</v>
+      </c>
+      <c r="K41" s="3">
         <v>892800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1972900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1431900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2018200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1852900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2139500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2131400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1771000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1855300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2006900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1534800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3841300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4899600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1569900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2086300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3345800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1900500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2144100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2610600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>3448500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2389300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>3222400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2846400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>3399800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>77800</v>
+        <v>186300</v>
       </c>
       <c r="E42" s="3">
+        <v>156200</v>
+      </c>
+      <c r="F42" s="3">
+        <v>77600</v>
+      </c>
+      <c r="G42" s="3">
+        <v>78700</v>
+      </c>
+      <c r="H42" s="3">
+        <v>55800</v>
+      </c>
+      <c r="I42" s="3">
+        <v>34100</v>
+      </c>
+      <c r="J42" s="3">
+        <v>69500</v>
+      </c>
+      <c r="K42" s="3">
+        <v>57500</v>
+      </c>
+      <c r="L42" s="3">
+        <v>62000</v>
+      </c>
+      <c r="M42" s="3">
         <v>78900</v>
       </c>
-      <c r="F42" s="3">
-        <v>56000</v>
-      </c>
-      <c r="G42" s="3">
-        <v>34200</v>
-      </c>
-      <c r="H42" s="3">
-        <v>69700</v>
-      </c>
-      <c r="I42" s="3">
-        <v>57500</v>
-      </c>
-      <c r="J42" s="3">
-        <v>62000</v>
-      </c>
-      <c r="K42" s="3">
-        <v>78900</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>93000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>71500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>54300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>59700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>54500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>65400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>93700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>100700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>80600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>97200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>103000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>76500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>93200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>83200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>69000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>187800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>189300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>192000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>297900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>306900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1409500</v>
+        <v>1413700</v>
       </c>
       <c r="E43" s="3">
-        <v>1477900</v>
+        <v>1468400</v>
       </c>
       <c r="F43" s="3">
-        <v>1556300</v>
+        <v>1405500</v>
       </c>
       <c r="G43" s="3">
-        <v>1787400</v>
+        <v>1473700</v>
       </c>
       <c r="H43" s="3">
-        <v>2152200</v>
+        <v>1551800</v>
       </c>
       <c r="I43" s="3">
+        <v>1782300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>2146100</v>
+      </c>
+      <c r="K43" s="3">
         <v>2167600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2025600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2044800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2132100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2213800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2213800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2730300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2652100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2945000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>3052900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3000200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3410000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2509600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>3068800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>2537200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2310300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2155700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2118400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2990300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>2713200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>2991200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>3085500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>3158100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>2854000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>100900</v>
+        <v>96900</v>
       </c>
       <c r="E44" s="3">
-        <v>118300</v>
+        <v>90300</v>
       </c>
       <c r="F44" s="3">
-        <v>121700</v>
+        <v>100600</v>
       </c>
       <c r="G44" s="3">
-        <v>147900</v>
+        <v>118000</v>
       </c>
       <c r="H44" s="3">
-        <v>174500</v>
+        <v>121400</v>
       </c>
       <c r="I44" s="3">
+        <v>147500</v>
+      </c>
+      <c r="J44" s="3">
+        <v>174000</v>
+      </c>
+      <c r="K44" s="3">
         <v>158600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>148200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>147000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>103400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>121500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>149300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>136000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>127100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>142500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>172600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>164400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>163400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>133400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>168100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>192100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>101800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>115000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>149800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>205300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>174100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>200000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>210800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>222200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>175900</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>85800</v>
+        <v>59200</v>
       </c>
       <c r="E45" s="3">
-        <v>70700</v>
+        <v>195800</v>
       </c>
       <c r="F45" s="3">
-        <v>51100</v>
+        <v>85600</v>
       </c>
       <c r="G45" s="3">
-        <v>141400</v>
+        <v>70500</v>
       </c>
       <c r="H45" s="3">
-        <v>141700</v>
+        <v>51000</v>
       </c>
       <c r="I45" s="3">
+        <v>141000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>141300</v>
+      </c>
+      <c r="K45" s="3">
         <v>154900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>140900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>421300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>417800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>385700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>143600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>128400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>141200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>187400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>599400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>386200</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
-      <c r="U45" s="3" t="s">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>395000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>101800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>439600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>2973600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>3045100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>197100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>178000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>117900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>438000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2595200</v>
+        <v>3729400</v>
       </c>
       <c r="E46" s="3">
-        <v>2933700</v>
+        <v>3760500</v>
       </c>
       <c r="F46" s="3">
-        <v>3146300</v>
+        <v>2587800</v>
       </c>
       <c r="G46" s="3">
-        <v>3052800</v>
+        <v>2925400</v>
       </c>
       <c r="H46" s="3">
-        <v>4077200</v>
+        <v>3137400</v>
       </c>
       <c r="I46" s="3">
+        <v>3044100</v>
+      </c>
+      <c r="J46" s="3">
+        <v>4065600</v>
+      </c>
+      <c r="K46" s="3">
         <v>3431500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4349600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4123900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4764600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4645400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4700400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>5185700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4746000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>5195700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>5925500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>5186200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>7495400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>7639800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>5304800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>4993900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>6290700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>7227900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>7526400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>6191100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>6703100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>5890400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>7254600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>6533800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>6691100</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5791200</v>
+        <v>5623800</v>
       </c>
       <c r="E47" s="3">
-        <v>5964200</v>
+        <v>4818600</v>
       </c>
       <c r="F47" s="3">
-        <v>5704900</v>
+        <v>5774700</v>
       </c>
       <c r="G47" s="3">
-        <v>3764600</v>
+        <v>5947300</v>
       </c>
       <c r="H47" s="3">
-        <v>578600</v>
+        <v>5688600</v>
       </c>
       <c r="I47" s="3">
+        <v>3753900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>576900</v>
+      </c>
+      <c r="K47" s="3">
         <v>558400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>532200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>534500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>533300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>565300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>587200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>664700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>826000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>847800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>543800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>475800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>272000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>253700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>486700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>268700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>52000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>53500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>53300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>55600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>51200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>51200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>1738500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>1944800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>1690700</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7552200</v>
+        <v>7598700</v>
       </c>
       <c r="E48" s="3">
-        <v>7715600</v>
+        <v>7327100</v>
       </c>
       <c r="F48" s="3">
-        <v>7623600</v>
+        <v>7530700</v>
       </c>
       <c r="G48" s="3">
-        <v>10562200</v>
+        <v>7693700</v>
       </c>
       <c r="H48" s="3">
-        <v>12022500</v>
+        <v>7601900</v>
       </c>
       <c r="I48" s="3">
+        <v>10532100</v>
+      </c>
+      <c r="J48" s="3">
+        <v>11988200</v>
+      </c>
+      <c r="K48" s="3">
         <v>11906500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>11630300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>11694700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>11352200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>11879500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>11961800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>14727000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>14716600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>16542600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>17296600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>15778500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>16995100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>14544500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>16139200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>8276600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>7060600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>7104000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>6984200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>8748700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>8271800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>8497000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>9027500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>8879600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>8405100</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3265300</v>
+        <v>3373600</v>
       </c>
       <c r="E49" s="3">
-        <v>3390600</v>
+        <v>3264400</v>
       </c>
       <c r="F49" s="3">
-        <v>3325900</v>
+        <v>3256000</v>
       </c>
       <c r="G49" s="3">
-        <v>3512000</v>
+        <v>3380900</v>
       </c>
       <c r="H49" s="3">
-        <v>3684700</v>
+        <v>3316400</v>
       </c>
       <c r="I49" s="3">
+        <v>3502000</v>
+      </c>
+      <c r="J49" s="3">
+        <v>3674300</v>
+      </c>
+      <c r="K49" s="3">
         <v>3603500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3422500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3540700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3501700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3610100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3575500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4160700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>4237300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>4643000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>4839800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>4296700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>5123000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2361900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>4394900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>5728300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>3698000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>3864400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>4002500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>6605500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>6627500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>6847600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>6962500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>7099100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>7250400</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4597,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1993500</v>
+        <v>1778900</v>
       </c>
       <c r="E52" s="3">
-        <v>2123300</v>
+        <v>1485500</v>
       </c>
       <c r="F52" s="3">
-        <v>2401500</v>
+        <v>1987800</v>
       </c>
       <c r="G52" s="3">
-        <v>1803600</v>
+        <v>2117200</v>
       </c>
       <c r="H52" s="3">
-        <v>1794500</v>
+        <v>2394600</v>
       </c>
       <c r="I52" s="3">
+        <v>1798400</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1789400</v>
+      </c>
+      <c r="K52" s="3">
         <v>1772500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1564500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1339300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1285100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1453900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1509100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1833200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1877000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2144700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2457300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1810800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2484200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2288400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1852300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2311800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1982900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1485500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1533000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1761500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>1790700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2147400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>850000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>981800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>874400</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>21197300</v>
+        <v>22104500</v>
       </c>
       <c r="E54" s="3">
-        <v>22127400</v>
+        <v>20656200</v>
       </c>
       <c r="F54" s="3">
-        <v>22202200</v>
+        <v>21137000</v>
       </c>
       <c r="G54" s="3">
-        <v>22695200</v>
+        <v>22064400</v>
       </c>
       <c r="H54" s="3">
-        <v>22157400</v>
+        <v>22139000</v>
       </c>
       <c r="I54" s="3">
+        <v>22630600</v>
+      </c>
+      <c r="J54" s="3">
+        <v>22094300</v>
+      </c>
+      <c r="K54" s="3">
         <v>21272400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>21499100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>21233100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>21436900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>22154100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>22334000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>26571300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>26402800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>29373700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>31063100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>27548100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>32369600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>27088300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>28177900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>21579300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>19084400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>19735400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>20099400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>23362400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>23444200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>23433600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>25833200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>25439100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>24911800</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4967,598 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1968700</v>
+        <v>2081300</v>
       </c>
       <c r="E57" s="3">
-        <v>2053500</v>
+        <v>1996600</v>
       </c>
       <c r="F57" s="3">
-        <v>2088000</v>
+        <v>1963100</v>
       </c>
       <c r="G57" s="3">
-        <v>2677600</v>
+        <v>2047700</v>
       </c>
       <c r="H57" s="3">
-        <v>2988700</v>
+        <v>2082000</v>
       </c>
       <c r="I57" s="3">
+        <v>2670000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2980200</v>
+      </c>
+      <c r="K57" s="3">
         <v>2954800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2927300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3040000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2817800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2822500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2982600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3510400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3344800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3834100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>4089800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3950300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>4383300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>3795600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>4040600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>4256500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3576100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3484800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>3486000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>4665800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>4258800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>4539200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>4887000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>5288300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>4924500</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>950400</v>
+        <v>1414100</v>
       </c>
       <c r="E58" s="3">
-        <v>1640600</v>
+        <v>1503600</v>
       </c>
       <c r="F58" s="3">
-        <v>1411700</v>
+        <v>947700</v>
       </c>
       <c r="G58" s="3">
-        <v>1502900</v>
+        <v>1635900</v>
       </c>
       <c r="H58" s="3">
-        <v>1684000</v>
+        <v>1407700</v>
       </c>
       <c r="I58" s="3">
+        <v>1498600</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1679300</v>
+      </c>
+      <c r="K58" s="3">
         <v>1238600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1486400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1528800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1664800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2078100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1462000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1718800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1883200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2466100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2069500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2662500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>4165700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3453100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>2723400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1775800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1588700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>2615700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>2051000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2629600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>2984700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3083000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>4001300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3202100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>3174000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1333500</v>
+        <v>763300</v>
       </c>
       <c r="E59" s="3">
-        <v>1296500</v>
+        <v>850000</v>
       </c>
       <c r="F59" s="3">
-        <v>824000</v>
+        <v>1329700</v>
       </c>
       <c r="G59" s="3">
-        <v>920800</v>
+        <v>1292800</v>
       </c>
       <c r="H59" s="3">
-        <v>1688200</v>
+        <v>821600</v>
       </c>
       <c r="I59" s="3">
+        <v>918200</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1683400</v>
+      </c>
+      <c r="K59" s="3">
         <v>1622000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1133200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1278700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1728800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1762500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1005200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1041100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1639300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1928100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1480500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1470400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2325000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2159400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1504100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1578100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2654800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2280400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1900000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1583800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2214000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2207700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1558500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1079900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>1033600</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4252700</v>
+        <v>4258700</v>
       </c>
       <c r="E60" s="3">
-        <v>4990600</v>
+        <v>4350200</v>
       </c>
       <c r="F60" s="3">
-        <v>4323600</v>
+        <v>4240600</v>
       </c>
       <c r="G60" s="3">
-        <v>5101300</v>
+        <v>4976400</v>
       </c>
       <c r="H60" s="3">
-        <v>6360900</v>
+        <v>4311300</v>
       </c>
       <c r="I60" s="3">
+        <v>5086800</v>
+      </c>
+      <c r="J60" s="3">
+        <v>6342800</v>
+      </c>
+      <c r="K60" s="3">
         <v>5815400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5546800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5847400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>6211400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6663100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>5449900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6270300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6867300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>8228300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>7639800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>8083200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>10873900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>9408000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>8268000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>7610400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>7819600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>8380900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>7437000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>8879100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>9457500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>9829900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>10446800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>9570300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>9132100</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8149200</v>
+        <v>8537000</v>
       </c>
       <c r="E61" s="3">
-        <v>8426700</v>
+        <v>8407800</v>
       </c>
       <c r="F61" s="3">
-        <v>7928200</v>
+        <v>8126000</v>
       </c>
       <c r="G61" s="3">
-        <v>10163400</v>
+        <v>8402700</v>
       </c>
       <c r="H61" s="3">
-        <v>11288000</v>
+        <v>7905600</v>
       </c>
       <c r="I61" s="3">
+        <v>10134500</v>
+      </c>
+      <c r="J61" s="3">
+        <v>11255800</v>
+      </c>
+      <c r="K61" s="3">
         <v>11328000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>10733700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>10902700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>10874900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>11236200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>11596800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>13901600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>13888300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>15270500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>15872400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>12837700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>14534900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>11137800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>13131100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>6309600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>4548900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>4739300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>4852400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>5973300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>5762600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>5949300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>6540000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>7446200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>7214000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1200200</v>
+        <v>1242300</v>
       </c>
       <c r="E62" s="3">
-        <v>1220800</v>
+        <v>1235800</v>
       </c>
       <c r="F62" s="3">
-        <v>1284000</v>
+        <v>1196800</v>
       </c>
       <c r="G62" s="3">
-        <v>1323900</v>
+        <v>1217300</v>
       </c>
       <c r="H62" s="3">
-        <v>1691400</v>
+        <v>1280400</v>
       </c>
       <c r="I62" s="3">
+        <v>1320100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1686600</v>
+      </c>
+      <c r="K62" s="3">
         <v>1562100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1481200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1520100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1510500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1560100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1579800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1850400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1790500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2093100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2227800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1830500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1962200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1408000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1872300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1515700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1260900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1244500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1065200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1292200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1284700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1223900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1479700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1592300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1503800</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>14153900</v>
+        <v>14667300</v>
       </c>
       <c r="E66" s="3">
-        <v>15171700</v>
+        <v>14556700</v>
       </c>
       <c r="F66" s="3">
-        <v>14064300</v>
+        <v>14113600</v>
       </c>
       <c r="G66" s="3">
-        <v>16990500</v>
+        <v>15128500</v>
       </c>
       <c r="H66" s="3">
-        <v>19811600</v>
+        <v>14024300</v>
       </c>
       <c r="I66" s="3">
+        <v>16942100</v>
+      </c>
+      <c r="J66" s="3">
+        <v>19755200</v>
+      </c>
+      <c r="K66" s="3">
         <v>19206700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>18282800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>18759900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>19035000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>19933600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>19135300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>22601700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>23108300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>26282800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>26436000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>23336400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>27950500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>22521100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>23869900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>16000800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>14120200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>14910200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>13911100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>16704900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>17006400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>17551000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>19074800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>19165800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>18363900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>6725200</v>
+        <v>7031200</v>
       </c>
       <c r="E72" s="3">
-        <v>6475800</v>
+        <v>5882300</v>
       </c>
       <c r="F72" s="3">
-        <v>7587500</v>
+        <v>6706100</v>
       </c>
       <c r="G72" s="3">
-        <v>5225900</v>
+        <v>6457400</v>
       </c>
       <c r="H72" s="3">
-        <v>1735200</v>
+        <v>7565900</v>
       </c>
       <c r="I72" s="3">
+        <v>5211100</v>
+      </c>
+      <c r="J72" s="3">
+        <v>1730200</v>
+      </c>
+      <c r="K72" s="3">
         <v>1549800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2847700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2111700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2030300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1803800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2791900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3421800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2516200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2252700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3551600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3562800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>3647400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>3964700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>5195400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>4828000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>4471800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>4521900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>5777800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>6005900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>5929300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>5278900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>5612000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>5136300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>5466800</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7043400</v>
+        <v>7437100</v>
       </c>
       <c r="E76" s="3">
-        <v>6955700</v>
+        <v>6099400</v>
       </c>
       <c r="F76" s="3">
-        <v>8137800</v>
+        <v>7023400</v>
       </c>
       <c r="G76" s="3">
-        <v>5704700</v>
+        <v>6935900</v>
       </c>
       <c r="H76" s="3">
-        <v>2345800</v>
+        <v>8114700</v>
       </c>
       <c r="I76" s="3">
+        <v>5688500</v>
+      </c>
+      <c r="J76" s="3">
+        <v>2339100</v>
+      </c>
+      <c r="K76" s="3">
         <v>2065800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3216200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2473200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2401900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2220500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3198700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3969600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3294600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>3090900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4627100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>4211700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4419100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>4567200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4308000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>5578500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>4964200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4825200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>6188300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>6657500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>6437800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5882600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>6758400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>6273400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>6547800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>232500</v>
+        <v>1093500</v>
       </c>
       <c r="E81" s="3">
-        <v>77900</v>
+        <v>-726700</v>
       </c>
       <c r="F81" s="3">
-        <v>1721300</v>
+        <v>231800</v>
       </c>
       <c r="G81" s="3">
-        <v>3595900</v>
+        <v>77700</v>
       </c>
       <c r="H81" s="3">
-        <v>146900</v>
+        <v>1716400</v>
       </c>
       <c r="I81" s="3">
+        <v>3585600</v>
+      </c>
+      <c r="J81" s="3">
+        <v>146500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-105600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>623200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>5000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>242400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>205500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-365300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>796400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>458600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>491800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>77400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>191400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-81700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>330100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>432600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>136900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>601600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>270600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>510700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>257600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>666400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-19300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>513900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>348900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7200,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>389700</v>
+        <v>393200</v>
       </c>
       <c r="E83" s="3">
-        <v>400200</v>
+        <v>399000</v>
       </c>
       <c r="F83" s="3">
-        <v>472700</v>
+        <v>388600</v>
       </c>
       <c r="G83" s="3">
-        <v>603500</v>
+        <v>399100</v>
       </c>
       <c r="H83" s="3">
+        <v>471300</v>
+      </c>
+      <c r="I83" s="3">
+        <v>601800</v>
+      </c>
+      <c r="J83" s="3">
+        <v>609000</v>
+      </c>
+      <c r="K83" s="3">
+        <v>859100</v>
+      </c>
+      <c r="L83" s="3">
+        <v>603300</v>
+      </c>
+      <c r="M83" s="3">
+        <v>700000</v>
+      </c>
+      <c r="N83" s="3">
+        <v>611300</v>
+      </c>
+      <c r="O83" s="3">
+        <v>635000</v>
+      </c>
+      <c r="P83" s="3">
+        <v>1267200</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>744900</v>
+      </c>
+      <c r="R83" s="3">
+        <v>722500</v>
+      </c>
+      <c r="S83" s="3">
+        <v>842100</v>
+      </c>
+      <c r="T83" s="3">
+        <v>795400</v>
+      </c>
+      <c r="U83" s="3">
+        <v>764600</v>
+      </c>
+      <c r="V83" s="3">
+        <v>756300</v>
+      </c>
+      <c r="W83" s="3">
+        <v>666600</v>
+      </c>
+      <c r="X83" s="3">
+        <v>641700</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>437000</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>571000</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>567700</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>597600</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>701200</v>
+      </c>
+      <c r="AD83" s="3">
         <v>610700</v>
       </c>
-      <c r="I83" s="3">
-        <v>859100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>603300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>700000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>611300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>635000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>1267200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>744900</v>
-      </c>
-      <c r="P83" s="3">
-        <v>722500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>842100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>795400</v>
-      </c>
-      <c r="S83" s="3">
-        <v>764600</v>
-      </c>
-      <c r="T83" s="3">
-        <v>756300</v>
-      </c>
-      <c r="U83" s="3">
-        <v>666600</v>
-      </c>
-      <c r="V83" s="3">
-        <v>641700</v>
-      </c>
-      <c r="W83" s="3">
-        <v>437000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>571000</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>567700</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>597600</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>701200</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>610700</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>662200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>630900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>3456500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>1136300</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>797400</v>
+        <v>814800</v>
       </c>
       <c r="E89" s="3">
-        <v>540000</v>
+        <v>843700</v>
       </c>
       <c r="F89" s="3">
-        <v>578800</v>
+        <v>795100</v>
       </c>
       <c r="G89" s="3">
-        <v>888500</v>
+        <v>538500</v>
       </c>
       <c r="H89" s="3">
-        <v>1029600</v>
+        <v>577200</v>
       </c>
       <c r="I89" s="3">
+        <v>885900</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1026700</v>
+      </c>
+      <c r="K89" s="3">
         <v>909600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>893000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>801700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1199300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>924400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1017300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1171000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1106800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1246300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1152100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>774300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1405400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>703500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1071600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>926100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1107200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>895600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>880500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1064600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1399400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1343300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1129900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>4904600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1293700</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7922,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3907000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-3170000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3191000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-3604000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-4763000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-9177000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-4428000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-5665000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-4491000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-4936000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-4134000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-439000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-535400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-504100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1395900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>571200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-610400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-8600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>1000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>32500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-101800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-827500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-1315200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>484600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-568500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-523100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-449500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-530800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-1393000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-2925500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-500200</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +8212,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-301100</v>
+        <v>-173600</v>
       </c>
       <c r="E94" s="3">
-        <v>-370600</v>
+        <v>-1256200</v>
       </c>
       <c r="F94" s="3">
-        <v>195800</v>
+        <v>-300200</v>
       </c>
       <c r="G94" s="3">
-        <v>-1091900</v>
+        <v>-369600</v>
       </c>
       <c r="H94" s="3">
-        <v>-289900</v>
+        <v>195200</v>
       </c>
       <c r="I94" s="3">
+        <v>-1088800</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-289100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-521000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-292700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-469500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-266300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-433500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-443000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>252400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-349300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-562400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-499100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1439700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-2515000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-535700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-564800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-906400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>1771500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-448800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-563600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-511600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>50900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-662400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-2602200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7894,91 +8361,97 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-656700</v>
+        <v>-576400</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-570900</v>
+        <v>-654800</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>-569200</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-663700</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-526500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-23400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-633100</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-623200</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-695500</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-631400</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-741900</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-1368800</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-639200</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-606500</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-747500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-30800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-1386600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8738,304 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-774300</v>
+        <v>-552000</v>
       </c>
       <c r="E100" s="3">
-        <v>-384400</v>
+        <v>1393200</v>
       </c>
       <c r="F100" s="3">
-        <v>-384000</v>
+        <v>-772100</v>
       </c>
       <c r="G100" s="3">
-        <v>-371900</v>
+        <v>-383300</v>
       </c>
       <c r="H100" s="3">
-        <v>-174800</v>
+        <v>-382900</v>
       </c>
       <c r="I100" s="3">
+        <v>-370800</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-174300</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1472900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-255600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-933400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-636000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-726000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-311400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1074200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-653300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-893600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-302200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1248800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-253200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>1835400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>209000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1683300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1548700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-652600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-311900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1372300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-107900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1948200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-1114300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>503100</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>14200</v>
       </c>
-      <c r="F101" s="3">
-        <v>41700</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-24100</v>
-      </c>
       <c r="H101" s="3">
-        <v>73400</v>
+        <v>41600</v>
       </c>
       <c r="I101" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>73200</v>
+      </c>
+      <c r="K101" s="3">
         <v>21000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-13400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>19600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-37400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>20100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-24300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-26100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-38800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>154000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>10400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>93000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-22000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-4100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>10700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-29500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>72600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-60200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>15500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>26300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-55000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-70700</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-277400</v>
+        <v>101700</v>
       </c>
       <c r="E102" s="3">
-        <v>-200700</v>
+        <v>982200</v>
       </c>
       <c r="F102" s="3">
-        <v>432400</v>
+        <v>-276600</v>
       </c>
       <c r="G102" s="3">
-        <v>-599400</v>
+        <v>-200200</v>
       </c>
       <c r="H102" s="3">
-        <v>638300</v>
+        <v>431100</v>
       </c>
       <c r="I102" s="3">
+        <v>-597700</v>
+      </c>
+      <c r="J102" s="3">
+        <v>636500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1063300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>331300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-581600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>259600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-215000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>238600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>323100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>67300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-248400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>504800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1900700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1268800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1989000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>700100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1652800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1326600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-211700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-864300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1083000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-642900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>373700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>1133100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>1819800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>TELNY</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1840400</v>
+        <v>1874800</v>
       </c>
       <c r="E8" s="3">
-        <v>1980100</v>
+        <v>1829700</v>
       </c>
       <c r="F8" s="3">
-        <v>1902000</v>
+        <v>1968600</v>
       </c>
       <c r="G8" s="3">
-        <v>1913000</v>
+        <v>1891000</v>
       </c>
       <c r="H8" s="3">
-        <v>1814900</v>
+        <v>1901900</v>
       </c>
       <c r="I8" s="3">
-        <v>1860300</v>
+        <v>1804300</v>
       </c>
       <c r="J8" s="3">
+        <v>1849500</v>
+      </c>
+      <c r="K8" s="3">
         <v>1847400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2659500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2562100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1417100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2515000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2550100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2583900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2483500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3039500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3219500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3236500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3165100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3421100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3112400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3010000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2674300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2820000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2813600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2777400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2247000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3179900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3280600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3402600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>15461200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3853000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>401800</v>
+        <v>401100</v>
       </c>
       <c r="E9" s="3">
-        <v>490400</v>
+        <v>399500</v>
       </c>
       <c r="F9" s="3">
-        <v>428000</v>
+        <v>487500</v>
       </c>
       <c r="G9" s="3">
-        <v>442600</v>
+        <v>425500</v>
       </c>
       <c r="H9" s="3">
-        <v>441500</v>
+        <v>440000</v>
       </c>
       <c r="I9" s="3">
-        <v>460900</v>
+        <v>439000</v>
       </c>
       <c r="J9" s="3">
+        <v>458300</v>
+      </c>
+      <c r="K9" s="3">
         <v>406600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>696700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>680400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>426600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>628700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>647300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>686400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>780400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>702800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>780300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>795900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>785200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>816200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>725100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>700800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>588400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>619800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>662700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>632900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>523300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>725500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>760900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1192600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5577700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1329500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1438600</v>
+        <v>1473700</v>
       </c>
       <c r="E10" s="3">
-        <v>1489800</v>
+        <v>1430300</v>
       </c>
       <c r="F10" s="3">
-        <v>1474000</v>
+        <v>1481100</v>
       </c>
       <c r="G10" s="3">
-        <v>1470400</v>
+        <v>1465400</v>
       </c>
       <c r="H10" s="3">
-        <v>1373400</v>
+        <v>1461900</v>
       </c>
       <c r="I10" s="3">
-        <v>1399400</v>
+        <v>1365400</v>
       </c>
       <c r="J10" s="3">
+        <v>1391200</v>
+      </c>
+      <c r="K10" s="3">
         <v>1440800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1962700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1881600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>990500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1886300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1902900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1897500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1703200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2336700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2439200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2440500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2380000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2605000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2387300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2309300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2085900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2200200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2150900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2144500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1723800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2454400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2519700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2210000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>9883500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2523500</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,204 +1338,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-654600</v>
+        <v>16800</v>
       </c>
       <c r="E14" s="3">
-        <v>740300</v>
+        <v>-650800</v>
       </c>
       <c r="F14" s="3">
-        <v>9400</v>
+        <v>736000</v>
       </c>
       <c r="G14" s="3">
-        <v>53500</v>
+        <v>9300</v>
       </c>
       <c r="H14" s="3">
-        <v>17400</v>
+        <v>53200</v>
       </c>
       <c r="I14" s="3">
-        <v>32300</v>
+        <v>17300</v>
       </c>
       <c r="J14" s="3">
+        <v>32100</v>
+      </c>
+      <c r="K14" s="3">
         <v>10500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>259800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>16900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>93600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>16900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>10300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>15300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>10900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>147800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>37000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>37100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>5200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>26900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>20700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>268700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>25500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>26600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>18600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>59900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>55600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>718100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-82400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>158900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>707900</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>393100</v>
+        <v>395300</v>
       </c>
       <c r="E15" s="3">
-        <v>396700</v>
+        <v>390800</v>
       </c>
       <c r="F15" s="3">
-        <v>389300</v>
+        <v>394400</v>
       </c>
       <c r="G15" s="3">
-        <v>397800</v>
+        <v>387100</v>
       </c>
       <c r="H15" s="3">
-        <v>380200</v>
+        <v>395400</v>
       </c>
       <c r="I15" s="3">
-        <v>412700</v>
+        <v>377900</v>
       </c>
       <c r="J15" s="3">
+        <v>410300</v>
+      </c>
+      <c r="K15" s="3">
         <v>394500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>622000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>603300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>360100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>607100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>603000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>599100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>459400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>722500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>761100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>722000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>756200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>757100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>666800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>637800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>462800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>553400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>529200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>547800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>457600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>556300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>570100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>581900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>2414600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>617700</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>644800</v>
+        <v>1463600</v>
       </c>
       <c r="E17" s="3">
-        <v>2323900</v>
+        <v>641100</v>
       </c>
       <c r="F17" s="3">
-        <v>1425800</v>
+        <v>2310400</v>
       </c>
       <c r="G17" s="3">
-        <v>1544700</v>
+        <v>1417600</v>
       </c>
       <c r="H17" s="3">
-        <v>1452200</v>
+        <v>1535700</v>
       </c>
       <c r="I17" s="3">
-        <v>1552100</v>
+        <v>1443800</v>
       </c>
       <c r="J17" s="3">
+        <v>1543100</v>
+      </c>
+      <c r="K17" s="3">
         <v>1376400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2368500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1912500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1395100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1956000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2017600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2050200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1679400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2209800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2664400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2547000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2550200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2612300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2398400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2269400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2378100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2132300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2221000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2183200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1893900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2354800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3111300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2705400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12375000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3663500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1195600</v>
+        <v>411100</v>
       </c>
       <c r="E18" s="3">
-        <v>-343700</v>
+        <v>1188700</v>
       </c>
       <c r="F18" s="3">
-        <v>476200</v>
+        <v>-341700</v>
       </c>
       <c r="G18" s="3">
-        <v>368300</v>
+        <v>473400</v>
       </c>
       <c r="H18" s="3">
-        <v>362700</v>
+        <v>366200</v>
       </c>
       <c r="I18" s="3">
-        <v>308200</v>
+        <v>360500</v>
       </c>
       <c r="J18" s="3">
+        <v>306400</v>
+      </c>
+      <c r="K18" s="3">
         <v>471100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>291000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>649600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>22000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>558900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>532500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>533700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>804100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>829700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>555100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>689500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>614900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>808800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>714000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>740600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>296200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>687700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>592500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>594300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>353200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>825100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>169300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>697100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3086200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>189500</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>114500</v>
+        <v>72800</v>
       </c>
       <c r="E20" s="3">
-        <v>-134800</v>
+        <v>113900</v>
       </c>
       <c r="F20" s="3">
-        <v>27200</v>
+        <v>-134000</v>
       </c>
       <c r="G20" s="3">
-        <v>-87400</v>
+        <v>27100</v>
       </c>
       <c r="H20" s="3">
+        <v>-86900</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-321600</v>
+      </c>
+      <c r="J20" s="3">
+        <v>90500</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-228500</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-211300</v>
+      </c>
+      <c r="M20" s="3">
+        <v>15700</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-86700</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>19500</v>
+      </c>
+      <c r="R20" s="3">
+        <v>219500</v>
+      </c>
+      <c r="S20" s="3">
+        <v>49700</v>
+      </c>
+      <c r="T20" s="3">
+        <v>120200</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-404300</v>
+      </c>
+      <c r="V20" s="3">
+        <v>85200</v>
+      </c>
+      <c r="W20" s="3">
+        <v>-202000</v>
+      </c>
+      <c r="X20" s="3">
+        <v>7100</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>62800</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>-258100</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>-124000</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>233900</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>-45200</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>211800</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>102900</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>100400</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-323500</v>
       </c>
-      <c r="I20" s="3">
-        <v>91000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-228500</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-211300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>15700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-86700</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-59500</v>
-      </c>
-      <c r="P20" s="3">
-        <v>19500</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>219500</v>
-      </c>
-      <c r="R20" s="3">
-        <v>49700</v>
-      </c>
-      <c r="S20" s="3">
-        <v>120200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-404300</v>
-      </c>
-      <c r="U20" s="3">
-        <v>85200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-202000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>7100</v>
-      </c>
-      <c r="X20" s="3">
-        <v>62800</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-258100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>9800</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-124000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>233900</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-45200</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>211800</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>102900</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>100400</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-323500</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>90900</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1703400</v>
+        <v>879400</v>
       </c>
       <c r="E21" s="3">
-        <v>-79600</v>
+        <v>1693500</v>
       </c>
       <c r="F21" s="3">
-        <v>892000</v>
+        <v>-79100</v>
       </c>
       <c r="G21" s="3">
-        <v>680000</v>
+        <v>886800</v>
       </c>
       <c r="H21" s="3">
-        <v>510500</v>
+        <v>676100</v>
       </c>
       <c r="I21" s="3">
-        <v>1001000</v>
+        <v>507500</v>
       </c>
       <c r="J21" s="3">
+        <v>995100</v>
+      </c>
+      <c r="K21" s="3">
         <v>851500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>938900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1268700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>712400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1083600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1108000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1820400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1768500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1602000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1517400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1080600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1464700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1363200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1387700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1445100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>516500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1017600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1422600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1009200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1647600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>934400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1428400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>6219100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1416700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>93900</v>
+        <v>92900</v>
       </c>
       <c r="E22" s="3">
-        <v>61400</v>
+        <v>93400</v>
       </c>
       <c r="F22" s="3">
-        <v>71400</v>
+        <v>61000</v>
       </c>
       <c r="G22" s="3">
-        <v>64500</v>
+        <v>71000</v>
       </c>
       <c r="H22" s="3">
-        <v>43900</v>
+        <v>64100</v>
       </c>
       <c r="I22" s="3">
-        <v>124000</v>
+        <v>43600</v>
       </c>
       <c r="J22" s="3">
+        <v>123300</v>
+      </c>
+      <c r="K22" s="3">
         <v>43700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>58700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>45200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>48700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>61000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>61600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>60700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>110900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>107400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>85400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>89800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>173900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>135400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>117100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>100900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>104900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>45900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>46200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>30500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>105800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>54700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>72700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>72500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>382700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1216200</v>
+        <v>391000</v>
       </c>
       <c r="E23" s="3">
-        <v>-539900</v>
+        <v>1209200</v>
       </c>
       <c r="F23" s="3">
-        <v>432000</v>
+        <v>-536800</v>
       </c>
       <c r="G23" s="3">
-        <v>216400</v>
+        <v>429500</v>
       </c>
       <c r="H23" s="3">
+        <v>215200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-4700</v>
       </c>
-      <c r="I23" s="3">
-        <v>275200</v>
-      </c>
       <c r="J23" s="3">
+        <v>273600</v>
+      </c>
+      <c r="K23" s="3">
         <v>198800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>620100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-36300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>411200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>411400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>492600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>912600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>772100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>589800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>195400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>526300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>471500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>603900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>702600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-66900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>651500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>422300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>797600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>202200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>982200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>199500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>725000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2379900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>210800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>48900</v>
+        <v>102000</v>
       </c>
       <c r="E24" s="3">
-        <v>167500</v>
+        <v>48600</v>
       </c>
       <c r="F24" s="3">
-        <v>156500</v>
+        <v>166500</v>
       </c>
       <c r="G24" s="3">
-        <v>67800</v>
+        <v>155600</v>
       </c>
       <c r="H24" s="3">
-        <v>17900</v>
+        <v>67400</v>
       </c>
       <c r="I24" s="3">
-        <v>-167900</v>
+        <v>17800</v>
       </c>
       <c r="J24" s="3">
+        <v>-166900</v>
+      </c>
+      <c r="K24" s="3">
         <v>78100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-36300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>39800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>134300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>138100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>154900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>158700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>217500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>221300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>69100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>147500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>483800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>216100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>203000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>55800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>205700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>125000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>235000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>77200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>272900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>186400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>197900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>730400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1167300</v>
+        <v>289000</v>
       </c>
       <c r="E26" s="3">
-        <v>-707400</v>
+        <v>1160500</v>
       </c>
       <c r="F26" s="3">
-        <v>275400</v>
+        <v>-703300</v>
       </c>
       <c r="G26" s="3">
-        <v>148600</v>
+        <v>273800</v>
       </c>
       <c r="H26" s="3">
-        <v>-22600</v>
+        <v>147700</v>
       </c>
       <c r="I26" s="3">
-        <v>443100</v>
+        <v>-22500</v>
       </c>
       <c r="J26" s="3">
+        <v>440500</v>
+      </c>
+      <c r="K26" s="3">
         <v>120700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>57400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>720600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-76100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>276900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>273200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>337700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>754000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>554600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>368500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>126300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>378700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-12400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>387800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>499600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-122700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>445800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>297300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>562700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>124900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>709300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>13100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>527100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1649500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1106800</v>
+        <v>247700</v>
       </c>
       <c r="E27" s="3">
-        <v>-732700</v>
+        <v>1100400</v>
       </c>
       <c r="F27" s="3">
-        <v>238600</v>
+        <v>-728400</v>
       </c>
       <c r="G27" s="3">
-        <v>91000</v>
+        <v>237200</v>
       </c>
       <c r="H27" s="3">
-        <v>-58500</v>
+        <v>90500</v>
       </c>
       <c r="I27" s="3">
-        <v>401800</v>
+        <v>-58100</v>
       </c>
       <c r="J27" s="3">
+        <v>399500</v>
+      </c>
+      <c r="K27" s="3">
         <v>47500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>656000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-142100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>203200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>197800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>266500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>668600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>461100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>266200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>277900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-113600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>302100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>397100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-160200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>370200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>208100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>484100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>46100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>623500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-79500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>441500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1282600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-93500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,106 +2722,112 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E29" s="3">
         <v>-13300</v>
       </c>
-      <c r="E29" s="3">
-        <v>6000</v>
-      </c>
       <c r="F29" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G29" s="3">
         <v>-6700</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-13300</v>
       </c>
-      <c r="H29" s="3">
-        <v>1774900</v>
-      </c>
       <c r="I29" s="3">
-        <v>3183800</v>
+        <v>1764600</v>
       </c>
       <c r="J29" s="3">
+        <v>3165300</v>
+      </c>
+      <c r="K29" s="3">
         <v>99000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-89500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-32700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>147100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>39200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>7600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-631800</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>127800</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-2500</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>225600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>67900</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-86600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>31900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>28000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>35400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>297100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>231400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>62500</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>26600</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>211500</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>42800</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>60200</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>72400</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-933600</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-501000</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-114500</v>
+        <v>-72800</v>
       </c>
       <c r="E32" s="3">
-        <v>134800</v>
+        <v>-113900</v>
       </c>
       <c r="F32" s="3">
-        <v>-27200</v>
+        <v>134000</v>
       </c>
       <c r="G32" s="3">
-        <v>87400</v>
+        <v>-27100</v>
       </c>
       <c r="H32" s="3">
+        <v>86900</v>
+      </c>
+      <c r="I32" s="3">
+        <v>321600</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-90500</v>
+      </c>
+      <c r="K32" s="3">
+        <v>228500</v>
+      </c>
+      <c r="L32" s="3">
+        <v>211300</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="N32" s="3">
+        <v>9600</v>
+      </c>
+      <c r="O32" s="3">
+        <v>86700</v>
+      </c>
+      <c r="P32" s="3">
+        <v>59500</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-219500</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-120200</v>
+      </c>
+      <c r="U32" s="3">
+        <v>404300</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-85200</v>
+      </c>
+      <c r="W32" s="3">
+        <v>202000</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-62800</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>258100</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>124000</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-233900</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>45200</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>-211800</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>-102900</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>-100400</v>
+      </c>
+      <c r="AH32" s="3">
         <v>323500</v>
       </c>
-      <c r="I32" s="3">
-        <v>-91000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>228500</v>
-      </c>
-      <c r="K32" s="3">
-        <v>211300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-15700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>9600</v>
-      </c>
-      <c r="N32" s="3">
-        <v>86700</v>
-      </c>
-      <c r="O32" s="3">
-        <v>59500</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-19500</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-219500</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-49700</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-120200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>404300</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-85200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>202000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-62800</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>258100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>124000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-233900</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>45200</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-211800</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-102900</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-100400</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>323500</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-90900</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1093500</v>
+        <v>238900</v>
       </c>
       <c r="E33" s="3">
-        <v>-726700</v>
+        <v>1087100</v>
       </c>
       <c r="F33" s="3">
-        <v>231800</v>
+        <v>-722500</v>
       </c>
       <c r="G33" s="3">
-        <v>77700</v>
+        <v>230500</v>
       </c>
       <c r="H33" s="3">
-        <v>1716400</v>
+        <v>77200</v>
       </c>
       <c r="I33" s="3">
-        <v>3585600</v>
+        <v>1706400</v>
       </c>
       <c r="J33" s="3">
+        <v>3564800</v>
+      </c>
+      <c r="K33" s="3">
         <v>146500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-105600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>623200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>242400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>205500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-365300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>796400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>458600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>491800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>77400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>191400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-81700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>330100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>432600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>136900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>601600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>270600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>510700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>257600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>666400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-19300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>513900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>348900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1093500</v>
+        <v>238900</v>
       </c>
       <c r="E35" s="3">
-        <v>-726700</v>
+        <v>1087100</v>
       </c>
       <c r="F35" s="3">
-        <v>231800</v>
+        <v>-722500</v>
       </c>
       <c r="G35" s="3">
-        <v>77700</v>
+        <v>230500</v>
       </c>
       <c r="H35" s="3">
-        <v>1716400</v>
+        <v>77200</v>
       </c>
       <c r="I35" s="3">
-        <v>3585600</v>
+        <v>1706400</v>
       </c>
       <c r="J35" s="3">
+        <v>3564800</v>
+      </c>
+      <c r="K35" s="3">
         <v>146500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-105600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>623200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>242400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>205500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-365300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>796400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>458600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>491800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>77400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>191400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-81700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>330100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>432600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>136900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>601600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>270600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>510700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>257600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>666400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-19300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>513900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>348900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,890 +3611,918 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1973200</v>
+        <v>1308800</v>
       </c>
       <c r="E41" s="3">
-        <v>1849800</v>
+        <v>1961800</v>
       </c>
       <c r="F41" s="3">
-        <v>918500</v>
+        <v>1839000</v>
       </c>
       <c r="G41" s="3">
-        <v>1184600</v>
+        <v>913100</v>
       </c>
       <c r="H41" s="3">
-        <v>1357400</v>
+        <v>1177700</v>
       </c>
       <c r="I41" s="3">
-        <v>939200</v>
+        <v>1349500</v>
       </c>
       <c r="J41" s="3">
+        <v>933700</v>
+      </c>
+      <c r="K41" s="3">
         <v>1534600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>892800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1972900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1431900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2018200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1852900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2139500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2131400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1771000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1855300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2006900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1534800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3841300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4899600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1569900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2086300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3345800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1900500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2144100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2610600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3448500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2389300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3222400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2846400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3399800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>186300</v>
+        <v>291900</v>
       </c>
       <c r="E42" s="3">
-        <v>156200</v>
+        <v>185300</v>
       </c>
       <c r="F42" s="3">
-        <v>77600</v>
+        <v>155300</v>
       </c>
       <c r="G42" s="3">
-        <v>78700</v>
+        <v>77100</v>
       </c>
       <c r="H42" s="3">
-        <v>55800</v>
+        <v>78200</v>
       </c>
       <c r="I42" s="3">
-        <v>34100</v>
+        <v>55500</v>
       </c>
       <c r="J42" s="3">
+        <v>33900</v>
+      </c>
+      <c r="K42" s="3">
         <v>69500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>57500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>62000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>78900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>93000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>71500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>54300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>59700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>54500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>65400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>93700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>100700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>80600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>97200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>103000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>76500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>93200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>83200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>69000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>187800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>189300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>192000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>297900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>306900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1413700</v>
+        <v>1378400</v>
       </c>
       <c r="E43" s="3">
-        <v>1468400</v>
+        <v>1405500</v>
       </c>
       <c r="F43" s="3">
-        <v>1405500</v>
+        <v>1459900</v>
       </c>
       <c r="G43" s="3">
-        <v>1473700</v>
+        <v>1397300</v>
       </c>
       <c r="H43" s="3">
-        <v>1551800</v>
+        <v>1465100</v>
       </c>
       <c r="I43" s="3">
-        <v>1782300</v>
+        <v>1542800</v>
       </c>
       <c r="J43" s="3">
+        <v>1771900</v>
+      </c>
+      <c r="K43" s="3">
         <v>2146100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2167600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2025600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2044800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2132100</v>
-      </c>
-      <c r="O43" s="3">
-        <v>2213800</v>
       </c>
       <c r="P43" s="3">
         <v>2213800</v>
       </c>
       <c r="Q43" s="3">
+        <v>2213800</v>
+      </c>
+      <c r="R43" s="3">
         <v>2730300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2652100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2945000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3052900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3000200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3410000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2509600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3068800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2537200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2310300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2155700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2118400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2990300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2713200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2991200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3085500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3158100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2854000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>96900</v>
+        <v>82200</v>
       </c>
       <c r="E44" s="3">
-        <v>90300</v>
+        <v>96300</v>
       </c>
       <c r="F44" s="3">
-        <v>100600</v>
+        <v>89800</v>
       </c>
       <c r="G44" s="3">
-        <v>118000</v>
+        <v>100100</v>
       </c>
       <c r="H44" s="3">
-        <v>121400</v>
+        <v>117300</v>
       </c>
       <c r="I44" s="3">
-        <v>147500</v>
+        <v>120700</v>
       </c>
       <c r="J44" s="3">
+        <v>146600</v>
+      </c>
+      <c r="K44" s="3">
         <v>174000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>158600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>148200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>147000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>103400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>121500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>149300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>136000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>127100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>142500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>172600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>164400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>163400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>133400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>168100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>192100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>101800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>115000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>149800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>205300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>174100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>200000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>210800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>222200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>175900</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>59200</v>
+        <v>49000</v>
       </c>
       <c r="E45" s="3">
-        <v>195800</v>
+        <v>58900</v>
       </c>
       <c r="F45" s="3">
-        <v>85600</v>
+        <v>194700</v>
       </c>
       <c r="G45" s="3">
-        <v>70500</v>
+        <v>85100</v>
       </c>
       <c r="H45" s="3">
-        <v>51000</v>
+        <v>70100</v>
       </c>
       <c r="I45" s="3">
-        <v>141000</v>
+        <v>50700</v>
       </c>
       <c r="J45" s="3">
+        <v>140200</v>
+      </c>
+      <c r="K45" s="3">
         <v>141300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>154900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>140900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>421300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>417800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>385700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>143600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>128400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>141200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>187400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>599400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>386200</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
-      <c r="W45" s="3" t="s">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>395000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>101800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>439600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2973600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3045100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>197100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>178000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>117900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>438000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3729400</v>
+        <v>3110400</v>
       </c>
       <c r="E46" s="3">
-        <v>3760500</v>
+        <v>3707700</v>
       </c>
       <c r="F46" s="3">
-        <v>2587800</v>
+        <v>3738700</v>
       </c>
       <c r="G46" s="3">
-        <v>2925400</v>
+        <v>2572700</v>
       </c>
       <c r="H46" s="3">
-        <v>3137400</v>
+        <v>2908400</v>
       </c>
       <c r="I46" s="3">
-        <v>3044100</v>
+        <v>3119100</v>
       </c>
       <c r="J46" s="3">
+        <v>3026400</v>
+      </c>
+      <c r="K46" s="3">
         <v>4065600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3431500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4349600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4123900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4764600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4645400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4700400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5185700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4746000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5195700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5925500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5186200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7495400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7639800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5304800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4993900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6290700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7227900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7526400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6191100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6703100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5890400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7254600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6533800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6691100</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5623800</v>
+        <v>5485800</v>
       </c>
       <c r="E47" s="3">
-        <v>4818600</v>
+        <v>5591100</v>
       </c>
       <c r="F47" s="3">
-        <v>5774700</v>
+        <v>4790600</v>
       </c>
       <c r="G47" s="3">
-        <v>5947300</v>
+        <v>5741100</v>
       </c>
       <c r="H47" s="3">
-        <v>5688600</v>
+        <v>5912700</v>
       </c>
       <c r="I47" s="3">
-        <v>3753900</v>
+        <v>5655600</v>
       </c>
       <c r="J47" s="3">
+        <v>3732100</v>
+      </c>
+      <c r="K47" s="3">
         <v>576900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>558400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>532200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>534500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>533300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>565300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>587200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>664700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>826000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>847800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>543800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>475800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>272000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>253700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>486700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>268700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>52000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>53500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>53300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>51200</v>
       </c>
       <c r="AE47" s="3">
         <v>51200</v>
       </c>
       <c r="AF47" s="3">
+        <v>51200</v>
+      </c>
+      <c r="AG47" s="3">
         <v>1738500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1944800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1690700</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7598700</v>
+        <v>7356400</v>
       </c>
       <c r="E48" s="3">
-        <v>7327100</v>
+        <v>7554500</v>
       </c>
       <c r="F48" s="3">
-        <v>7530700</v>
+        <v>7284500</v>
       </c>
       <c r="G48" s="3">
-        <v>7693700</v>
+        <v>7486900</v>
       </c>
       <c r="H48" s="3">
-        <v>7601900</v>
+        <v>7648900</v>
       </c>
       <c r="I48" s="3">
-        <v>10532100</v>
+        <v>7557700</v>
       </c>
       <c r="J48" s="3">
+        <v>10470900</v>
+      </c>
+      <c r="K48" s="3">
         <v>11988200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11906500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11630300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11694700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11352200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11879500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11961800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14727000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14716600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16542600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>17296600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15778500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16995100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14544500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16139200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8276600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7060600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7104000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6984200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8748700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8271800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8497000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9027500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8879600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8405100</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3373600</v>
+        <v>3278100</v>
       </c>
       <c r="E49" s="3">
-        <v>3264400</v>
+        <v>3354000</v>
       </c>
       <c r="F49" s="3">
-        <v>3256000</v>
+        <v>3245400</v>
       </c>
       <c r="G49" s="3">
-        <v>3380900</v>
+        <v>3237000</v>
       </c>
       <c r="H49" s="3">
-        <v>3316400</v>
+        <v>3361300</v>
       </c>
       <c r="I49" s="3">
-        <v>3502000</v>
+        <v>3297100</v>
       </c>
       <c r="J49" s="3">
+        <v>3481600</v>
+      </c>
+      <c r="K49" s="3">
         <v>3674300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3603500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3422500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3540700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3501700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3610100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3575500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4160700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4237300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4643000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4839800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4296700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5123000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2361900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4394900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5728300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3698000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3864400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4002500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6605500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6627500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6847600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6962500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7099100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7250400</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1778900</v>
+        <v>1516900</v>
       </c>
       <c r="E52" s="3">
+        <v>1768500</v>
+      </c>
+      <c r="F52" s="3">
+        <v>1476900</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1976300</v>
+      </c>
+      <c r="H52" s="3">
+        <v>2104900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>2380700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1788000</v>
+      </c>
+      <c r="K52" s="3">
+        <v>1789400</v>
+      </c>
+      <c r="L52" s="3">
+        <v>1772500</v>
+      </c>
+      <c r="M52" s="3">
+        <v>1564500</v>
+      </c>
+      <c r="N52" s="3">
+        <v>1339300</v>
+      </c>
+      <c r="O52" s="3">
+        <v>1285100</v>
+      </c>
+      <c r="P52" s="3">
+        <v>1453900</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>1509100</v>
+      </c>
+      <c r="R52" s="3">
+        <v>1833200</v>
+      </c>
+      <c r="S52" s="3">
+        <v>1877000</v>
+      </c>
+      <c r="T52" s="3">
+        <v>2144700</v>
+      </c>
+      <c r="U52" s="3">
+        <v>2457300</v>
+      </c>
+      <c r="V52" s="3">
+        <v>1810800</v>
+      </c>
+      <c r="W52" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="X52" s="3">
+        <v>2288400</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>1852300</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>2311800</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>1982900</v>
+      </c>
+      <c r="AB52" s="3">
         <v>1485500</v>
       </c>
-      <c r="F52" s="3">
-        <v>1987800</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2117200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>2394600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1798400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1789400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1772500</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1564500</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1339300</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1285100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1453900</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1509100</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>1833200</v>
-      </c>
-      <c r="R52" s="3">
-        <v>1877000</v>
-      </c>
-      <c r="S52" s="3">
-        <v>2144700</v>
-      </c>
-      <c r="T52" s="3">
-        <v>2457300</v>
-      </c>
-      <c r="U52" s="3">
-        <v>1810800</v>
-      </c>
-      <c r="V52" s="3">
-        <v>2484200</v>
-      </c>
-      <c r="W52" s="3">
-        <v>2288400</v>
-      </c>
-      <c r="X52" s="3">
-        <v>1852300</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>2311800</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>1982900</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>1485500</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1533000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1761500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1790700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2147400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>850000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>981800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>874400</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>22104500</v>
+        <v>20747600</v>
       </c>
       <c r="E54" s="3">
-        <v>20656200</v>
+        <v>21975900</v>
       </c>
       <c r="F54" s="3">
-        <v>21137000</v>
+        <v>20536100</v>
       </c>
       <c r="G54" s="3">
-        <v>22064400</v>
+        <v>21014100</v>
       </c>
       <c r="H54" s="3">
-        <v>22139000</v>
+        <v>21936100</v>
       </c>
       <c r="I54" s="3">
-        <v>22630600</v>
+        <v>22010300</v>
       </c>
       <c r="J54" s="3">
+        <v>22499000</v>
+      </c>
+      <c r="K54" s="3">
         <v>22094300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21272400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21499100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21233100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21436900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>22154100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22334000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26571300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26402800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>29373700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31063100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>27548100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32369600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>27088300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>28177900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>21579300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>19084400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>19735400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>20099400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>23362400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>23444200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>23433600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>25833200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>25439100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>24911800</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2081300</v>
+        <v>2063800</v>
       </c>
       <c r="E57" s="3">
-        <v>1996600</v>
+        <v>2069200</v>
       </c>
       <c r="F57" s="3">
-        <v>1963100</v>
+        <v>1985000</v>
       </c>
       <c r="G57" s="3">
-        <v>2047700</v>
+        <v>1951700</v>
       </c>
       <c r="H57" s="3">
-        <v>2082000</v>
+        <v>2035800</v>
       </c>
       <c r="I57" s="3">
-        <v>2670000</v>
+        <v>2069900</v>
       </c>
       <c r="J57" s="3">
+        <v>2654500</v>
+      </c>
+      <c r="K57" s="3">
         <v>2980200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2954800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2927300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3040000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2817800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2822500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2982600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3510400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3344800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3834100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4089800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3950300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4383300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3795600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4040600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4256500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3576100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3484800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3486000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4665800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4258800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4539200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4887000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5288300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4924500</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1414100</v>
+        <v>2029700</v>
       </c>
       <c r="E58" s="3">
-        <v>1503600</v>
+        <v>1405900</v>
       </c>
       <c r="F58" s="3">
-        <v>947700</v>
+        <v>1494900</v>
       </c>
       <c r="G58" s="3">
-        <v>1635900</v>
+        <v>942200</v>
       </c>
       <c r="H58" s="3">
-        <v>1407700</v>
+        <v>1626400</v>
       </c>
       <c r="I58" s="3">
-        <v>1498600</v>
+        <v>1399500</v>
       </c>
       <c r="J58" s="3">
+        <v>1489900</v>
+      </c>
+      <c r="K58" s="3">
         <v>1679300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1238600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1486400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1528800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1664800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2078100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1462000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1718800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1883200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2466100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2069500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2662500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4165700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3453100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2723400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1775800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1588700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2615700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2051000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2629600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2984700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3083000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4001300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3202100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3174000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>763300</v>
+        <v>1275800</v>
       </c>
       <c r="E59" s="3">
-        <v>850000</v>
+        <v>758900</v>
       </c>
       <c r="F59" s="3">
-        <v>1329700</v>
+        <v>845000</v>
       </c>
       <c r="G59" s="3">
-        <v>1292800</v>
+        <v>1322000</v>
       </c>
       <c r="H59" s="3">
-        <v>821600</v>
+        <v>1285200</v>
       </c>
       <c r="I59" s="3">
-        <v>918200</v>
+        <v>816800</v>
       </c>
       <c r="J59" s="3">
+        <v>912800</v>
+      </c>
+      <c r="K59" s="3">
         <v>1683400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1622000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1133200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1278700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1728800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1762500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1005200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1041100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1639300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1928100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1480500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1470400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2325000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2159400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1504100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1578100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2654800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2280400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1900000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1583800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2214000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2207700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1558500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1079900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1033600</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4258700</v>
+        <v>5369300</v>
       </c>
       <c r="E60" s="3">
-        <v>4350200</v>
+        <v>4234000</v>
       </c>
       <c r="F60" s="3">
-        <v>4240600</v>
+        <v>4324900</v>
       </c>
       <c r="G60" s="3">
-        <v>4976400</v>
+        <v>4215900</v>
       </c>
       <c r="H60" s="3">
-        <v>4311300</v>
+        <v>4947400</v>
       </c>
       <c r="I60" s="3">
-        <v>5086800</v>
+        <v>4286200</v>
       </c>
       <c r="J60" s="3">
+        <v>5057200</v>
+      </c>
+      <c r="K60" s="3">
         <v>6342800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5815400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5546800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5847400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6211400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6663100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5449900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6270300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6867300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8228300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7639800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8083200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10873900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9408000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8268000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7610400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7819600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8380900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7437000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8879100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9457500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9829900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>10446800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>9570300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>9132100</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8537000</v>
+        <v>7525900</v>
       </c>
       <c r="E61" s="3">
-        <v>8407800</v>
+        <v>8487400</v>
       </c>
       <c r="F61" s="3">
-        <v>8126000</v>
+        <v>8358900</v>
       </c>
       <c r="G61" s="3">
-        <v>8402700</v>
+        <v>8078800</v>
       </c>
       <c r="H61" s="3">
-        <v>7905600</v>
+        <v>8353900</v>
       </c>
       <c r="I61" s="3">
-        <v>10134500</v>
+        <v>7859700</v>
       </c>
       <c r="J61" s="3">
+        <v>10075500</v>
+      </c>
+      <c r="K61" s="3">
         <v>11255800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11328000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10733700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10902700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10874900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11236200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11596800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13901600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13888300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>15270500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>15872400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>12837700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14534900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>11137800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>13131100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6309600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4548900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4739300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4852400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5973300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5762600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5949300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6540000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7446200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7214000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1242300</v>
+        <v>1175400</v>
       </c>
       <c r="E62" s="3">
-        <v>1235800</v>
+        <v>1235100</v>
       </c>
       <c r="F62" s="3">
-        <v>1196800</v>
+        <v>1228600</v>
       </c>
       <c r="G62" s="3">
-        <v>1217300</v>
+        <v>1189800</v>
       </c>
       <c r="H62" s="3">
-        <v>1280400</v>
+        <v>1210200</v>
       </c>
       <c r="I62" s="3">
-        <v>1320100</v>
+        <v>1272900</v>
       </c>
       <c r="J62" s="3">
+        <v>1312400</v>
+      </c>
+      <c r="K62" s="3">
         <v>1686600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1562100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1481200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1520100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1510500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1560100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1579800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1850400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1790500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2093100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2227800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1830500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1962200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1408000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1872300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1515700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1260900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1244500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1065200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1292200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1284700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1223900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1479700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1592300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1503800</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>14667300</v>
+        <v>14645800</v>
       </c>
       <c r="E66" s="3">
-        <v>14556700</v>
+        <v>14582000</v>
       </c>
       <c r="F66" s="3">
-        <v>14113600</v>
+        <v>14472100</v>
       </c>
       <c r="G66" s="3">
-        <v>15128500</v>
+        <v>14031500</v>
       </c>
       <c r="H66" s="3">
-        <v>14024300</v>
+        <v>15040600</v>
       </c>
       <c r="I66" s="3">
-        <v>16942100</v>
+        <v>13942700</v>
       </c>
       <c r="J66" s="3">
+        <v>16843600</v>
+      </c>
+      <c r="K66" s="3">
         <v>19755200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19206700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18282800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18759900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19035000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19933600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19135300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22601700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23108300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>26282800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>26436000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23336400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>27950500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>22521100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23869900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16000800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14120200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14910200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13911100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16704900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17006400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17551000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19074800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19165800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>18363900</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7031200</v>
+        <v>5837600</v>
       </c>
       <c r="E72" s="3">
-        <v>5882300</v>
+        <v>6990300</v>
       </c>
       <c r="F72" s="3">
-        <v>6706100</v>
+        <v>5848100</v>
       </c>
       <c r="G72" s="3">
-        <v>6457400</v>
+        <v>6667100</v>
       </c>
       <c r="H72" s="3">
-        <v>7565900</v>
+        <v>6419800</v>
       </c>
       <c r="I72" s="3">
-        <v>5211100</v>
+        <v>7521900</v>
       </c>
       <c r="J72" s="3">
+        <v>5180800</v>
+      </c>
+      <c r="K72" s="3">
         <v>1730200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1549800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2847700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2111700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2030300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1803800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2791900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3421800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2516200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2252700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3551600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3562800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3647400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3964700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5195400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4828000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4471800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4521900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5777800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6005900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5929300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5278900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5612000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5136300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5466800</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7437100</v>
+        <v>6101800</v>
       </c>
       <c r="E76" s="3">
-        <v>6099400</v>
+        <v>7393900</v>
       </c>
       <c r="F76" s="3">
-        <v>7023400</v>
+        <v>6064000</v>
       </c>
       <c r="G76" s="3">
-        <v>6935900</v>
+        <v>6982600</v>
       </c>
       <c r="H76" s="3">
-        <v>8114700</v>
+        <v>6895600</v>
       </c>
       <c r="I76" s="3">
-        <v>5688500</v>
+        <v>8067500</v>
       </c>
       <c r="J76" s="3">
+        <v>5655400</v>
+      </c>
+      <c r="K76" s="3">
         <v>2339100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2065800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3216200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2473200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2401900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2220500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3198700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3969600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3294600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3090900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4627100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4211700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4419100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4567200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4308000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5578500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4964200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4825200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6188300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6657500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6437800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5882600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6758400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6273400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6547800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1093500</v>
+        <v>238900</v>
       </c>
       <c r="E81" s="3">
-        <v>-726700</v>
+        <v>1087100</v>
       </c>
       <c r="F81" s="3">
-        <v>231800</v>
+        <v>-722500</v>
       </c>
       <c r="G81" s="3">
-        <v>77700</v>
+        <v>230500</v>
       </c>
       <c r="H81" s="3">
-        <v>1716400</v>
+        <v>77200</v>
       </c>
       <c r="I81" s="3">
-        <v>3585600</v>
+        <v>1706400</v>
       </c>
       <c r="J81" s="3">
+        <v>3564800</v>
+      </c>
+      <c r="K81" s="3">
         <v>146500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-105600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>623200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>242400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>205500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-365300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>796400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>458600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>491800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>77400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>191400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-81700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>330100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>432600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>136900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>601600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>270600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>510700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>257600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>666400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-19300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>513900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>348900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>393200</v>
+        <v>395400</v>
       </c>
       <c r="E83" s="3">
-        <v>399000</v>
+        <v>390900</v>
       </c>
       <c r="F83" s="3">
-        <v>388600</v>
+        <v>396700</v>
       </c>
       <c r="G83" s="3">
-        <v>399100</v>
+        <v>386300</v>
       </c>
       <c r="H83" s="3">
-        <v>471300</v>
+        <v>396800</v>
       </c>
       <c r="I83" s="3">
-        <v>601800</v>
+        <v>468600</v>
       </c>
       <c r="J83" s="3">
+        <v>598300</v>
+      </c>
+      <c r="K83" s="3">
         <v>609000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>859100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>603300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>700000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>611300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>635000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1267200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>744900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>722500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>842100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>795400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>764600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>756300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>666600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>641700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>437000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>571000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>567700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>597600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>701200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>610700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>662200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>630900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3456500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1136300</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>814800</v>
+        <v>709600</v>
       </c>
       <c r="E89" s="3">
-        <v>843700</v>
+        <v>810100</v>
       </c>
       <c r="F89" s="3">
-        <v>795100</v>
+        <v>838800</v>
       </c>
       <c r="G89" s="3">
-        <v>538500</v>
+        <v>790500</v>
       </c>
       <c r="H89" s="3">
-        <v>577200</v>
+        <v>535400</v>
       </c>
       <c r="I89" s="3">
-        <v>885900</v>
+        <v>573800</v>
       </c>
       <c r="J89" s="3">
+        <v>880800</v>
+      </c>
+      <c r="K89" s="3">
         <v>1026700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>909600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>893000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>801700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1199300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>924400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1017300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1171000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1106800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1246300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1152100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>774300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1405400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>703500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1071600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>926100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1107200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>895600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>880500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1064600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1399400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1343300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1129900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4904600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1293700</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3094000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3907000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3170000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3191000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3604000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4763000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9177000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4428000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5665000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4491000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4936000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4134000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-439000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-535400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-504100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1395900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>571200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-610400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>1000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>32500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-101800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-827500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1315200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>484600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-568500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-523100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-449500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-530800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1393000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2925500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-500200</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-173600</v>
+        <v>-291900</v>
       </c>
       <c r="E94" s="3">
-        <v>-1256200</v>
+        <v>-172600</v>
       </c>
       <c r="F94" s="3">
-        <v>-300200</v>
+        <v>-1248900</v>
       </c>
       <c r="G94" s="3">
-        <v>-369600</v>
+        <v>-298500</v>
       </c>
       <c r="H94" s="3">
-        <v>195200</v>
+        <v>-367400</v>
       </c>
       <c r="I94" s="3">
-        <v>-1088800</v>
+        <v>194100</v>
       </c>
       <c r="J94" s="3">
+        <v>-1082500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-289100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-521000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-292700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-469500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-266300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-433500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-443000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>252400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-349300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-562400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-499100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1439700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2515000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-535700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-564800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-906400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1771500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-563600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-511600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>50900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-662400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2602200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,106 +8585,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-651200</v>
       </c>
       <c r="E96" s="3">
-        <v>-576400</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-573100</v>
       </c>
       <c r="G96" s="3">
-        <v>-654800</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-651000</v>
       </c>
       <c r="I96" s="3">
-        <v>-569200</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-565900</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-663700</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-526500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-23400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-633100</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-623200</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-695500</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-631400</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-741900</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1368800</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-639200</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-606500</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-747500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-30800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1386600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-552000</v>
+        <v>-1076900</v>
       </c>
       <c r="E100" s="3">
-        <v>1393200</v>
+        <v>-548800</v>
       </c>
       <c r="F100" s="3">
-        <v>-772100</v>
+        <v>1385100</v>
       </c>
       <c r="G100" s="3">
-        <v>-383300</v>
+        <v>-1777900</v>
       </c>
       <c r="H100" s="3">
-        <v>-382900</v>
+        <v>629200</v>
       </c>
       <c r="I100" s="3">
-        <v>-370800</v>
+        <v>-380700</v>
       </c>
       <c r="J100" s="3">
+        <v>-368600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-174300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1472900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-255600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-933400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-636000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-726000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-311400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1074200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-653300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-893600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-302200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1248800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-253200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1835400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>209000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1683300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1548700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-652600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-311900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1372300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-107900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1948200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1114300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>503100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>12500</v>
+        <v>-14600</v>
       </c>
       <c r="E101" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F101" s="3">
         <v>1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>700</v>
       </c>
-      <c r="G101" s="3">
-        <v>14200</v>
-      </c>
       <c r="H101" s="3">
-        <v>41600</v>
+        <v>14100</v>
       </c>
       <c r="I101" s="3">
-        <v>-24000</v>
+        <v>41400</v>
       </c>
       <c r="J101" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="K101" s="3">
         <v>73200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>21000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-13400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>19600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-37400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>20100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-24300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-26100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-37000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-38800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>154000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>10400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>93000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-22000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>10700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-29500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>72600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-60200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>15500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>26300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-55000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-70700</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>101700</v>
+        <v>-673800</v>
       </c>
       <c r="E102" s="3">
-        <v>982200</v>
+        <v>101100</v>
       </c>
       <c r="F102" s="3">
-        <v>-276600</v>
+        <v>976500</v>
       </c>
       <c r="G102" s="3">
-        <v>-200200</v>
+        <v>-275000</v>
       </c>
       <c r="H102" s="3">
-        <v>431100</v>
+        <v>-199000</v>
       </c>
       <c r="I102" s="3">
-        <v>-597700</v>
+        <v>428600</v>
       </c>
       <c r="J102" s="3">
+        <v>-594200</v>
+      </c>
+      <c r="K102" s="3">
         <v>636500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1063300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>331300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-581600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>259600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-215000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>238600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>323100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>67300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-248400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>504800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1900700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1268800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1989000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>700100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1652800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1326600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-211700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-864300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1083000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-642900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>373700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1133100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1819800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>TELNY</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>1874800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1829700</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1968600</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1891000</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1901900</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1804300</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>1849500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1847400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2659500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2562100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1417100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2515000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2550100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2583900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2483500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3039500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3219500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3236500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3165100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3421100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3112400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3010000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2674300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2820000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2813600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2777400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2247000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3179900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3280600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3402600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>15461200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3853000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>401100</v>
-      </c>
-      <c r="E9" s="3">
-        <v>399500</v>
-      </c>
-      <c r="F9" s="3">
-        <v>487500</v>
-      </c>
-      <c r="G9" s="3">
-        <v>425500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>440000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>439000</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>458300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>406600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>696700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>680400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>426600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>628700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>647300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>686400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>780400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>702800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>780300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>795900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>785200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>816200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>725100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>700800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>588400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>619800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>662700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>632900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>523300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>725500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>760900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1192600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5577700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1329500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>1473700</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1430300</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1481100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1465400</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1461900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1365400</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>1391200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1440800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1962700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1881600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>990500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1886300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1902900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1897500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1703200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2336700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2439200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2440500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2380000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2605000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2387300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2309300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2085900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2200200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2150900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2144500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1723800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2454400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2519700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2210000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>9883500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2523500</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,210 +1358,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>16800</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-650800</v>
-      </c>
-      <c r="F14" s="3">
-        <v>736000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>9300</v>
-      </c>
-      <c r="H14" s="3">
-        <v>53200</v>
-      </c>
-      <c r="I14" s="3">
-        <v>17300</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>32100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>259800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>16900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>93600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>16900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>13700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>10300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>15300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>10900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>147800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>37000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>37100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>26900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>20700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>268700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>25500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>26600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>18600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>59900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>55600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>718100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-82400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>158900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>707900</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>395300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>390800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>394400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>387100</v>
-      </c>
-      <c r="H15" s="3">
-        <v>395400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>377900</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="3">
         <v>410300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>394500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>622000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>603300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>360100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>607100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>603000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>599100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>459400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>722500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>761100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>722000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>756200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>757100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>666800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>637800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>462800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>553400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>529200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>547800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>457600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>556300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>570100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>581900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>2414600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>617700</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>1463600</v>
-      </c>
-      <c r="E17" s="3">
-        <v>641100</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2310400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1417600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1535700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1443800</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>1543100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1376400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2368500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1912500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1395100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1956000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2017600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2050200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1679400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2209800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2664400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2547000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2550200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2612300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2398400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2269400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2378100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2132300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2221000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2183200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1893900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2354800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3111300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2705400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>12375000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3663500</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>411100</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1188700</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-341700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>473400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>366200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>360500</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>306400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>471100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>291000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>649600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>22000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>558900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>532500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>533700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>804100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>829700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>555100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>689500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>614900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>808800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>714000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>740600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>296200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>687700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>592500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>594300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>353200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>825100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>169300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>697100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3086200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>189500</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>72800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>113900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-134000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>27100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-86900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-321600</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>90500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-228500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-211300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>15700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-86700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-59500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>19500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>219500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>49700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>120200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-404300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>85200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-202000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>7100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>62800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-258100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-124000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>233900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-45200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>211800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>102900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>100400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-323500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>90900</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>879400</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1693500</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-79100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>886800</v>
-      </c>
-      <c r="H21" s="3">
-        <v>676100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>507500</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>995100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>851500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>938900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1268700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>712400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1083600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1108000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1820400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1768500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1602000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1517400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1080600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1464700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1363200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1387700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1445100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>516500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1017600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1422600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1009200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1647600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>934400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1428400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>6219100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1416700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>92900</v>
-      </c>
-      <c r="E22" s="3">
-        <v>93400</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
+        <v>123300</v>
+      </c>
+      <c r="L22" s="3">
+        <v>43700</v>
+      </c>
+      <c r="M22" s="3">
+        <v>58700</v>
+      </c>
+      <c r="N22" s="3">
+        <v>45200</v>
+      </c>
+      <c r="O22" s="3">
+        <v>48700</v>
+      </c>
+      <c r="P22" s="3">
         <v>61000</v>
       </c>
-      <c r="G22" s="3">
-        <v>71000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>64100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>43600</v>
-      </c>
-      <c r="J22" s="3">
-        <v>123300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>43700</v>
-      </c>
-      <c r="L22" s="3">
-        <v>58700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>45200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>48700</v>
-      </c>
-      <c r="O22" s="3">
-        <v>61000</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>61600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>60700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>110900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>107400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>85400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>89800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>173900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>135400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>117100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>100900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>104900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>45900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>46200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>30500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>105800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>54700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>72700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>72500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>382700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>391000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1209200</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-536800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>429500</v>
-      </c>
-      <c r="H23" s="3">
-        <v>215200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>273600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>198800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>21100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>620100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-36300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>411200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>411400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>492600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>912600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>772100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>589800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>195400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>526300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>471500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>603900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>702600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-66900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>651500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>422300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>797600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>202200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>982200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>199500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>725000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2379900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>210800</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>102000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>48600</v>
-      </c>
-      <c r="F24" s="3">
-        <v>166500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>155600</v>
-      </c>
-      <c r="H24" s="3">
-        <v>67400</v>
-      </c>
-      <c r="I24" s="3">
-        <v>17800</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>-166900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>78100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-36300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>39800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>134300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>138100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>154900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>158700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>217500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>221300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>69100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>147500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>483800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>216100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>203000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>55800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>205700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>125000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>235000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>77200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>272900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>186400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>197900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>730400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>289000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>1160500</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-703300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>273800</v>
-      </c>
-      <c r="H26" s="3">
-        <v>147700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-22500</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>440500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>120700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>57400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>720600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-76100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>276900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>273200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>337700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>754000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>554600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>368500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>126300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>378700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-12400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>387800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>499600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-122700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>445800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>297300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>562700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>124900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>709300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>13100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>527100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1649500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>247700</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1100400</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-728400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>237200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>90500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-58100</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>399500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>47500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>656000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-142100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>203200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>197800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>266500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>668600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>461100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>266200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>277900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-113600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>302100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>397100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-160200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>370200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>208100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>484100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>46100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>623500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-79500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>441500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1282600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-93500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,109 +2783,115 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="E29" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="F29" s="3">
-        <v>5900</v>
-      </c>
-      <c r="G29" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="H29" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="I29" s="3">
-        <v>1764600</v>
-      </c>
-      <c r="J29" s="3">
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K29" s="3">
         <v>3165300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>99000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-89500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-32700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>147100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>39200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>7600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-631800</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>127800</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-2500</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>225600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>67900</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-86600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>31900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>28000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>35400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>297100</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>231400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>62500</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>26600</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>211500</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>42800</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>60200</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>72400</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-933600</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-501000</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-72800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-113900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>134000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-27100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>86900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>321600</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-90500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>228500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>211300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-15700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>86700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>59500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-19500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-219500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-49700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-120200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>404300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-85200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>202000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-62800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>258100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>124000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-233900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>45200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-211800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-102900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-100400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>323500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-90900</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>238900</v>
-      </c>
-      <c r="E33" s="3">
-        <v>1087100</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-722500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>230500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>77200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1706400</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>3564800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>146500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-105600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>623200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>242400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>205500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-365300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>796400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>458600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>491800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>77400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>191400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-81700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>330100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>432600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>136900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>601600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>270600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>510700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>257600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>666400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-19300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>513900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>348900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>238900</v>
-      </c>
-      <c r="E35" s="3">
-        <v>1087100</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-722500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>230500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>77200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1706400</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>3564800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>146500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-105600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>623200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>242400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>205500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-365300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>796400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>458600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>491800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>77400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>191400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-81700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>330100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>432600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>136900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>601600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>270600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>510700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>257600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>666400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-19300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>513900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>348900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,917 +3698,945 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1308800</v>
+        <v>1582900</v>
       </c>
       <c r="E41" s="3">
-        <v>1961800</v>
+        <v>1306100</v>
       </c>
       <c r="F41" s="3">
-        <v>1839000</v>
+        <v>1926200</v>
       </c>
       <c r="G41" s="3">
-        <v>913100</v>
+        <v>1928500</v>
       </c>
       <c r="H41" s="3">
-        <v>1177700</v>
+        <v>910500</v>
       </c>
       <c r="I41" s="3">
-        <v>1349500</v>
+        <v>1168300</v>
       </c>
       <c r="J41" s="3">
+        <v>1371900</v>
+      </c>
+      <c r="K41" s="3">
         <v>933700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1534600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>892800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1972900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1431900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2018200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1852900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2139500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2131400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1771000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1855300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2006900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1534800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3841300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4899600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1569900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2086300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3345800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1900500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2144100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2610600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3448500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2389300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3222400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2846400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3399800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>291900</v>
+        <v>135700</v>
       </c>
       <c r="E42" s="3">
-        <v>185300</v>
+        <v>245900</v>
       </c>
       <c r="F42" s="3">
-        <v>155300</v>
+        <v>125400</v>
       </c>
       <c r="G42" s="3">
-        <v>77100</v>
+        <v>128800</v>
       </c>
       <c r="H42" s="3">
-        <v>78200</v>
+        <v>30400</v>
       </c>
       <c r="I42" s="3">
-        <v>55500</v>
+        <v>30300</v>
       </c>
       <c r="J42" s="3">
+        <v>31300</v>
+      </c>
+      <c r="K42" s="3">
         <v>33900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>69500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>57500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>62000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>78900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>93000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>71500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>54300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>59700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>54500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>65400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>93700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>100700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>80600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>97200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>103000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>76500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>93200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>83200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>69000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>187800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>189300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>192000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>297900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>306900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1378400</v>
+        <v>1343400</v>
       </c>
       <c r="E43" s="3">
-        <v>1405500</v>
+        <v>1375500</v>
       </c>
       <c r="F43" s="3">
-        <v>1459900</v>
+        <v>1380000</v>
       </c>
       <c r="G43" s="3">
-        <v>1397300</v>
+        <v>1356500</v>
       </c>
       <c r="H43" s="3">
-        <v>1465100</v>
+        <v>1393300</v>
       </c>
       <c r="I43" s="3">
-        <v>1542800</v>
+        <v>1453400</v>
       </c>
       <c r="J43" s="3">
+        <v>1568500</v>
+      </c>
+      <c r="K43" s="3">
         <v>1771900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2146100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2167600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2025600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2044800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2132100</v>
-      </c>
-      <c r="P43" s="3">
-        <v>2213800</v>
       </c>
       <c r="Q43" s="3">
         <v>2213800</v>
       </c>
       <c r="R43" s="3">
+        <v>2213800</v>
+      </c>
+      <c r="S43" s="3">
         <v>2730300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2652100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2945000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3052900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3000200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3410000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2509600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3068800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2537200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2310300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2155700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2118400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2990300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2713200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2991200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3085500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3158100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2854000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>82200</v>
+        <v>83700</v>
       </c>
       <c r="E44" s="3">
-        <v>96300</v>
+        <v>82000</v>
       </c>
       <c r="F44" s="3">
-        <v>89800</v>
+        <v>94500</v>
       </c>
       <c r="G44" s="3">
-        <v>100100</v>
+        <v>94200</v>
       </c>
       <c r="H44" s="3">
-        <v>117300</v>
+        <v>99800</v>
       </c>
       <c r="I44" s="3">
-        <v>120700</v>
+        <v>116300</v>
       </c>
       <c r="J44" s="3">
+        <v>122700</v>
+      </c>
+      <c r="K44" s="3">
         <v>146600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>174000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>158600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>148200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>147000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>103400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>121500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>149300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>136000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>127100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>142500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>172600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>164400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>163400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>133400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>168100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>192100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>101800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>115000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>149800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>205300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>174100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>200000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>210800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>222200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>175900</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>49000</v>
+        <v>38300</v>
       </c>
       <c r="E45" s="3">
-        <v>58900</v>
+        <v>45400</v>
       </c>
       <c r="F45" s="3">
-        <v>194700</v>
+        <v>56500</v>
       </c>
       <c r="G45" s="3">
-        <v>85100</v>
+        <v>209600</v>
       </c>
       <c r="H45" s="3">
-        <v>70100</v>
+        <v>46400</v>
       </c>
       <c r="I45" s="3">
-        <v>50700</v>
+        <v>47300</v>
       </c>
       <c r="J45" s="3">
+        <v>25000</v>
+      </c>
+      <c r="K45" s="3">
         <v>140200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>141300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>154900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>140900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>421300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>417800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>385700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>143600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>128400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>141200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>187400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>599400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>386200</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z45" s="3">
         <v>395000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>101800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>439600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2973600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3045100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>197100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>178000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>117900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>438000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3110400</v>
+        <v>3234800</v>
       </c>
       <c r="E46" s="3">
-        <v>3707700</v>
+        <v>3103800</v>
       </c>
       <c r="F46" s="3">
-        <v>3738700</v>
+        <v>3640400</v>
       </c>
       <c r="G46" s="3">
-        <v>2572700</v>
+        <v>3920600</v>
       </c>
       <c r="H46" s="3">
-        <v>2908400</v>
+        <v>2565300</v>
       </c>
       <c r="I46" s="3">
-        <v>3119100</v>
+        <v>2885200</v>
       </c>
       <c r="J46" s="3">
+        <v>3171000</v>
+      </c>
+      <c r="K46" s="3">
         <v>3026400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4065600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3431500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4349600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4123900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4764600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4645400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4700400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5185700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4746000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5195700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5925500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5186200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7495400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7639800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5304800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4993900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6290700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7227900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7526400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6191100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6703100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5890400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7254600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6533800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6691100</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5485800</v>
+        <v>6414000</v>
       </c>
       <c r="E47" s="3">
-        <v>5591100</v>
+        <v>5474200</v>
       </c>
       <c r="F47" s="3">
-        <v>4790600</v>
+        <v>5489700</v>
       </c>
       <c r="G47" s="3">
-        <v>5741100</v>
+        <v>5164400</v>
       </c>
       <c r="H47" s="3">
-        <v>5912700</v>
+        <v>5724600</v>
       </c>
       <c r="I47" s="3">
-        <v>5655600</v>
+        <v>5865500</v>
       </c>
       <c r="J47" s="3">
+        <v>5749600</v>
+      </c>
+      <c r="K47" s="3">
         <v>3732100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>576900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>558400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>532200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>534500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>533300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>565300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>587200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>664700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>826000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>847800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>543800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>475800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>272000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>253700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>486700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>268700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>52000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>53500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>53300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>51200</v>
       </c>
       <c r="AF47" s="3">
         <v>51200</v>
       </c>
       <c r="AG47" s="3">
+        <v>51200</v>
+      </c>
+      <c r="AH47" s="3">
         <v>1738500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1944800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1690700</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7356400</v>
+        <v>7471100</v>
       </c>
       <c r="E48" s="3">
-        <v>7554500</v>
+        <v>7340700</v>
       </c>
       <c r="F48" s="3">
-        <v>7284500</v>
+        <v>7417400</v>
       </c>
       <c r="G48" s="3">
-        <v>7486900</v>
+        <v>7639000</v>
       </c>
       <c r="H48" s="3">
-        <v>7648900</v>
+        <v>7465400</v>
       </c>
       <c r="I48" s="3">
-        <v>7557700</v>
+        <v>7587900</v>
       </c>
       <c r="J48" s="3">
+        <v>7683400</v>
+      </c>
+      <c r="K48" s="3">
         <v>10470900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11988200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11906500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11630300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11694700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11352200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11879500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11961800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14727000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14716600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16542600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>17296600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>15778500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16995100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14544500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16139200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8276600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7060600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7104000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6984200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8748700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8271800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8497000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9027500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8879600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8405100</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3278100</v>
+        <v>3393000</v>
       </c>
       <c r="E49" s="3">
-        <v>3354000</v>
+        <v>3271200</v>
       </c>
       <c r="F49" s="3">
-        <v>3245400</v>
+        <v>3293200</v>
       </c>
       <c r="G49" s="3">
-        <v>3237000</v>
+        <v>3403300</v>
       </c>
       <c r="H49" s="3">
-        <v>3361300</v>
+        <v>3227700</v>
       </c>
       <c r="I49" s="3">
-        <v>3297100</v>
+        <v>3334400</v>
       </c>
       <c r="J49" s="3">
+        <v>3352000</v>
+      </c>
+      <c r="K49" s="3">
         <v>3481600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3674300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3603500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3422500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3540700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3501700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3610100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3575500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4160700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4237300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4643000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4839800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4296700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5123000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2361900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4394900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5728300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3698000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3864400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4002500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6605500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6627500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6847600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>6962500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7099100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7250400</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1516900</v>
+        <v>1233800</v>
       </c>
       <c r="E52" s="3">
-        <v>1768500</v>
+        <v>1198500</v>
       </c>
       <c r="F52" s="3">
-        <v>1476900</v>
+        <v>1346200</v>
       </c>
       <c r="G52" s="3">
-        <v>1976300</v>
+        <v>531600</v>
       </c>
       <c r="H52" s="3">
-        <v>2104900</v>
+        <v>1612000</v>
       </c>
       <c r="I52" s="3">
-        <v>2380700</v>
+        <v>1628600</v>
       </c>
       <c r="J52" s="3">
+        <v>1912600</v>
+      </c>
+      <c r="K52" s="3">
         <v>1788000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1789400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1772500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1564500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1339300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1285100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1453900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1509100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1833200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1877000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2144700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2457300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1810800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2484200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2288400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1852300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2311800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1982900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1485500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1533000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1761500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1790700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2147400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>850000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>981800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>874400</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>20747600</v>
+        <v>22066300</v>
       </c>
       <c r="E54" s="3">
-        <v>21975900</v>
+        <v>20703500</v>
       </c>
       <c r="F54" s="3">
-        <v>20536100</v>
+        <v>21577000</v>
       </c>
       <c r="G54" s="3">
-        <v>21014100</v>
+        <v>21535400</v>
       </c>
       <c r="H54" s="3">
-        <v>21936100</v>
+        <v>20953700</v>
       </c>
       <c r="I54" s="3">
-        <v>22010300</v>
+        <v>21761100</v>
       </c>
       <c r="J54" s="3">
+        <v>22376200</v>
+      </c>
+      <c r="K54" s="3">
         <v>22499000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22094300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21272400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21499100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21233100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21436900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22154100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22334000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26571300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26402800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>29373700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31063100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>27548100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32369600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>27088300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>28177900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21579300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>19084400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>19735400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>20099400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>23362400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>23444200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>23433600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>25833200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>25439100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>24911800</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2063800</v>
+        <v>2025300</v>
       </c>
       <c r="E57" s="3">
-        <v>2069200</v>
+        <v>2059400</v>
       </c>
       <c r="F57" s="3">
-        <v>1985000</v>
+        <v>2031600</v>
       </c>
       <c r="G57" s="3">
-        <v>1951700</v>
+        <v>542500</v>
       </c>
       <c r="H57" s="3">
-        <v>2035800</v>
+        <v>1946100</v>
       </c>
       <c r="I57" s="3">
-        <v>2069900</v>
+        <v>2019500</v>
       </c>
       <c r="J57" s="3">
+        <v>2104300</v>
+      </c>
+      <c r="K57" s="3">
         <v>2654500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2980200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2954800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2927300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3040000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2817800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2822500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2982600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3510400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3344800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3834100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4089800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3950300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4383300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3795600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4040600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4256500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3576100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3484800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3486000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4665800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4258800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4539200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4887000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5288300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4924500</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2029700</v>
+        <v>2118600</v>
       </c>
       <c r="E58" s="3">
-        <v>1405900</v>
+        <v>2025300</v>
       </c>
       <c r="F58" s="3">
-        <v>1494900</v>
+        <v>1380400</v>
       </c>
       <c r="G58" s="3">
-        <v>942200</v>
+        <v>1620600</v>
       </c>
       <c r="H58" s="3">
-        <v>1626400</v>
+        <v>939500</v>
       </c>
       <c r="I58" s="3">
-        <v>1399500</v>
+        <v>1613400</v>
       </c>
       <c r="J58" s="3">
+        <v>1422800</v>
+      </c>
+      <c r="K58" s="3">
         <v>1489900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1679300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1238600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1486400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1528800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1664800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2078100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1462000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1718800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1883200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2466100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2069500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2662500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4165700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3453100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2723400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1775800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1588700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2615700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2051000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2629600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2984700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3083000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4001300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3202100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3174000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1275800</v>
+        <v>1292100</v>
       </c>
       <c r="E59" s="3">
-        <v>758900</v>
+        <v>1273100</v>
       </c>
       <c r="F59" s="3">
-        <v>845000</v>
+        <v>745100</v>
       </c>
       <c r="G59" s="3">
-        <v>1322000</v>
+        <v>1299300</v>
       </c>
       <c r="H59" s="3">
-        <v>1285200</v>
+        <v>1318200</v>
       </c>
       <c r="I59" s="3">
-        <v>816800</v>
+        <v>1275000</v>
       </c>
       <c r="J59" s="3">
+        <v>830400</v>
+      </c>
+      <c r="K59" s="3">
         <v>912800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1683400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1622000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1133200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1278700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1728800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1762500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1005200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1041100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1639300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1928100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1480500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1470400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2325000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2159400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1504100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1578100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2654800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2280400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1900000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1583800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2214000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2207700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1558500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1079900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1033600</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5369300</v>
+        <v>5436000</v>
       </c>
       <c r="E60" s="3">
-        <v>4234000</v>
+        <v>5357900</v>
       </c>
       <c r="F60" s="3">
-        <v>4324900</v>
+        <v>4157100</v>
       </c>
       <c r="G60" s="3">
-        <v>4215900</v>
+        <v>4535400</v>
       </c>
       <c r="H60" s="3">
-        <v>4947400</v>
+        <v>4203800</v>
       </c>
       <c r="I60" s="3">
-        <v>4286200</v>
+        <v>4908000</v>
       </c>
       <c r="J60" s="3">
+        <v>4357500</v>
+      </c>
+      <c r="K60" s="3">
         <v>5057200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6342800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5815400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5546800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5847400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6211400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6663100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5449900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6270300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6867300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8228300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7639800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8083200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10873900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9408000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8268000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7610400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7819600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8380900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7437000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8879100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9457500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9829900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>10446800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>9570300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>9132100</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7525900</v>
+        <v>7830100</v>
       </c>
       <c r="E61" s="3">
-        <v>8487400</v>
+        <v>7509900</v>
       </c>
       <c r="F61" s="3">
-        <v>8358900</v>
+        <v>8333300</v>
       </c>
       <c r="G61" s="3">
-        <v>8078800</v>
+        <v>8765700</v>
       </c>
       <c r="H61" s="3">
-        <v>8353900</v>
+        <v>8055600</v>
       </c>
       <c r="I61" s="3">
-        <v>7859700</v>
+        <v>8287200</v>
       </c>
       <c r="J61" s="3">
+        <v>7990300</v>
+      </c>
+      <c r="K61" s="3">
         <v>10075500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11255800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11328000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10733700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10902700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10874900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11236200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11596800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13901600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13888300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>15270500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15872400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>12837700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14534900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11137800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>13131100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6309600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4548900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4739300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4852400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5973300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5762600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5949300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6540000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7446200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7214000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1175400</v>
+        <v>723500</v>
       </c>
       <c r="E62" s="3">
-        <v>1235100</v>
+        <v>714600</v>
       </c>
       <c r="F62" s="3">
-        <v>1228600</v>
+        <v>724400</v>
       </c>
       <c r="G62" s="3">
-        <v>1189800</v>
+        <v>775600</v>
       </c>
       <c r="H62" s="3">
-        <v>1210200</v>
+        <v>714300</v>
       </c>
       <c r="I62" s="3">
-        <v>1272900</v>
+        <v>724700</v>
       </c>
       <c r="J62" s="3">
+        <v>799100</v>
+      </c>
+      <c r="K62" s="3">
         <v>1312400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1686600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1562100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1481200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1520100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1510500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1560100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1579800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1850400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1790500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2093100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2227800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1830500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1962200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1408000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1872300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1515700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1260900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1244500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1065200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1292200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1284700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1223900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1479700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1592300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1503800</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>14645800</v>
+        <v>14468700</v>
       </c>
       <c r="E66" s="3">
-        <v>14582000</v>
+        <v>14040700</v>
       </c>
       <c r="F66" s="3">
-        <v>14472100</v>
+        <v>13703200</v>
       </c>
       <c r="G66" s="3">
-        <v>14031500</v>
+        <v>14589500</v>
       </c>
       <c r="H66" s="3">
-        <v>15040600</v>
+        <v>13445800</v>
       </c>
       <c r="I66" s="3">
-        <v>13942700</v>
+        <v>14395700</v>
       </c>
       <c r="J66" s="3">
+        <v>13641900</v>
+      </c>
+      <c r="K66" s="3">
         <v>16843600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19755200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19206700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18282800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18759900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19035000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19933600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19135300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>22601700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23108300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>26282800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>26436000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23336400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>27950500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>22521100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23869900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16000800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14120200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14910200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13911100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16704900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17006400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17551000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19074800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>19165800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>18363900</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5837600</v>
+        <v>8400900</v>
       </c>
       <c r="E72" s="3">
-        <v>6990300</v>
+        <v>7993300</v>
       </c>
       <c r="F72" s="3">
-        <v>5848100</v>
+        <v>8839200</v>
       </c>
       <c r="G72" s="3">
-        <v>6667100</v>
+        <v>8292600</v>
       </c>
       <c r="H72" s="3">
-        <v>6419800</v>
+        <v>8613400</v>
       </c>
       <c r="I72" s="3">
-        <v>7521900</v>
+        <v>8340700</v>
       </c>
       <c r="J72" s="3">
+        <v>9713600</v>
+      </c>
+      <c r="K72" s="3">
         <v>5180800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1730200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1549800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2847700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2111700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2030300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1803800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2791900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3421800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2516200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2252700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3551600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3562800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3647400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3964700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5195400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4828000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4471800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4521900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5777800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6005900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5929300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5278900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5612000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5136300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5466800</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6101800</v>
+        <v>7081800</v>
       </c>
       <c r="E76" s="3">
-        <v>7393900</v>
+        <v>6088800</v>
       </c>
       <c r="F76" s="3">
-        <v>6064000</v>
+        <v>7259700</v>
       </c>
       <c r="G76" s="3">
-        <v>6982600</v>
+        <v>6359100</v>
       </c>
       <c r="H76" s="3">
-        <v>6895600</v>
+        <v>6962400</v>
       </c>
       <c r="I76" s="3">
-        <v>8067500</v>
+        <v>6840500</v>
       </c>
       <c r="J76" s="3">
+        <v>8201600</v>
+      </c>
+      <c r="K76" s="3">
         <v>5655400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2339100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2065800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3216200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2473200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2401900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2220500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3198700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3969600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3294600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3090900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4627100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4211700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4419100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4567200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4308000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5578500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4964200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4825200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6188300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6657500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6437800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5882600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6758400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6273400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6547800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>238900</v>
-      </c>
-      <c r="E81" s="3">
-        <v>1087100</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-722500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>230500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>77200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1706400</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>3564800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>146500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-105600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>623200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>242400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>205500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-365300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>796400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>458600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>491800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>77400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>191400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-81700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>330100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>432600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>136900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>601600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>270600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>510700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>257600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>666400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-19300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>513900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>348900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>395400</v>
+        <v>385200</v>
       </c>
       <c r="E83" s="3">
-        <v>390900</v>
+        <v>393600</v>
       </c>
       <c r="F83" s="3">
-        <v>396700</v>
+        <v>476400</v>
       </c>
       <c r="G83" s="3">
-        <v>386300</v>
+        <v>-454700</v>
       </c>
       <c r="H83" s="3">
-        <v>396800</v>
+        <v>594700</v>
       </c>
       <c r="I83" s="3">
-        <v>468600</v>
+        <v>663700</v>
       </c>
       <c r="J83" s="3">
+        <v>726200</v>
+      </c>
+      <c r="K83" s="3">
         <v>598300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>609000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>859100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>603300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>700000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>611300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>635000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1267200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>744900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>722500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>842100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>795400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>764600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>756300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>666600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>641700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>437000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>571000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>567700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>597600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>701200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>610700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>662200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>630900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3456500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1136300</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>709600</v>
+        <v>686200</v>
       </c>
       <c r="E89" s="3">
-        <v>810100</v>
+        <v>708100</v>
       </c>
       <c r="F89" s="3">
-        <v>838800</v>
+        <v>795300</v>
       </c>
       <c r="G89" s="3">
-        <v>790500</v>
+        <v>879700</v>
       </c>
       <c r="H89" s="3">
-        <v>535400</v>
+        <v>788100</v>
       </c>
       <c r="I89" s="3">
-        <v>573800</v>
+        <v>531100</v>
       </c>
       <c r="J89" s="3">
+        <v>583400</v>
+      </c>
+      <c r="K89" s="3">
         <v>880800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1026700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>909600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>893000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>801700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1199300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>924400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1017300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1171000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1106800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1246300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1152100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>774300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1405400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>703500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1071600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>926100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1107200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>895600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>880500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1064600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1399400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1343300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1129900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4904600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1293700</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-3094000</v>
+        <v>-260000</v>
       </c>
       <c r="E91" s="3">
-        <v>-3907000</v>
+        <v>-290300</v>
       </c>
       <c r="F91" s="3">
-        <v>-3170000</v>
+        <v>-360700</v>
       </c>
       <c r="G91" s="3">
-        <v>-3191000</v>
+        <v>-312600</v>
       </c>
       <c r="H91" s="3">
-        <v>-3604000</v>
+        <v>-299200</v>
       </c>
       <c r="I91" s="3">
-        <v>-4763000</v>
+        <v>-336200</v>
       </c>
       <c r="J91" s="3">
+        <v>-455400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-9177000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4428000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5665000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4491000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4936000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4134000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-439000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-535400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-504100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1395900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>571200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-610400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>1000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>32500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-101800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-827500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1315200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>484600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-568500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-523100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-449500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-530800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1393000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2925500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-500200</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-291900</v>
+        <v>-271100</v>
       </c>
       <c r="E94" s="3">
-        <v>-172600</v>
+        <v>-291300</v>
       </c>
       <c r="F94" s="3">
-        <v>-1248900</v>
+        <v>-169400</v>
       </c>
       <c r="G94" s="3">
-        <v>-298500</v>
+        <v>-1309600</v>
       </c>
       <c r="H94" s="3">
-        <v>-367400</v>
+        <v>-297600</v>
       </c>
       <c r="I94" s="3">
-        <v>194100</v>
+        <v>-358500</v>
       </c>
       <c r="J94" s="3">
+        <v>-835800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1082500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-289100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-521000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-292700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-469500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-266300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-433500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-443000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>252400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-349300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-562400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-499100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1439700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2515000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-535700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-564800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-906400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1771500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-563600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-511600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>50900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-662400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2602200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,109 +8819,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-651200</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-573100</v>
+        <v>649800</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-651000</v>
+        <v>601000</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+        <v>645800</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>-565900</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-663700</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-526500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-23400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-633100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-623200</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-695500</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-631400</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-741900</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1368800</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-639200</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-606500</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-747500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-30800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1386600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1076900</v>
+        <v>-126900</v>
       </c>
       <c r="E100" s="3">
-        <v>-548800</v>
+        <v>-1074700</v>
       </c>
       <c r="F100" s="3">
-        <v>1385100</v>
+        <v>-538900</v>
       </c>
       <c r="G100" s="3">
-        <v>-1777900</v>
+        <v>1452500</v>
       </c>
       <c r="H100" s="3">
-        <v>629200</v>
+        <v>-765400</v>
       </c>
       <c r="I100" s="3">
-        <v>-380700</v>
+        <v>-383900</v>
       </c>
       <c r="J100" s="3">
+        <v>646200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-368600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-174300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1472900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-255600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-933400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-636000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-726000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-311400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1074200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-653300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-893600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-302200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1248800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-253200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1835400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>209000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1683300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1548700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-652600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-311900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1372300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-107900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1948200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1114300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>503100</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-14600</v>
+        <v>700</v>
       </c>
       <c r="E101" s="3">
-        <v>12400</v>
+        <v>14000</v>
       </c>
       <c r="F101" s="3">
-        <v>1400</v>
+        <v>42100</v>
       </c>
       <c r="G101" s="3">
-        <v>700</v>
+        <v>-25800</v>
       </c>
       <c r="H101" s="3">
-        <v>14100</v>
+        <v>71300</v>
       </c>
       <c r="I101" s="3">
-        <v>41400</v>
+        <v>22300</v>
       </c>
       <c r="J101" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="K101" s="3">
         <v>-23900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>73200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>21000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-13400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>19600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-37400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>20100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-24300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-26100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-37000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-38800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>154000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>10400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>93000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>10700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-29500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>72600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-60200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>15500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>26300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-55000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-70700</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-673800</v>
+        <v>279300</v>
       </c>
       <c r="E102" s="3">
-        <v>101100</v>
+        <v>-672400</v>
       </c>
       <c r="F102" s="3">
-        <v>976500</v>
+        <v>99200</v>
       </c>
       <c r="G102" s="3">
-        <v>-275000</v>
+        <v>1024000</v>
       </c>
       <c r="H102" s="3">
-        <v>-199000</v>
+        <v>-274300</v>
       </c>
       <c r="I102" s="3">
-        <v>428600</v>
+        <v>-197300</v>
       </c>
       <c r="J102" s="3">
+        <v>435900</v>
+      </c>
+      <c r="K102" s="3">
         <v>-594200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>636500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1063300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>331300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-581600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>259600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-215000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>238600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>323100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>67300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-248400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>504800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1900700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1268800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1989000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>700100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1652800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1326600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-211700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-24400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-864300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1083000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-642900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>373700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1133100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1819800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>TELNY</t>
   </si>
@@ -656,155 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -829,86 +832,89 @@
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>1849500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1847400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2659500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2562100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1417100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2515000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2550100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2583900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2483500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3039500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3219500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3236500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3165100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3421100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3112400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3010000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2674300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2820000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2813600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2777400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2247000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3179900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3280600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3402600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>15461200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3853000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -933,86 +939,89 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>458300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>406600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>696700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>680400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>426600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>628700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>647300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>686400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>780400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>702800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>780300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>795900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>785200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>816200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>725100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>700800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>588400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>619800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>662700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>632900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>523300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>725500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>760900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1192600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>5577700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1329500</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1037,86 +1046,89 @@
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>1391200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1440800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1962700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1881600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>990500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1886300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1902900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1897500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1703200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2336700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2439200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2440500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2380000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2605000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2387300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2309300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2085900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2200200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2150900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2144500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1723800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2454400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2519700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2210000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>9883500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2523500</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,86 +1406,89 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>32100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>10500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>259800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>16900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>93600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>16900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>13700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>10300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>15300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>147800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>37000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>37100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>26900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>20700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>268700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>25500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>26600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>18600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>59900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>55600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>718100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-82400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>158900</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>707900</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,86 +1513,89 @@
       <c r="J15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="3">
         <v>410300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>394500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>622000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>603300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>360100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>607100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>603000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>599100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>459400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>722500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>761100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>722000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>756200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>757100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>666800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>637800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>462800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>553400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>529200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>547800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>457600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>556300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>570100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>581900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>2414600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>617700</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,8 +1629,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1630,86 +1656,89 @@
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>1543100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1376400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2368500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1912500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1395100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1956000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2017600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2050200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1679400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2209800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2664400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2547000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2550200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2612300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2398400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2269400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2378100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2132300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2221000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2183200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1893900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2354800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3111300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2705400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>12375000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3663500</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1734,86 +1763,89 @@
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>306400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>471100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>291000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>649600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>22000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>558900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>532500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>533700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>804100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>829700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>555100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>689500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>614900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>808800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>714000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>740600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>296200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>687700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>592500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>594300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>353200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>825100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>169300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>697100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3086200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>189500</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,86 +1909,89 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>90500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-228500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-211300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>15700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-86700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-59500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>19500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>219500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>49700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>120200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-404300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>85200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-202000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>7100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>62800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-258100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>9800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-124000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>233900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-45200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>211800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>102900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>100400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-323500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>90900</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1980,86 +2016,89 @@
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3">
         <v>995100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>851500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>938900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1268700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>712400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1083600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1108000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1820400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1768500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1602000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1517400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1080600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1464700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1363200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1387700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1445100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>516500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1017600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1422600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1009200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1647600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>934400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1428400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>6219100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1416700</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2084,86 +2123,89 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>123300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>43700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>58700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>45200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>48700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>61000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>61600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>60700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>110900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>107400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>85400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>89800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>173900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>135400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>117100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>100900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>104900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>45900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>46200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>30500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>105800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>54700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>72700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>72500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>382700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2188,86 +2230,89 @@
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>273600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>198800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>620100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-36300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>411200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>411400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>492600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>912600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>772100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>589800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>195400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>526300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>471500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>603900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>702600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-66900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>651500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>422300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>797600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>202200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>982200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>199500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>725000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2379900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>210800</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,86 +2337,89 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>-166900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>78100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-36300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>39800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>134300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>138100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>154900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>158700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>217500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>221300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>69100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>147500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>483800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>216100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>203000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>55800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>205700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>125000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>235000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>77200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>272900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>186400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>197900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>730400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,8 +2522,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2500,86 +2551,89 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>440500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>120700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>57400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>720600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-76100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>276900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>273200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>337700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>754000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>554600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>368500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>126300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>378700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>387800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>499600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-122700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>445800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>297300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>562700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>124900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>709300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>13100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>527100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1649500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2604,86 +2658,89 @@
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>399500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>47500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>656000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-142100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>203200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>197800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>266500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>668600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>461100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>266200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>277900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-113600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>302100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>397100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-160200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>370200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>208100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>484100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>46100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>623500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-79500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>441500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1282600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-93500</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2812,86 +2872,89 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="3">
         <v>3165300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>99000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-89500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-32700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>147100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>39200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>7600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-631800</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>127800</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-2500</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>225600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>67900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-86600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>31900</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>28000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>35400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>297100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>231400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>62500</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>26600</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>211500</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>42800</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>60200</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>72400</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-933600</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-501000</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,86 +3193,89 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-90500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>228500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>211300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-15700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>86700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>59500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-19500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-219500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-49700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-120200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>404300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-85200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>202000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-62800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>258100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>124000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-233900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>45200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-211800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-102900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-100400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>323500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-90900</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3228,86 +3300,89 @@
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>3564800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>146500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-105600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>623200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>242400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>205500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-365300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>796400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>458600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>491800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>77400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>191400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-81700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>330100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>432600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>136900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>601600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>270600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>510700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>257600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>666400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-19300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>513900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>348900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,8 +3485,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3436,195 +3514,201 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>3564800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>146500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-105600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>623200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>242400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>205500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-365300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>796400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>458600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>491800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>77400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>191400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-81700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>330100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>432600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>136900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>601600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>270600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>510700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>257600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>666400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-19300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>513900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>348900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,944 +3784,972 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>913700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1582900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1306100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1926200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1928500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>910500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1168300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1371900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>933700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1534600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>892800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1972900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1431900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2018200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1852900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2139500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2131400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1771000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1855300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2006900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1534800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3841300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4899600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1569900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2086300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3345800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1900500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2144100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2610600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3448500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2389300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3222400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2846400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3399800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E42" s="3">
         <v>135700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>245900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>125400</v>
       </c>
-      <c r="G42" s="3">
-        <v>128800</v>
-      </c>
       <c r="H42" s="3">
+        <v>32200</v>
+      </c>
+      <c r="I42" s="3">
         <v>30400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>30300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>31300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>33900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>69500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>57500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>62000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>78900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>93000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>71500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>54300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>59700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>54500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>65400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>93700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>100700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>80600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>97200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>103000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>76500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>93200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>83200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>69000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>187800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>189300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>192000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>297900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>306900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1143800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1343400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1375500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1380000</v>
       </c>
-      <c r="G43" s="3">
-        <v>1356500</v>
-      </c>
       <c r="H43" s="3">
+        <v>1453000</v>
+      </c>
+      <c r="I43" s="3">
         <v>1393300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1453400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1568500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1771900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2146100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2167600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2025600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2044800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2132100</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>2213800</v>
       </c>
       <c r="R43" s="3">
         <v>2213800</v>
       </c>
       <c r="S43" s="3">
+        <v>2213800</v>
+      </c>
+      <c r="T43" s="3">
         <v>2730300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2652100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2945000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3052900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3000200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3410000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2509600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3068800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2537200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2310300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2155700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2118400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2990300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2713200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2991200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3085500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3158100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2854000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>77200</v>
+      </c>
+      <c r="E44" s="3">
         <v>83700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>82000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>94500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>94200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>99800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>116300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>122700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>146600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>174000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>158600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>148200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>147000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>103400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>121500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>149300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>136000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>127100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>142500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>172600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>164400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>163400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>133400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>168100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>192100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>101800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>115000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>149800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>205300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>174100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>200000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>210800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>222200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>175900</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E45" s="3">
         <v>38300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>45400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>56500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>209600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>46400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>47300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>25000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>140200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>141300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>154900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>140900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>421300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>417800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>385700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>143600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>128400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>141200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>187400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>599400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>386200</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3">
         <v>395000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>101800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>439600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2973600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3045100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>197100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>178000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>117900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>438000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2416500</v>
+      </c>
+      <c r="E46" s="3">
         <v>3234800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3103800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3640400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3920600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2565300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2885200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3171000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3026400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4065600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3431500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4349600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4123900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4764600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4645400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4700400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5185700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4746000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5195700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5925500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5186200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7495400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7639800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5304800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4993900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6290700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7227900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7526400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6191100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6703100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5890400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7254600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6533800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6691100</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6343500</v>
+      </c>
+      <c r="E47" s="3">
         <v>6414000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5474200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5489700</v>
       </c>
-      <c r="G47" s="3">
-        <v>5164400</v>
-      </c>
       <c r="H47" s="3">
+        <v>5518400</v>
+      </c>
+      <c r="I47" s="3">
         <v>5724600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5865500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5749600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3732100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>576900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>558400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>532200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>534500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>533300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>565300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>587200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>664700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>826000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>847800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>543800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>475800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>272000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>253700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>486700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>268700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>52000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>53500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>53300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AF47" s="3">
-        <v>51200</v>
       </c>
       <c r="AG47" s="3">
         <v>51200</v>
       </c>
       <c r="AH47" s="3">
+        <v>51200</v>
+      </c>
+      <c r="AI47" s="3">
         <v>1738500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1944800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1690700</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7112000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7471100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7340700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7417400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7639000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7465400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7587900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7683400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10470900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11988200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11906500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11630300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11694700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11352200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11879500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11961800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14727000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>14716600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16542600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>17296600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>15778500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16995100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14544500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16139200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8276600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7060600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7104000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6984200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8748700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8271800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8497000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9027500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8879600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8405100</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3156500</v>
+      </c>
+      <c r="E49" s="3">
         <v>3393000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3271200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3293200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3403300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3227700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3334400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3352000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3481600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3674300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3603500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3422500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3540700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3501700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3610100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3575500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4160700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4237300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4643000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4839800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4296700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5123000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2361900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4394900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5728300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3698000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3864400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4002500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6605500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6627500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>6847600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>6962500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7099100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7250400</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>142300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1233800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1198500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1346200</v>
       </c>
-      <c r="G52" s="3">
-        <v>531600</v>
-      </c>
       <c r="H52" s="3">
+        <v>95800</v>
+      </c>
+      <c r="I52" s="3">
         <v>1612000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1628600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1912600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1788000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1789400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1772500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1564500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1339300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1285100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1453900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1509100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1833200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1877000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2144700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2457300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1810800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2484200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2288400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1852300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2311800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1982900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1485500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1533000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1761500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1790700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2147400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>850000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>981800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>874400</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20140000</v>
+      </c>
+      <c r="E54" s="3">
         <v>22066300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20703500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21577000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21535400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20953700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21761100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22376200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22499000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>22094300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21272400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21499100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21233100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21436900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22154100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22334000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26571300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26402800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>29373700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31063100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>27548100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32369600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>27088300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>28177900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>21579300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>19084400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19735400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>20099400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>23362400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>23444200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>23433600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>25833200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>25439100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>24911800</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>584100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2025300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2059400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2031600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>542500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1946100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2019500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2104300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2654500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2980200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2954800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2927300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3040000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2817800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2822500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2982600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3510400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3344800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3834100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4089800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3950300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4383300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3795600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4040600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4256500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3576100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3484800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3486000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4665800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4258800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4539200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4887000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5288300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4924500</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1337400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2118600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2025300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1380400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1620600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>939500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1613400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1422800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1489900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1679300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1238600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1486400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1528800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1664800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2078100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1462000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1718800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1883200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2466100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2069500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2662500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4165700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3453100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2723400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1775800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1588700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2615700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2051000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2629600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2984700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3083000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>4001300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3202100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3174000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1158800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1292100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1273100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>745100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1299300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1318200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1275000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>830400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>912800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1683400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1622000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1133200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1278700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1728800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1762500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1005200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1041100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1639300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1928100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1480500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1470400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2325000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2159400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1504100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1578100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2654800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2280400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1900000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1583800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2214000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2207700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1558500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1079900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1033600</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4082800</v>
+      </c>
+      <c r="E60" s="3">
         <v>5436000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5357900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4157100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4535400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4203800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4908000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4357500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5057200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6342800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5815400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5546800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5847400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6211400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6663100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5449900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6270300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6867300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8228300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7639800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8083200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10873900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9408000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8268000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7610400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7819600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8380900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7437000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8879100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9457500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>9829900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>10446800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>9570300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>9132100</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7607400</v>
+      </c>
+      <c r="E61" s="3">
         <v>7830100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7509900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8333300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8765700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8055600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8287200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7990300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10075500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11255800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11328000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10733700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10902700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10874900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11236200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11596800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13901600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13888300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15270500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15872400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>12837700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14534900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>11137800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13131100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6309600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4548900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4739300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4852400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5973300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5762600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5949300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6540000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7446200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7214000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>729100</v>
+      </c>
+      <c r="E62" s="3">
         <v>723500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>714600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>724400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>775600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>714300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>724700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>799100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1312400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1686600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1562100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1481200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1520100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1510500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1560100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1579800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1850400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1790500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2093100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2227800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1830500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1962200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1408000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1872300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1515700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1260900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1244500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1065200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1292200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1284700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1223900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1479700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1592300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1503800</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12942300</v>
+      </c>
+      <c r="E66" s="3">
         <v>14468700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14040700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13703200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14589500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13445800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14395700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13641900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16843600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19755200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19206700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18282800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18759900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19035000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19933600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19135300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>22601700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23108300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>26282800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26436000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23336400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>27950500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22521100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23869900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16000800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14120200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14910200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13911100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16704900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17006400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17551000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>19074800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>19165800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>18363900</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7871800</v>
+      </c>
+      <c r="E72" s="3">
         <v>8400900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7993300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8839200</v>
       </c>
-      <c r="G72" s="3">
-        <v>8292600</v>
-      </c>
       <c r="H72" s="3">
+        <v>8301100</v>
+      </c>
+      <c r="I72" s="3">
         <v>8613400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8340700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9713600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5180800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1730200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1549800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2847700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2111700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2030300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1803800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2791900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3421800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2516200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2252700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3551600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3562800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3647400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3964700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5195400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4828000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4471800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4521900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5777800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6005900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5929300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5278900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5612000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5136300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5466800</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6676900</v>
+      </c>
+      <c r="E76" s="3">
         <v>7081800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6088800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7259700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6359100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6962400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6840500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8201600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5655400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2339100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2065800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3216200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2473200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2401900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2220500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3198700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3969600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3294600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3090900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4627100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4211700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4419100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4567200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4308000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5578500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4964200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4825200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6188300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6657500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6437800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5882600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6758400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6273400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6547800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,117 +7537,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7484,86 +7678,89 @@
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>3564800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>146500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-105600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>623200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>242400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>205500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-365300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>796400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>458600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>491800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>77400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>191400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-81700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>330100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>432600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>136900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>601600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>270600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>510700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>257600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>666400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-19300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>513900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>348900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E83" s="3">
         <v>385200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>393600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>476400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-454700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>594700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>663700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>726200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>598300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>609000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>859100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>603300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>700000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>611300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>635000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1267200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>744900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>722500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>842100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>795400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>764600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>756300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>666600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>641700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>437000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>571000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>567700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>597600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>701200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>610700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>662200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>630900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>3456500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1136300</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>712600</v>
+      </c>
+      <c r="E89" s="3">
         <v>686200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>708100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>795300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>879700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>788100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>531100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>583400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>880800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1026700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>909600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>893000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>801700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1199300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>924400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1017300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1171000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1106800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1246300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1152100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>774300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1405400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>703500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1071600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>926100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1107200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>895600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>880500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1064600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1399400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1343300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1129900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4904600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1293700</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-320800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-260000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-290300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-360700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-312600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-299200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-336200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-455400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9177000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4428000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5665000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4491000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4936000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4134000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-439000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-535400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-504100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1395900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>571200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-610400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>1000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>32500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-101800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-827500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1315200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>484600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-568500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-523100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-449500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-530800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1393000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2925500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-500200</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-324900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-271100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-291300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-169400</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1309600</v>
-      </c>
       <c r="H94" s="3">
+        <v>-250200</v>
+      </c>
+      <c r="I94" s="3">
         <v>-297600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-358500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-835800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1082500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-289100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-521000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-292700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-469500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-266300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-433500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-443000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>252400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-349300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-562400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-499100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1439700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2515000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-535700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-564800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-906400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1771500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-563600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-511600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>50900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-662400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2602200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,112 +9052,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>541900</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>649800</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
         <v>601000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>645800</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>-565900</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-663700</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-526500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-633100</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-623200</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-695500</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-631400</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-741900</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1368800</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-639200</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-606500</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-747500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-30800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1386600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-947700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-126900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1074700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-538900</v>
       </c>
-      <c r="G100" s="3">
-        <v>1452500</v>
-      </c>
       <c r="H100" s="3">
+        <v>393000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-765400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-383900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>646200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-368600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-174300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1472900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-255600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-933400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-636000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-726000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-311400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1074200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-653300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-893600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-302200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1248800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-253200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1835400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>209000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1683300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1548700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-652600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-311900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1372300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-107900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1948200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1114300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>503100</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>14000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>42100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-25800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>71300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>22300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-16100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-23900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>73200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>21000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-13400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>19600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-37400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>20100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-24300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-26100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-37000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-38800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>154000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>10400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>93000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-22000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>10700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-29500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>72600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-60200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>15500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>26300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-55000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-70700</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-556600</v>
+      </c>
+      <c r="E102" s="3">
         <v>279300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-672400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>99200</v>
       </c>
-      <c r="G102" s="3">
-        <v>1024000</v>
-      </c>
       <c r="H102" s="3">
+        <v>1023900</v>
+      </c>
+      <c r="I102" s="3">
         <v>-274300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-197300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>435900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-594200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>636500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1063300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>331300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-581600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>259600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-215000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>238600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>323100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>67300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-248400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>504800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1900700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1268800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1989000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>700100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1652800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1326600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-211700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-24400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-864300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1083000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-642900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>373700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1133100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1819800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>TELNY</t>
   </si>
@@ -656,158 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -835,86 +839,89 @@
       <c r="K8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>1849500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1847400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2659500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2562100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1417100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2515000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2550100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2583900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2483500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3039500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3219500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3236500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3165100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3421100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3112400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3010000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2674300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2820000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2813600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2777400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2247000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3179900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3280600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3402600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>15461200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3853000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -942,86 +949,89 @@
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>458300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>406600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>696700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>680400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>426600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>628700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>647300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>686400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>780400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>702800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>780300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>795900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>785200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>816200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>725100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>700800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>588400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>619800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>662700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>632900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>523300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>725500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>760900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1192600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>5577700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1329500</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1049,86 +1059,89 @@
       <c r="K10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>1391200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1440800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1962700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1881600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>990500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1886300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1902900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1897500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1703200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2336700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2439200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2440500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2380000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2605000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2387300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2309300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2085900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2200200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2150900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2144500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1723800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2454400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2519700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2210000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>9883500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2523500</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,86 +1429,89 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>32100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>10500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>259800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>16900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>93600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>16900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>13700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>10300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>15300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>10900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>147800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>37000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>37100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>26900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>20700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>268700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>25500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>26600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>18600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>59900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>55600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>718100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-82400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>158900</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>707900</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1516,86 +1539,89 @@
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="3">
         <v>410300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>394500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>622000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>603300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>360100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>607100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>603000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>599100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>459400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>722500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>761100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>722000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>756200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>757100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>666800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>637800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>462800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>553400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>529200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>547800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>457600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>556300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>570100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>581900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>2414600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>617700</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,8 +1656,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1659,86 +1686,89 @@
       <c r="K17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>1543100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1376400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2368500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1912500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1395100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1956000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2017600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2050200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1679400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2209800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2664400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2547000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2550200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2612300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2398400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2269400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2378100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2132300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2221000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2183200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1893900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2354800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3111300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2705400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>12375000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3663500</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1766,86 +1796,89 @@
       <c r="K18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>306400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>471100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>291000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>649600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>22000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>558900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>532500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>533700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>804100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>829700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>555100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>689500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>614900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>808800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>714000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>740600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>296200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>687700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>592500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>594300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>353200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>825100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>169300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>697100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3086200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>189500</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1912,86 +1946,89 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>90500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-228500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-211300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>15700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-86700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-59500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>19500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>219500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>49700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>120200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-404300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>85200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-202000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>62800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-258100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>9800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-124000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>233900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-45200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>211800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>102900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>100400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-323500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>90900</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2019,86 +2056,89 @@
       <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>995100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>851500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>938900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1268700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>712400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1083600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1108000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1820400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1768500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1602000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1517400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1080600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1464700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1363200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1387700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1445100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>516500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1017600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1422600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1009200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1647600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>934400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1428400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>6219100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1416700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2126,86 +2166,89 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>123300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>43700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>58700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>45200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>48700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>61000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>61600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>60700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>110900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>107400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>85400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>89800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>173900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>135400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>117100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>100900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>104900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>45900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>46200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>30500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>105800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>54700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>72700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>72500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>382700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2233,86 +2276,89 @@
       <c r="K23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>273600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>198800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>620100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-36300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>411200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>411400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>492600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>912600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>772100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>589800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>195400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>526300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>471500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>603900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>702600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-66900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>651500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>422300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>797600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>202200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>982200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>199500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>725000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2379900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>210800</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2340,86 +2386,89 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>-166900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>78100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-36300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>39800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>134300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>138100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>154900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>158700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>217500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>221300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>69100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>147500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>483800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>216100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>203000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>55800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>205700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>125000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>235000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>77200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>272900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>186400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>197900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>730400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,8 +2574,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2554,86 +2606,89 @@
       <c r="K26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>440500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>120700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>57400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>720600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-76100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>276900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>273200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>337700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>754000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>554600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>368500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>126300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>378700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-12400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>387800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>499600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-122700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>445800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>297300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>562700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>124900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>709300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>13100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>527100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1649500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2661,86 +2716,89 @@
       <c r="K27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>399500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>47500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>656000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-142100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>203200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>197800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>266500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>668600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>461100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>266200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>9600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>277900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-113600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>302100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>397100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-160200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>370200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>208100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>484100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>46100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>623500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-79500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>441500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1282600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-93500</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2875,86 +2936,89 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="3">
         <v>3165300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>99000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-89500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-32700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>147100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>39200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>7600</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-631800</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>127800</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-2500</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>225600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>67900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-86600</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>31900</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>28000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>35400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>297100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>231400</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>62500</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>26600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>211500</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>42800</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>60200</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>72400</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-933600</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-501000</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3196,86 +3266,89 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-90500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>228500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>211300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-15700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>86700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>59500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-19500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-219500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-49700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-120200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>404300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-85200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>202000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-62800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>258100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>124000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-233900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>45200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-211800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-102900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-100400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>323500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-90900</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3303,86 +3376,89 @@
       <c r="K33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>3564800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>146500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-105600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>623200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>242400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>205500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-365300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>796400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>458600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>491800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>77400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>191400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-81700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>330100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>432600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>136900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>601600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>270600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>510700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>257600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>666400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-19300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>513900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>348900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,8 +3564,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3517,198 +3596,204 @@
       <c r="K35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>3564800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>146500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-105600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>623200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>242400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>205500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-365300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>796400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>458600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>491800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>77400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>191400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-81700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>330100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>432600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>136900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>601600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>270600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>510700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>257600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>666400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-19300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>513900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>348900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,971 +3871,999 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>921700</v>
+      </c>
+      <c r="E41" s="3">
         <v>913700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1582900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1306100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1926200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1928500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>910500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1168300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1371900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>933700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1534600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>892800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1972900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1431900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2018200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1852900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2139500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2131400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1771000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1855300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2006900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1534800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3841300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4899600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1569900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2086300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3345800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1900500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2144100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2610600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3448500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2389300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3222400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2846400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3399800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>118900</v>
+      </c>
+      <c r="E42" s="3">
         <v>35300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>135700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>245900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>125400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>32200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>30400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>30300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>31300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>33900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>69500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>57500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>62000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>78900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>93000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>71500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>54300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>59700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>54500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>65400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>93700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>100700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>80600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>97200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>103000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>76500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>93200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>83200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>69000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>187800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>189300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>192000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>297900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>306900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1277300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1143800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1343400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1375500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1380000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1453000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1393300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1453400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1568500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1771900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2146100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2167600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2025600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2044800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2132100</v>
-      </c>
-      <c r="R43" s="3">
-        <v>2213800</v>
       </c>
       <c r="S43" s="3">
         <v>2213800</v>
       </c>
       <c r="T43" s="3">
+        <v>2213800</v>
+      </c>
+      <c r="U43" s="3">
         <v>2730300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2652100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2945000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3052900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3000200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3410000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2509600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3068800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2537200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2310300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2155700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2118400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2990300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2713200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2991200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3085500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3158100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2854000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E44" s="3">
         <v>77200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>83700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>82000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>94500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>94200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>99800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>116300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>122700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>146600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>174000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>158600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>148200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>147000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>103400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>121500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>149300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>136000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>127100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>142500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>172600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>164400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>163400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>133400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>168100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>192100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>101800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>115000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>149800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>205300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>174100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>200000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>210800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>222200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>175900</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E45" s="3">
         <v>23500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>38300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>45400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>56500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>209600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>46400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>47300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>140200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>141300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>154900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>140900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>421300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>417800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>385700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>143600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>128400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>141200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>187400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>599400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>386200</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB45" s="3">
         <v>395000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>101800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>439600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2973600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3045100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>197100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>178000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>117900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>438000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2503000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2416500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3234800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3103800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3640400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3920600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2565300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2885200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3171000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3026400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4065600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3431500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4349600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4123900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4764600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4645400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4700400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5185700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4746000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5195700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5925500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5186200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7495400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7639800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5304800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4993900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6290700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7227900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7526400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6191100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6703100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5890400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7254600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6533800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6691100</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5951400</v>
+      </c>
+      <c r="E47" s="3">
         <v>6343500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6414000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5474200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5489700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5518400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5724600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5865500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5749600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3732100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>576900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>558400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>532200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>534500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>533300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>565300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>587200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>664700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>826000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>847800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>543800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>475800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>272000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>253700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>486700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>268700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>52000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>53500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>53300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AG47" s="3">
-        <v>51200</v>
       </c>
       <c r="AH47" s="3">
         <v>51200</v>
       </c>
       <c r="AI47" s="3">
+        <v>51200</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>1738500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1944800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1690700</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7445300</v>
+      </c>
+      <c r="E48" s="3">
         <v>7112000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7471100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7340700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7417400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7639000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7465400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7587900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7683400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10470900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11988200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11906500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11630300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11694700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11352200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11879500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11961800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>14727000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14716600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16542600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>17296600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>15778500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16995100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14544500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16139200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8276600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7060600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7104000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6984200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8748700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8271800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8497000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9027500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8879600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8405100</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3333200</v>
+      </c>
+      <c r="E49" s="3">
         <v>3156500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3393000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3271200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3293200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3403300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3227700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3334400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3352000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3481600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3674300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3603500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3422500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3540700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3501700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3610100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3575500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4160700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4237300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4643000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4839800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4296700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5123000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2361900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4394900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5728300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3698000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3864400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4002500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6605500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>6627500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>6847600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>6962500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7099100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7250400</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1220300</v>
+      </c>
+      <c r="E52" s="3">
         <v>142300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1233800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1198500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1346200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>95800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1612000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1628600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1912600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1788000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1789400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1772500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1564500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1339300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1285100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1453900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1509100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1833200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1877000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2144700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2457300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1810800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2484200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2288400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1852300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2311800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1982900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1485500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1533000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1761500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1790700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2147400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>850000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>981800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>874400</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20864300</v>
+      </c>
+      <c r="E54" s="3">
         <v>20140000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22066300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20703500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21577000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21535400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20953700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21761100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22376200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>22499000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>22094300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21272400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21499100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21233100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21436900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22154100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>22334000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26571300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>26402800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>29373700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>31063100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>27548100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>32369600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>27088300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28177900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>21579300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19084400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>19735400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>20099400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>23362400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>23444200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>23433600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>25833200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>25439100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>24911800</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2109600</v>
+      </c>
+      <c r="E57" s="3">
         <v>584100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2025300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2059400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2031600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>542500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1946100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2019500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2104300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2654500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2980200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2954800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2927300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3040000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2817800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2822500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2982600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3510400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3344800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3834100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4089800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3950300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4383300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3795600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4040600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4256500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3576100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3484800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3486000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4665800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4258800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4539200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4887000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>5288300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4924500</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1073800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1337400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2118600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2025300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1380400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1620600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>939500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1613400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1422800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1489900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1679300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1238600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1486400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1528800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1664800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2078100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1462000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1718800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1883200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2466100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2069500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2662500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4165700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3453100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2723400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1775800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1588700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2615700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2051000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2629600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2984700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3083000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4001300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3202100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3174000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>824000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1158800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1292100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1273100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>745100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1299300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1318200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1275000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>830400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>912800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1683400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1622000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1133200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1278700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1728800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1762500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1005200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1041100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1639300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1928100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1480500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1470400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2325000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2159400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1504100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1578100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2654800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2280400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1900000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1583800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2214000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2207700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1558500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1079900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1033600</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4007400</v>
+      </c>
+      <c r="E60" s="3">
         <v>4082800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5436000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5357900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4157100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4535400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4203800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4908000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4357500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5057200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6342800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5815400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5546800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5847400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6211400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6663100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5449900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6270300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6867300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8228300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7639800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8083200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10873900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9408000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8268000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7610400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7819600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8380900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7437000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8879100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>9457500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>9829900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>10446800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>9570300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>9132100</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7975200</v>
+      </c>
+      <c r="E61" s="3">
         <v>7607400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7830100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7509900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8333300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8765700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8055600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8287200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7990300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10075500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11255800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11328000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10733700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10902700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10874900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11236200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11596800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13901600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13888300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15270500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15872400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>12837700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14534900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>11137800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>13131100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6309600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4548900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4739300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4852400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5973300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5762600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5949300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6540000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7446200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7214000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>775000</v>
+      </c>
+      <c r="E62" s="3">
         <v>729100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>723500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>714600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>724400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>775600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>714300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>724700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>799100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1312400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1686600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1562100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1481200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1520100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1510500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1560100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1579800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1850400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1790500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2093100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2227800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1830500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1962200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1408000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1872300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1515700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1260900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1244500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1065200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1292200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1284700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1223900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1479700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1592300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1503800</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13293400</v>
+      </c>
+      <c r="E66" s="3">
         <v>12942300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14468700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14040700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13703200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14589500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13445800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14395700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13641900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16843600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19755200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19206700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18282800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18759900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19035000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19933600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19135300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>22601700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23108300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26282800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26436000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23336400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>27950500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22521100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23869900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16000800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14120200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14910200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13911100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>16704900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17006400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>17551000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>19074800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>19165800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>18363900</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8709200</v>
+      </c>
+      <c r="E72" s="3">
         <v>7871800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8400900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7993300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8839200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8301100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8613400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8340700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9713600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5180800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1730200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1549800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2847700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2111700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2030300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1803800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2791900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3421800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2516200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2252700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3551600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3562800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3647400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3964700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5195400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4828000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4471800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4521900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5777800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6005900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5929300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5278900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5612000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5136300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5466800</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7017800</v>
+      </c>
+      <c r="E76" s="3">
         <v>6676900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7081800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6088800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7259700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6359100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6962400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6840500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8201600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5655400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2339100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2065800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3216200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2473200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2401900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2220500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3198700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3969600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3294600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3090900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4627100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4211700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4419100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4567200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4308000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5578500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4964200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4825200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6188300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6657500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6437800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5882600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6758400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6273400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6547800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,120 +7729,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7681,86 +7876,89 @@
       <c r="K81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>3564800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>146500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-105600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>623200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>242400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>205500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-365300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>796400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>458600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>491800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>77400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>191400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-81700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>330100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>432600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>136900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>601600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>270600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>510700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>257600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>666400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-19300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>513900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>348900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>383700</v>
+      </c>
+      <c r="E83" s="3">
         <v>43800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>385200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>393600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>476400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-454700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>594700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>663700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>726200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>598300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>609000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>859100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>603300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>700000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>611300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>635000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1267200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>744900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>722500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>842100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>795400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>764600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>756300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>666600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>641700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>437000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>571000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>567700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>597600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>701200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>610700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>662200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>630900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>3456500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1136300</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>724500</v>
+      </c>
+      <c r="E89" s="3">
         <v>712600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>686200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>708100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>795300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>879700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>788100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>531100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>583400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>880800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1026700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>909600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>893000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>801700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1199300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>924400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1017300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1171000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1106800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1246300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1152100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>774300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1405400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>703500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1071600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>926100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1107200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>895600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>880500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1064600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1399400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1343300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1129900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>4904600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1293700</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-286000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-320800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-260000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-290300</v>
       </c>
-      <c r="G91" s="3">
-        <v>-360700</v>
-      </c>
       <c r="H91" s="3">
+        <v>-352800</v>
+      </c>
+      <c r="I91" s="3">
         <v>-312600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-299200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-336200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-455400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9177000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4428000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5665000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4491000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4936000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4134000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-439000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-535400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-504100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1395900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>571200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-610400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>1000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>32500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-101800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-827500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1315200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>484600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-568500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-523100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-449500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-530800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1393000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2925500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-500200</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-289100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-324900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-271100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-291300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-169400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-250200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-297600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-358500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-835800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1082500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-289100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-521000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-292700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-469500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-266300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-433500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-443000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>252400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-349300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-562400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-499100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1439700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2515000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-535700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-564800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-906400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1771500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-563600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-511600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>50900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-662400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2602200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,115 +9286,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
         <v>541900</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>649800</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
         <v>601000</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>645800</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>-565900</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-663700</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-526500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-23400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-633100</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-623200</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-695500</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-631400</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-741900</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1368800</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-639200</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-606500</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-747500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-30800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1386600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-495100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-947700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-126900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1074700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-538900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>393000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-765400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-383900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>646200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-368600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-174300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1472900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-255600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-933400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-636000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-726000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-311400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1074200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-653300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-893600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-302200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1248800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-253200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1835400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>209000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1683300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1548700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-652600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-311900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1372300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-107900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1948200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1114300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>503100</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E101" s="3">
         <v>1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>14000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>42100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-25800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>71300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>22300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-16100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-23900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>73200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>21000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-13400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>19600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-37400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>20100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-24300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-26100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-37000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-38800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>154000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>10400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>93000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>10700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-29500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>72600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-60200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>15500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>26300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-55000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-70700</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-59800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-556600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>279300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-672400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>99200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1023900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-274300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-197300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>435900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-594200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>636500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1063300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>331300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-581600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>259600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-215000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>238600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>323100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>67300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-248400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>504800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1900700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1268800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1989000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>700100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1652800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1326600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-211700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-24400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-864300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1083000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-642900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>373700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1133100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1819800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
   <si>
     <t>TELNY</t>
   </si>
@@ -656,162 +656,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -842,86 +846,89 @@
       <c r="L8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>1849500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1847400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2659500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2562100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1417100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2515000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2550100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2583900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2483500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3039500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3219500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3236500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3165100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3421100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3112400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3010000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2674300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2820000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2813600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2777400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2247000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3179900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3280600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3402600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>15461200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3853000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -952,86 +959,89 @@
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>458300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>406600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>696700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>680400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>426600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>628700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>647300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>686400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>780400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>702800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>780300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>795900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>785200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>816200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>725100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>700800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>588400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>619800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>662700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>632900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>523300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>725500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>760900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1192600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>5577700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1329500</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1062,86 +1072,89 @@
       <c r="L10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>1391200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1440800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1962700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1881600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>990500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1886300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1902900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1897500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1703200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2336700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2439200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2440500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2380000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2605000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2387300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2309300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2085900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2200200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2150900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2144500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1723800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2454400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2519700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2210000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>9883500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2523500</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,86 +1452,89 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>32100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>10500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>259800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>16900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>93600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>16900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>13700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>15300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>10900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>147800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>37000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>37100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>26900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>20700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>268700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>25500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>26600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>18600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>59900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>55600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>718100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-82400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>158900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>707900</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1542,86 +1565,89 @@
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="3">
         <v>410300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>394500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>622000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>603300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>360100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>607100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>603000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>599100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>459400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>722500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>761100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>722000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>756200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>757100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>666800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>637800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>462800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>553400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>529200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>547800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>457600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>556300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>570100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>581900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>2414600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>617700</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,8 +1683,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1689,86 +1716,89 @@
       <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>1543100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1376400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2368500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1912500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1395100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1956000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2017600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2050200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1679400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2209800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2664400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2547000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2550200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2612300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2398400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2269400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2378100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2132300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2221000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2183200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1893900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2354800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3111300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2705400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>12375000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3663500</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1799,86 +1829,89 @@
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>306400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>471100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>291000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>649600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>22000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>558900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>532500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>533700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>804100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>829700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>555100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>689500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>614900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>808800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>714000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>740600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>296200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>687700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>592500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>594300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>353200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>825100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>169300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>697100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3086200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>189500</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1949,86 +1983,89 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>90500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-228500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-211300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>15700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-86700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-59500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>19500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>219500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>49700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>120200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-404300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>85200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-202000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>62800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-258100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>9800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-124000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>233900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-45200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>211800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>102900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>100400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-323500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>90900</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2059,86 +2096,89 @@
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>995100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>851500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>938900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1268700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>712400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1083600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1108000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1820400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1768500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1602000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1517400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1080600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1464700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1363200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1387700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1445100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>516500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1017600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1422600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1009200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1647600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>934400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1428400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>6219100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1416700</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2169,86 +2209,89 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>123300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>43700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>58700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>45200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>48700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>61000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>61600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>60700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>110900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>107400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>85400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>89800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>173900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>135400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>117100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>100900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>104900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>45900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>46200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>30500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>105800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>54700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>72700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>72500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>382700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2279,86 +2322,89 @@
       <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>273600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>198800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>21100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>620100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-36300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>411200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>411400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>492600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>912600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>772100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>589800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>195400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>526300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>471500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>603900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>702600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-66900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>651500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>422300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>797600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>202200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>982200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>199500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>725000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2379900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>210800</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2389,86 +2435,89 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>-166900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>78100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-36300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>39800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>134300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>138100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>154900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>158700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>217500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>221300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>69100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>147500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>483800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>216100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>203000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>55800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>205700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>125000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>235000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>77200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>272900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>186400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>197900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>730400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,8 +2626,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2609,86 +2661,89 @@
       <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>440500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>120700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>57400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>720600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-76100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>276900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>273200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>337700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>754000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>554600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>368500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>126300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>378700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-12400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>387800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>499600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-122700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>445800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>297300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>562700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>124900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>709300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>13100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>527100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1649500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2719,86 +2774,89 @@
       <c r="L27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>399500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>47500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-16100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>656000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-142100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>203200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>197800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>266500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>668600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>461100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>266200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>9600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>277900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-113600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>302100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>397100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-160200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>370200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>208100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>484100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>46100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>623500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-79500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>441500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1282600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-93500</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2939,86 +3000,89 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="3">
         <v>3165300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>99000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-89500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-32700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>147100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>39200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>7600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-631800</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>127800</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-2500</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>225600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>67900</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-86600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>31900</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>28000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>35400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>297100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>231400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>62500</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>26600</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>211500</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>42800</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>60200</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>72400</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-933600</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-501000</v>
       </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3269,86 +3339,89 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>-90500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>228500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>211300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>86700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>59500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-19500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-219500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-49700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-120200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>404300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-85200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>202000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-62800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>258100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>124000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-233900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>45200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-211800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-102900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-100400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>323500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-90900</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3379,86 +3452,89 @@
       <c r="L33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>3564800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>146500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-105600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>623200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>242400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>205500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-365300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>796400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>458600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>491800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>77400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>191400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-81700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>330100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>432600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>136900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>601600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>270600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>510700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>257600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>666400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-19300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>513900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>348900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,8 +3643,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3599,201 +3678,207 @@
       <c r="L35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>3564800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>146500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-105600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>623200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>242400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>205500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-365300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>796400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>458600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>491800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>77400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>191400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-81700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>330100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>432600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>136900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>601600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>270600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>510700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>257600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>666400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-19300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>513900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>348900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,998 +3958,1026 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>614900</v>
+      </c>
+      <c r="E41" s="3">
         <v>921700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>913700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1582900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1306100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1926200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1928500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>910500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1168300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1371900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>933700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1534600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>892800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1972900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1431900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2018200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1852900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2139500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2131400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1771000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1855300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2006900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1534800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3841300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4899600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1569900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2086300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3345800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1900500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2144100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2610600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3448500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2389300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3222400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2846400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3399800</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>118900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>35300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>135700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>245900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>125400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>32200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>30400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>30300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>31300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>33900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>69500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>57500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>62000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>78900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>93000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>71500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>54300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>59700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>54500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>65400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>93700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>100700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>80600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>97200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>103000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>76500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>93200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>83200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>69000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>187800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>189300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>192000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>297900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>306900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1354900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1277300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1143800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1343400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1375500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1380000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1453000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1393300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1453400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1568500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1771900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2146100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2167600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2025600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2044800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2132100</v>
-      </c>
-      <c r="S43" s="3">
-        <v>2213800</v>
       </c>
       <c r="T43" s="3">
         <v>2213800</v>
       </c>
       <c r="U43" s="3">
+        <v>2213800</v>
+      </c>
+      <c r="V43" s="3">
         <v>2730300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2652100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2945000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3052900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3000200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3410000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2509600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3068800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2537200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2310300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2155700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2118400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2990300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2713200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2991200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3085500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3158100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2854000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E44" s="3">
         <v>83400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>77200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>83700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>82000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>94500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>94200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>99800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>116300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>122700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>146600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>174000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>158600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>148200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>147000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>103400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>121500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>149300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>136000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>127100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>142500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>172600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>164400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>163400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>133400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>168100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>192100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>101800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>115000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>149800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>205300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>174100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>200000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>210800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>222200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>175900</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>122100</v>
+      </c>
+      <c r="E45" s="3">
         <v>20200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>38300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>45400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>56500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>209600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>46400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>47300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>140200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>141300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>154900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>140900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>421300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>417800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>385700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>143600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>128400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>141200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>187400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>599400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>386200</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3">
         <v>395000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>101800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>439600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2973600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3045100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>197100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>178000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>117900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>438000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2285800</v>
+      </c>
+      <c r="E46" s="3">
         <v>2503000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2416500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3234800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3103800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3640400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3920600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2565300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2885200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3171000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3026400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4065600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3431500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4349600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4123900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4764600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4645400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4700400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5185700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4746000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5195700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5925500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5186200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7495400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7639800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5304800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4993900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6290700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7227900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7526400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6191100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6703100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5890400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7254600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6533800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6691100</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6516500</v>
+      </c>
+      <c r="E47" s="3">
         <v>5951400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6343500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6414000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5474200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5489700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5518400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5724600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5865500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5749600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3732100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>576900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>558400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>532200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>534500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>533300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>565300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>587200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>664700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>826000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>847800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>543800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>475800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>272000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>253700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>486700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>268700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>52000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>53500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>53300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AH47" s="3">
-        <v>51200</v>
       </c>
       <c r="AI47" s="3">
         <v>51200</v>
       </c>
       <c r="AJ47" s="3">
+        <v>51200</v>
+      </c>
+      <c r="AK47" s="3">
         <v>1738500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1944800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1690700</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7700800</v>
+      </c>
+      <c r="E48" s="3">
         <v>7445300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7112000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7471100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7340700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7417400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7639000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7465400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7587900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7683400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10470900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11988200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11906500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11630300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11694700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11352200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11879500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11961800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14727000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14716600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16542600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>17296600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>15778500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16995100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>14544500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>16139200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8276600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7060600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7104000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6984200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8748700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8271800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8497000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9027500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8879600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8405100</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3578200</v>
+      </c>
+      <c r="E49" s="3">
         <v>3333200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3156500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3393000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3271200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3293200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3403300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3227700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3334400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3352000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3481600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3674300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3603500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3422500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3540700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3501700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3610100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3575500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4160700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4237300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4643000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4839800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4296700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5123000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2361900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4394900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5728300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3698000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3864400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4002500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>6605500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>6627500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>6847600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>6962500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7099100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>7250400</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1181900</v>
+      </c>
+      <c r="E52" s="3">
         <v>1220300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>142300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1233800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1198500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1346200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>95800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1612000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1628600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1912600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1788000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1789400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1772500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1564500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1339300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1285100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1453900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1509100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1833200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1877000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2144700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2457300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1810800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2484200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2288400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1852300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2311800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1982900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1485500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1533000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1761500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1790700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2147400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>850000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>981800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>874400</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21680900</v>
+      </c>
+      <c r="E54" s="3">
         <v>20864300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20140000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22066300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20703500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21577000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21535400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20953700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21761100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>22376200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>22499000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22094300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21272400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21499100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21233100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>21436900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>22154100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22334000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>26571300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>26402800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>29373700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>31063100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>27548100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>32369600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>27088300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28177900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>21579300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>19084400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>19735400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>20099400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>23362400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>23444200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>23433600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>25833200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>25439100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>24911800</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2114900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2109600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>584100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2025300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2059400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2031600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>542500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1946100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2019500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2104300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2654500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2980200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2954800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2927300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3040000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2817800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2822500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2982600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3510400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3344800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3834100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4089800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3950300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4383300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3795600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4040600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4256500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3576100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3484800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3486000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4665800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4258800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4539200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4887000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>5288300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4924500</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1670800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1073800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1337400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2118600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2025300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1380400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1620600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>939500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1613400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1422800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1489900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1679300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1238600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1486400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1528800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1664800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2078100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1462000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1718800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1883200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2466100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2069500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2662500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4165700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3453100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2723400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1775800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1588700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2615700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2051000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2629600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2984700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3083000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>4001300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3202100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3174000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1412700</v>
+      </c>
+      <c r="E59" s="3">
         <v>824000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1158800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1292100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1273100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>745100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1299300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1318200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1275000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>830400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>912800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1683400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1622000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1133200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1278700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1728800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1762500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1005200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1041100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1639300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1928100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1480500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1470400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2325000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2159400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1504100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1578100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2654800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2280400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1900000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1583800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2214000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2207700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1558500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1079900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1033600</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5198400</v>
+      </c>
+      <c r="E60" s="3">
         <v>4007400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4082800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5436000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5357900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4157100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4535400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4203800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4908000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4357500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5057200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6342800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5815400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5546800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5847400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6211400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6663100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5449900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6270300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6867300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8228300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7639800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8083200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10873900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9408000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8268000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7610400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7819600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8380900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7437000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8879100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>9457500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>9829900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>10446800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>9570300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>9132100</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8217800</v>
+      </c>
+      <c r="E61" s="3">
         <v>7975200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7607400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7830100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7509900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8333300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8765700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8055600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8287200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7990300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10075500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11255800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11328000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10733700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10902700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10874900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11236200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11596800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13901600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13888300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15270500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>15872400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>12837700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14534900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>11137800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>13131100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6309600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4548900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4739300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4852400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5973300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5762600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5949300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6540000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7446200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7214000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>776400</v>
+      </c>
+      <c r="E62" s="3">
         <v>775000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>729100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>723500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>714600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>724400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>775600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>714300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>724700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>799100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1312400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1686600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1562100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1481200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1520100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1510500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1560100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1579800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1850400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1790500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2093100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2227800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1830500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1962200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1408000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1872300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1515700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1260900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1244500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1065200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1292200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1284700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1223900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1479700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1592300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1503800</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14778100</v>
+      </c>
+      <c r="E66" s="3">
         <v>13293400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12942300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14468700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14040700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13703200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14589500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13445800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14395700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13641900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16843600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19755200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19206700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18282800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18759900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19035000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19933600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19135300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>22601700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23108300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26282800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26436000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23336400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>27950500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>22521100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23869900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16000800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14120200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14910200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13911100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16704900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>17006400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>17551000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>19074800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>19165800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>18363900</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8126500</v>
+      </c>
+      <c r="E72" s="3">
         <v>8709200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7871800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8400900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7993300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8839200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8301100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8613400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8340700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9713600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5180800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1730200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1549800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2847700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2111700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2030300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1803800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2791900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3421800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2516200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2252700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3551600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3562800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3647400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3964700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5195400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4828000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4471800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4521900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5777800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6005900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5929300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5278900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5612000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5136300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5466800</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6383000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7017800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6676900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7081800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6088800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7259700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6359100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6962400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6840500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8201600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5655400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2339100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2065800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3216200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2473200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2401900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2220500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3198700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3969600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3294600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3090900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4627100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4211700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4419100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4567200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4308000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5578500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4964200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4825200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6188300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6657500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6437800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5882600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6758400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6273400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6547800</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,123 +7921,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7879,86 +8074,89 @@
       <c r="L81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>3564800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>146500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-105600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>623200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>242400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>205500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-365300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>796400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>458600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>491800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>77400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>191400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-81700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>330100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>432600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>136900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>601600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>270600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>510700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>257600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>666400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-19300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>513900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>348900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>394500</v>
+      </c>
+      <c r="E83" s="3">
         <v>383700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>43800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>385200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>393600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>476400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-454700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>594700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>663700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>726200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>598300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>609000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>859100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>603300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>700000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>611300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>635000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1267200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>744900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>722500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>842100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>795400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>764600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>756300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>666600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>641700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>437000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>571000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>567700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>597600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>701200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>610700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>662200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>630900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>3456500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1136300</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>645800</v>
+      </c>
+      <c r="E89" s="3">
         <v>724500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>712600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>686200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>708100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>795300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>879700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>788100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>531100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>583400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>880800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1026700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>909600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>893000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>801700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1199300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>924400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1017300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1171000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1106800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1246300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1152100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>774300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1405400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>703500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1071600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>926100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1107200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>895600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>880500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1064600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1399400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1343300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1129900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>4904600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1293700</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-278400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-286000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-320800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-260000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-290300</v>
-      </c>
       <c r="H91" s="3">
+        <v>-279300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-352800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-312600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-299200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-336200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-455400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9177000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4428000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5665000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4491000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4936000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4134000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-439000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-535400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-504100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1395900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>571200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-610400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>1000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>32500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-101800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-827500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1315200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>484600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-568500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-523100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-449500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-530800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1393000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2925500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-500200</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-343800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-289100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-324900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-271100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-291300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-169400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-250200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-297600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-358500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-835800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1082500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-289100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-521000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-292700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-469500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-266300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-433500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-443000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>252400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-349300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-562400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-499100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1439700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2515000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-535700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-564800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-906400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1771500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-563600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-511600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>50900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-662400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2602200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,118 +9520,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>643100</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>541900</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
         <v>649800</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>601000</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>645800</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>-565900</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-663700</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-526500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-23400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-633100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-623200</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-695500</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-631400</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-741900</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1368800</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-639200</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-606500</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-747500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-30800</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1386600</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-667900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-495100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-947700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-126900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1074700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-538900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>393000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-765400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-383900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>646200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-368600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-174300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1472900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-255600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-933400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-636000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-726000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-311400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1074200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-653300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-893600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-302200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1248800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-253200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1835400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>209000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1683300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1548700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-652600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-311900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1372300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-107900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1948200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1114300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>503100</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E101" s="3">
         <v>12200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>14000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>42100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-25800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>71300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>22300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-16100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-23900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>73200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>21000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>19600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-37400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>20100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-24300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-26100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-37000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-38800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>154000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>10400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>93000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>10700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-29500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>72600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-60200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>15500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>26300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-55000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-70700</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-355600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-59800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-556600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>279300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-672400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>99200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1023900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-274300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-197300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>435900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-594200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>636500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1063300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>331300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-581600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>259600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-215000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>238600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>323100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>67300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-248400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>504800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1900700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1268800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1989000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>700100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1652800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1326600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-211700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-24400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-864300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1083000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-642900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>373700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1133100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1819800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>TELNY</t>
   </si>
@@ -656,170 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -856,86 +863,92 @@
       <c r="N8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="3">
         <v>1849500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1847400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2659500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2562100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1417100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2515000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2550100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2583900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2483500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3039500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3219500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3236500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>3165100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>3421100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3112400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>3010000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2674300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2820000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>2813600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>2777400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>2247000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>3179900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>3280600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>3402600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>15461200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>3853000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,86 +985,92 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
         <v>458300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>406600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>696700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>680400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>426600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>628700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>647300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>686400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>780400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>702800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>780300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>795900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>785200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>816200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>725100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>700800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>588400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>619800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>662700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>632900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>523300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>725500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>760900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>1192600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>5577700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>1329500</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1088,86 +1107,92 @@
       <c r="N10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1391200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1440800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1962700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1881600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>990500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1886300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1902900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1897500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1703200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2336700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>2439200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2440500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>2380000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2605000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>2387300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>2309300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>2085900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>2200200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>2150900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>2144500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1723800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>2454400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>2519700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>2210000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>9883500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>2523500</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1233,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1351,14 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1473,14 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1478,86 +1517,92 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>32100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>10500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>259800</v>
-      </c>
-      <c r="R14" s="3">
-        <v>16900</v>
-      </c>
-      <c r="S14" s="3">
-        <v>93600</v>
       </c>
       <c r="T14" s="3">
         <v>16900</v>
       </c>
       <c r="U14" s="3">
+        <v>93600</v>
+      </c>
+      <c r="V14" s="3">
+        <v>16900</v>
+      </c>
+      <c r="W14" s="3">
         <v>13700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>10300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>15300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>10900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>147800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>37000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>37100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>5200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>26900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>20700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>268700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>25500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>26600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>18600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>59900</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>55600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>718100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>-82400</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AO14" s="3">
         <v>158900</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AP14" s="3">
         <v>707900</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1594,86 +1639,92 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3">
         <v>410300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>394500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>622000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>603300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>360100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>607100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>603000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>599100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>459400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>722500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>761100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>722000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>756200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>757100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>666800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>637800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>462800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>553400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>529200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>547800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>457600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>556300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>570100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>581900</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AO15" s="3">
         <v>2414600</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AP15" s="3">
         <v>617700</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,8 +1762,10 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1749,86 +1802,92 @@
       <c r="N17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1543100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1376400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2368500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1912500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1395100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1956000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2017600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2050200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1679400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2209800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2664400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2547000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2550200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2612300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2398400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2269400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>2378100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2132300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>2221000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>2183200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>1893900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>2354800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>3111300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>2705400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>12375000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>3663500</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1865,86 +1924,92 @@
       <c r="N18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="3">
         <v>306400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>471100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>291000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>649600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>22000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>558900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>532500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>533700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>804100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>829700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>555100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>689500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>614900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>808800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>714000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>740600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>296200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>687700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>592500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>594300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>353200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>825100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>169300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>697100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>3086200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>189500</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,8 +2050,10 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2023,86 +2090,92 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>90500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-228500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-211300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>15700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-9600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-86700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-59500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>19500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>219500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>49700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>120200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-404300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>85200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-202000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>7100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>62800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-258100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>9800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-124000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>233900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-45200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>211800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>102900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>100400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>-323500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>90900</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2139,86 +2212,92 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>995100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>851500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>938900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1268700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>712400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1083600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1108000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1820400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1768500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1602000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1517400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1080600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1464700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1363200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1387700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1445100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>516500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>1017600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>1422600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>1009200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>1647600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>934400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>1428400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>6219100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>1416700</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2255,86 +2334,92 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
         <v>123300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>43700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>58700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>45200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>48700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>61000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>61600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>60700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>110900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>107400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>85400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>89800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>173900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>135400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>117100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>100900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>104900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>45900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>46200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>30500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>105800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>54700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>72700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>72500</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>382700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2371,86 +2456,92 @@
       <c r="N23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="3">
         <v>273600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>198800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>21100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>620100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-36300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>411200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>411400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>492600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>912600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>772100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>589800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>195400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>526300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>471500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>603900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>702600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-66900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>651500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>422300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>797600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>202200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>982200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>199500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>725000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>2379900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>210800</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2487,86 +2578,92 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-166900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>78100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-36300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-100500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>39800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>134300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>138100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>154900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>158700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>217500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>221300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>69100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>147500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>483800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>216100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>203000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>55800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>205700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>125000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>235000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>77200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>272900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>186400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>197900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>730400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,8 +2778,14 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2719,86 +2822,92 @@
       <c r="N26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3">
         <v>440500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>120700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>57400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>720600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-76100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>276900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>273200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>337700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>754000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>554600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>368500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>126300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>378700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>387800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>499600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-122700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>445800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>297300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>562700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>124900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>709300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>13100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>527100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>1649500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2835,86 +2944,92 @@
       <c r="N27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="3">
         <v>399500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>47500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-16100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>656000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-142100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>203200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>197800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>266500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>668600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>461100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>266200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>9600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>277900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-113600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>302100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>397100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-160200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>370200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>208100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>484100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>46100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>623500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-79500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>441500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>1282600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>-93500</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3144,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3067,86 +3188,92 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3">
         <v>3165300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>99000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-89500</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-32700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>147100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>39200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>7600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>-631800</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>127800</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>225600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>67900</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>-86600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>31900</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>28000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>35400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>297100</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AH29" s="3">
         <v>231400</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AI29" s="3">
         <v>62500</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AJ29" s="3">
         <v>26600</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AK29" s="3">
         <v>211500</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AL29" s="3">
         <v>42800</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AM29" s="3">
         <v>60200</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AN29" s="3">
         <v>72400</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AO29" s="3">
         <v>-933600</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AP29" s="3">
         <v>-501000</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3388,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,8 +3510,14 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3415,86 +3554,92 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-90500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>228500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>211300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-15700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>9600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>86700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>59500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-19500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-219500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-49700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-120200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>404300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-85200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>202000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-62800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>258100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>124000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-233900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>45200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-211800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-102900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-100400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>323500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-90900</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3531,86 +3676,92 @@
       <c r="N33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="3">
         <v>3564800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>146500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-105600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>623200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>5000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>242400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>205500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-365300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>796400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>458600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>491800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>77400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>191400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-81700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>330100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>432600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>136900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>601600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>270600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>510700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>257600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>666400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-19300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>513900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>348900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,8 +3876,14 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3763,207 +3920,219 @@
       <c r="N35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35" s="3">
         <v>3564800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>146500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-105600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>623200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>5000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>242400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>205500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-365300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>796400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>458600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>491800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>77400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>191400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-81700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>330100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>432600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>136900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>601600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>270600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>510700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>257600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>666400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-19300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>513900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>348900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4173,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4217,132 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4889200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1620400</v>
+      </c>
+      <c r="F41" s="3">
         <v>1055500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>614900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>921700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>913700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1582900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1306100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1926200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1928500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>910500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1168300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1371900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>933700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1534600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>892800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1972900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1431900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2018200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1852900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2139500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2131400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1771000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1855300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2006900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1534800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>3841300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>4899600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>1569900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2086300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>3345800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>1900500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>2144100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>2610600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>3448500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>2389300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>3222400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>2846400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>3399800</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4171,927 +4350,975 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>44600</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>35300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>135700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>245900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>125400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>32200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>30400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>30300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>31300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>33900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>69500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>57500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>62000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>78900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>93000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>71500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>54300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>59700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>54500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>65400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>93700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>100700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>80600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>97200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>103000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>76500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>93200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>83200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>69000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>187800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>189300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>192000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>297900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>306900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1291500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1145900</v>
+      </c>
+      <c r="F43" s="3">
         <v>1370300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1354900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1277300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1143800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1343400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1375500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1380000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1453000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1393300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1453400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1568500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1771900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2146100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2167600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2025600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2044800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>2132100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2213800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2213800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>2730300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2652100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2945000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>3052900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>3000200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>3410000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>2509600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>3068800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>2537200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>2310300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>2155700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>2118400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>2990300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>2713200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>2991200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>3085500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>3158100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>2854000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>85500</v>
+      </c>
+      <c r="F44" s="3">
         <v>90500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>91300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>83400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>77200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>83700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>82000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>94500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>94200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>99800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>116300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>122700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>146600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>174000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>158600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>148200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>147000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>103400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>121500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>149300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>136000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>127100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>142500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>172600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>164400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>163400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>133400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>168100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>192100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>101800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>115000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>149800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>205300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>174100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>200000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>210800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>222200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>175900</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>969600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>48000</v>
+      </c>
+      <c r="F45" s="3">
         <v>200400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>122100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>139100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>23500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>38300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>45400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>56500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>209600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>46400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>47300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>25000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>140200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>141300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>154900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>140900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>421300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>417800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>385700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>143600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>128400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>141200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>187400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>599400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>386200</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF45" s="3">
         <v>395000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>101800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>439600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>2973600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>3045100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>197100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>178000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>117900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>438000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7255400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3167800</v>
+      </c>
+      <c r="F46" s="3">
         <v>2802900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2285800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2503000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2416500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3234800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3103800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3640400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3920600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2565300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2885200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3171000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3026400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4065600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3431500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4349600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4123900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>4764600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4645400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>4700400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>5185700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4746000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>5195700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>5925500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>5186200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>7495400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>7639800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>5304800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>4993900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>6290700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>7227900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>7526400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>6191100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>6703100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>5890400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>7254600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>6533800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>6691100</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3200600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>7189600</v>
+      </c>
+      <c r="F47" s="3">
         <v>6409900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>6516500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>5951400</v>
       </c>
-      <c r="G47" s="3">
-        <v>6343500</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
+        <v>6369800</v>
+      </c>
+      <c r="J47" s="3">
         <v>6414000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>5474200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>5489700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>5518400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>5724600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>5865500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>5749600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3732100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>576900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>558400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>532200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>534500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>533300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>565300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>587200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>664700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>826000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>847800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>543800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>475800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>272000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>253700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>486700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>268700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>52000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>53500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>53300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>55600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>51200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>51200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>1738500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>1944800</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>1690700</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7255200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>7130300</v>
+      </c>
+      <c r="F48" s="3">
         <v>7720700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7700800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7445300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7112000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7471100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7340700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>7417400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>7639000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>7465400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>7587900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>7683400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>10470900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>11988200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>11906500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>11630300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>11694700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>11352200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>11879500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>11961800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>14727000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>14716600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>16542600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>17296600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>15778500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>16995100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>14544500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>16139200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>8276600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>7060600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>7104000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>6984200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>8748700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>8271800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>8497000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>9027500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>8879600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>8405100</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3529000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3591100</v>
+      </c>
+      <c r="F49" s="3">
         <v>3571700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3578200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3333200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3156500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3393000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3271200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3293200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3403300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3227700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3334400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3352000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3481600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3674300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3603500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>3422500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>3540700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3501700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>3610100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>3575500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>4160700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>4237300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>4643000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>4839800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>4296700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>5123000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>2361900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>4394900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>5728300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>3698000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>3864400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>4002500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>6605500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>6627500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>6847600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>6962500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>7099100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>7250400</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5433,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5555,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1202900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>27000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1215700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1181900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1220300</v>
       </c>
-      <c r="G52" s="3">
-        <v>142300</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>116100</v>
+      </c>
+      <c r="J52" s="3">
         <v>1233800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1198500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1346200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>95800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1612000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1628600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1912600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1788000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1789400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1772500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1564500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1339300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1285100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1453900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1509100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1833200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1877000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2144700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2457300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1810800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2484200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2288400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>1852300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>2311800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1982900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>1485500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>1533000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>1761500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>1790700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>2147400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>850000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>981800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>874400</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5799,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22751400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>21987700</v>
+      </c>
+      <c r="F54" s="3">
         <v>22172000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>21680900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>20864300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>20140000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>22066300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>20703500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>21577000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>21535400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>20953700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>21761100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>22376200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>22499000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>22094300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>21272400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>21499100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>21233100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>21436900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>22154100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>22334000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>26571300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>26402800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>29373700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>31063100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>27548100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>32369600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>27088300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>28177900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>21579300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>19084400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>19735400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>20099400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>23362400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>23444200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>23433600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>25833200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>25439100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>24911800</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5969,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,704 +6013,742 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2069000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>646000</v>
+      </c>
+      <c r="F57" s="3">
         <v>2163900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2114900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2109600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>584100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2025300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2059400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2031600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>542500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1946100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2019500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2104300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2654500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2980200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2954800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2927300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3040000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2817800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2822500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2982600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>3510400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3344800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3834100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>4089800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>3950300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>4383300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>3795600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>4040600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>4256500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>3576100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>3484800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>3486000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>4665800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>4258800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>4539200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>4887000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>5288300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>4924500</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1552000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1613700</v>
+      </c>
+      <c r="F58" s="3">
         <v>1732900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1670800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1073800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1337400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2118600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2025300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1380400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1620600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>939500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1613400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1422800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1489900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1679300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1238600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1486400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1528800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1664800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>2078100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1462000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1718800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1883200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>2466100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>2069500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2662500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>4165700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3453100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>2723400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1775800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1588700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>2615700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>2051000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>2629600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>2984700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>3083000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>4001300</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>3202100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>3174000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1339600</v>
+      </c>
+      <c r="F59" s="3">
         <v>1453800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1412700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>824000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1158800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1292100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1273100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>745100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1299300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1318200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1275000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>830400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>912800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1683400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1622000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1133200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1278700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1728800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1762500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1005200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1041100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1639300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1928100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1480500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1470400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2325000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2159400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1504100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1578100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>2654800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>2280400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>1900000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>1583800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>2214000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>2207700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>1558500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>1079900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>1033600</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4621900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4591500</v>
+      </c>
+      <c r="F60" s="3">
         <v>5350600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5198400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4007400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4082800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5436000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5357900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4157100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4535400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4203800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4908000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>4357500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>5057200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6342800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>5815400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>5546800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>5847400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>6211400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>6663100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>5449900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>6270300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>6867300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>8228300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>7639800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>8083200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>10873900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>9408000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>8268000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>7610400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>7819600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>8380900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>7437000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>8879100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>9457500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>9829900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>10446800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>9570300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>9132100</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8414700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>8490100</v>
+      </c>
+      <c r="F61" s="3">
         <v>8230500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>8217800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7975200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7607400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7830100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>7509900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>8333300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8765700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>8055600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>8287200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>7990300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>10075500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>11255800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>11328000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>10733700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>10902700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>10874900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>11236200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>11596800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>13901600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>13888300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>15270500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>15872400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>12837700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>14534900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>11137800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>13131100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>6309600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>4548900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>4739300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>4852400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>5973300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>5762600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>5949300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>6540000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>7446200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>7214000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>804500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>767000</v>
+      </c>
+      <c r="F62" s="3">
         <v>772600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>776400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>775000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>729100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>723500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>714600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>724400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>775600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>714300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>724700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>799100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1312400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1686600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1562100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1481200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1520100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1510500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1560100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1579800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1850400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1790500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2093100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2227800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1830500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1962200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1408000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1872300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1515700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1260900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1244500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>1065200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>1292200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>1284700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>1223900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>1479700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>1592300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>1503800</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6863,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6985,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +7107,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14437000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14485300</v>
+      </c>
+      <c r="F66" s="3">
         <v>14973200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>14778100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>13293400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>12942300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>14468700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>14040700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>13703200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>14589500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>13445800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>14395700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>13641900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>16843600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>19755200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>19206700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>18282800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>18759900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>19035000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>19933600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>19135300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>22601700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>23108300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>26282800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>26436000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>23336400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>27950500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>22521100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>23869900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>16000800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>14120200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>14910200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>13911100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>16704900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>17006400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>17551000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>19074800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>19165800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>18363900</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7277,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7395,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7517,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7639,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7761,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9398100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>8265800</v>
+      </c>
+      <c r="F72" s="3">
         <v>8534000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>8126500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>8709200</v>
       </c>
-      <c r="G72" s="3">
-        <v>7871800</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
+        <v>7871400</v>
+      </c>
+      <c r="J72" s="3">
         <v>8400900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>7993300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>8839200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>8301100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>8613400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>8340700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>9713600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>5180800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1730200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1549800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>2847700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2111700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2030300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1803800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2791900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>3421800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2516200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>2252700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>3551600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>3562800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>3647400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>3964700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>5195400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>4828000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>4471800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>4521900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>5777800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>6005900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>5929300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>5278900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>5612000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>5136300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>5466800</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8005,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8127,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8249,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7779400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6991500</v>
+      </c>
+      <c r="F76" s="3">
         <v>6707600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6383000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>7017800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>6676900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>7081800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>6088800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7259700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>6359100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6962400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>6840500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>8201600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5655400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2339100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2065800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>3216200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2473200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2401900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2220500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>3198700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>3969600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>3294600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>3090900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4627100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4211700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>4419100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>4567200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>4308000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>5578500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>4964200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>4825200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>6188300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>6657500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>6437800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>5882600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>6758400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>6273400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>6547800</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,129 +8493,141 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8275,86 +8664,92 @@
       <c r="N81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81" s="3">
         <v>3564800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>146500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-105600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>623200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>5000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>242400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>205500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-365300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>796400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>458600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>491800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>77400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>191400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-81700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>330100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>432600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>136900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>601600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>270600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>510700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>257600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>666400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-19300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>513900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>348900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8790,132 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>408400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>39100</v>
+      </c>
+      <c r="F83" s="3">
         <v>399900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>394500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>383700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>43800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>385200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>393600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>476400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>-454700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>594700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>663700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>726200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>598300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>609000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>859100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>603300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>700000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>611300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>635000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1267200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>744900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>722500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>842100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>795400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>764600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>756300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>666600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>641700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>437000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>571000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>567700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>597600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>701200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>610700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>662200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>630900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>3456500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>1136300</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9030,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9152,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9274,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9396,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9518,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>594800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>861100</v>
+      </c>
+      <c r="F89" s="3">
         <v>839800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>645800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>724500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>712600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>686200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>708100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>795300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>879700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>788100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>531100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>583400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>880800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1026700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>909600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>893000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>801700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1199300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>924400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1017300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1171000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1106800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1246300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1152100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>774300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1405400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>703500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1071600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>926100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1107200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>895600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>880500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>1064600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>1399400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>1343300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>1129900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>4904600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>1293700</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9688,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-271000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-284000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-259000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-278400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-286000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-320800</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>-305000</v>
+      </c>
+      <c r="J91" s="3">
         <v>-253300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-279300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-352800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-312600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-299200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-336200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-455400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-9177000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-4428000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-5665000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-4491000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-4936000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-4134000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-439000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-535400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-504100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-1395900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>571200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-610400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>1000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>32500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-101800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-827500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-1315200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>484600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-568500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-523100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-449500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-530800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-1393000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-2925500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-500200</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9928,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +10050,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2820800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-65400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-266300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-343800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-289100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-324900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-271100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-291300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-169400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-250200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-297600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-358500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-835800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1082500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-289100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-521000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-292700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-469500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-266300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-433500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-443000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>252400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-349300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-562400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-499100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1439700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-2515000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-535700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-564800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-906400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>1771500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-563600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-511600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>50900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-662400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-2602200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,124 +10220,132 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
+        <v>624400</v>
+      </c>
+      <c r="F96" s="3">
         <v>33500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>643100</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
         <v>541900</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>649800</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>601000</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3">
         <v>645800</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-565900</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-663700</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-526500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-23400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-633100</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-623200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-695500</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-631400</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-741900</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1368800</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-639200</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-606500</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-747500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-30800</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-1386600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10460,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10582,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10704,376 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-159800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-190800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-131700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-667900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-495100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-947700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-126900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1074700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-538900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>393000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-765400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-383900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>646200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-368600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-174300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1472900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-255600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-933400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-636000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-726000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-311400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1074200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-653300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-893600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-302200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1248800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-253200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>1835400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>209000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-1683300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-1548700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-652600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-311900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-1372300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-107900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-1948200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-1114300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>503100</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-8900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-14500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>12200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>14000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>42100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-25800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>71300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>22300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-16100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-23900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>73200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>21000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-13400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>19600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-37400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>20100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-24300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-26100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-37000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-38800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>154000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>10400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>93000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>10700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-29500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>72600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>-60200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>15500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>26300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-55000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>-70700</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3217000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>597600</v>
+      </c>
+      <c r="F102" s="3">
         <v>436200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-355600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-59800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-556600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>279300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-672400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>99200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1023900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-274300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-197300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>435900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-594200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>636500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1063300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>331300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-581600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>259600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-215000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>238600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>323100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>67300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-248400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>504800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-1900700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1268800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>1989000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>700100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-1652800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>1326600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-211700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-864300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>1083000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-642900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>373700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>1133100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>1819800</v>
       </c>
     </row>
